--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="613">
   <si>
     <t>Main Field</t>
   </si>
@@ -1635,12 +1635,6 @@
     <t>LP07000</t>
   </si>
   <si>
-    <t>LP07004</t>
-  </si>
-  <si>
-    <t>Twabi Milley</t>
-  </si>
-  <si>
     <t>LP07007</t>
   </si>
   <si>
@@ -1746,24 +1740,12 @@
     <t>Petro  Mchinga</t>
   </si>
   <si>
-    <t>LF08014</t>
-  </si>
-  <si>
-    <t>Alice Sumaili</t>
-  </si>
-  <si>
     <t>LF08017</t>
   </si>
   <si>
     <t>James Glad</t>
   </si>
   <si>
-    <t>LF08019</t>
-  </si>
-  <si>
-    <t>Phillip Martin Banda</t>
-  </si>
-  <si>
     <t>LF08024</t>
   </si>
   <si>
@@ -1819,18 +1801,6 @@
   </si>
   <si>
     <t>LF10000</t>
-  </si>
-  <si>
-    <t>LP10007</t>
-  </si>
-  <si>
-    <t>Dickson Kampanje</t>
-  </si>
-  <si>
-    <t>LF1001</t>
-  </si>
-  <si>
-    <t>Nora Boni</t>
   </si>
   <si>
     <t>LF1003</t>
@@ -2250,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K309"/>
+  <dimension ref="A1:K304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2320,7 +2290,7 @@
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2355,7 +2325,7 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2390,7 +2360,7 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2425,7 +2395,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2460,7 +2430,7 @@
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2495,7 +2465,7 @@
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2530,7 +2500,7 @@
         <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2565,7 +2535,7 @@
         <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2600,7 +2570,7 @@
         <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2635,7 +2605,7 @@
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2670,7 +2640,7 @@
         <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2705,7 +2675,7 @@
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2740,7 +2710,7 @@
         <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2775,7 +2745,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2810,7 +2780,7 @@
         <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2845,7 +2815,7 @@
         <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2880,7 +2850,7 @@
         <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2915,7 +2885,7 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2950,7 +2920,7 @@
         <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2985,7 +2955,7 @@
         <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3020,7 +2990,7 @@
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3055,7 +3025,7 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3090,7 +3060,7 @@
         <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3125,7 +3095,7 @@
         <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3160,7 +3130,7 @@
         <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3195,7 +3165,7 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3230,7 +3200,7 @@
         <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3265,7 +3235,7 @@
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3300,7 +3270,7 @@
         <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3335,7 +3305,7 @@
         <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3370,7 +3340,7 @@
         <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3405,7 +3375,7 @@
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3440,7 +3410,7 @@
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3475,7 +3445,7 @@
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3510,7 +3480,7 @@
         <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3545,7 +3515,7 @@
         <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3580,7 +3550,7 @@
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3615,7 +3585,7 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3650,7 +3620,7 @@
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3685,7 +3655,7 @@
         <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3720,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3755,7 +3725,7 @@
         <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3790,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3825,7 +3795,7 @@
         <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3860,7 +3830,7 @@
         <v>17</v>
       </c>
       <c r="K46" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3895,7 +3865,7 @@
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3930,7 +3900,7 @@
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3965,7 +3935,7 @@
         <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4000,7 +3970,7 @@
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4035,7 +4005,7 @@
         <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4070,7 +4040,7 @@
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4105,7 +4075,7 @@
         <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4140,7 +4110,7 @@
         <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4175,7 +4145,7 @@
         <v>17</v>
       </c>
       <c r="K55" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4210,7 +4180,7 @@
         <v>17</v>
       </c>
       <c r="K56" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4245,7 +4215,7 @@
         <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4280,7 +4250,7 @@
         <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4315,7 +4285,7 @@
         <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4350,7 +4320,7 @@
         <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4385,7 +4355,7 @@
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4420,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4455,7 +4425,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4490,7 +4460,7 @@
         <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4525,7 +4495,7 @@
         <v>17</v>
       </c>
       <c r="K65" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4560,7 +4530,7 @@
         <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4595,7 +4565,7 @@
         <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4630,7 +4600,7 @@
         <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4665,7 +4635,7 @@
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4700,7 +4670,7 @@
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4735,7 +4705,7 @@
         <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4770,7 +4740,7 @@
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4805,7 +4775,7 @@
         <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4840,7 +4810,7 @@
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4875,7 +4845,7 @@
         <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4910,7 +4880,7 @@
         <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4945,7 +4915,7 @@
         <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4980,7 +4950,7 @@
         <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5015,7 +4985,7 @@
         <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5050,7 +5020,7 @@
         <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5085,7 +5055,7 @@
         <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5120,7 +5090,7 @@
         <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5155,7 +5125,7 @@
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5190,7 +5160,7 @@
         <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5225,7 +5195,7 @@
         <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5260,7 +5230,7 @@
         <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -5295,7 +5265,7 @@
         <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5330,7 +5300,7 @@
         <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5365,7 +5335,7 @@
         <v>17</v>
       </c>
       <c r="K89" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5400,7 +5370,7 @@
         <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5435,7 +5405,7 @@
         <v>17</v>
       </c>
       <c r="K91" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5470,7 +5440,7 @@
         <v>17</v>
       </c>
       <c r="K92" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5505,7 +5475,7 @@
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5540,7 +5510,7 @@
         <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5575,7 +5545,7 @@
         <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5610,7 +5580,7 @@
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5645,7 +5615,7 @@
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5680,7 +5650,7 @@
         <v>17</v>
       </c>
       <c r="K98" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5715,7 +5685,7 @@
         <v>17</v>
       </c>
       <c r="K99" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5750,7 +5720,7 @@
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5785,7 +5755,7 @@
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5820,7 +5790,7 @@
         <v>17</v>
       </c>
       <c r="K102" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5855,7 +5825,7 @@
         <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5890,7 +5860,7 @@
         <v>17</v>
       </c>
       <c r="K104" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5925,7 +5895,7 @@
         <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5960,7 +5930,7 @@
         <v>17</v>
       </c>
       <c r="K106" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -5995,7 +5965,7 @@
         <v>17</v>
       </c>
       <c r="K107" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6030,7 +6000,7 @@
         <v>17</v>
       </c>
       <c r="K108" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6065,7 +6035,7 @@
         <v>17</v>
       </c>
       <c r="K109" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6100,7 +6070,7 @@
         <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6135,7 +6105,7 @@
         <v>17</v>
       </c>
       <c r="K111" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6170,7 +6140,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6205,7 +6175,7 @@
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6240,7 +6210,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6275,7 +6245,7 @@
         <v>17</v>
       </c>
       <c r="K115" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6310,7 +6280,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6345,7 +6315,7 @@
         <v>17</v>
       </c>
       <c r="K117" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6380,7 +6350,7 @@
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6415,7 +6385,7 @@
         <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6450,7 +6420,7 @@
         <v>17</v>
       </c>
       <c r="K120" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6485,7 +6455,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6520,7 +6490,7 @@
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6555,7 +6525,7 @@
         <v>17</v>
       </c>
       <c r="K123" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6590,7 +6560,7 @@
         <v>17</v>
       </c>
       <c r="K124" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6625,7 +6595,7 @@
         <v>17</v>
       </c>
       <c r="K125" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6660,7 +6630,7 @@
         <v>17</v>
       </c>
       <c r="K126" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6695,7 +6665,7 @@
         <v>17</v>
       </c>
       <c r="K127" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6730,7 +6700,7 @@
         <v>17</v>
       </c>
       <c r="K128" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6765,7 +6735,7 @@
         <v>17</v>
       </c>
       <c r="K129" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6800,7 +6770,7 @@
         <v>17</v>
       </c>
       <c r="K130" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6835,7 +6805,7 @@
         <v>17</v>
       </c>
       <c r="K131" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6870,7 +6840,7 @@
         <v>17</v>
       </c>
       <c r="K132" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6905,7 +6875,7 @@
         <v>17</v>
       </c>
       <c r="K133" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6940,7 +6910,7 @@
         <v>17</v>
       </c>
       <c r="K134" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6975,7 +6945,7 @@
         <v>17</v>
       </c>
       <c r="K135" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -7010,7 +6980,7 @@
         <v>17</v>
       </c>
       <c r="K136" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7045,7 +7015,7 @@
         <v>17</v>
       </c>
       <c r="K137" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7080,7 +7050,7 @@
         <v>17</v>
       </c>
       <c r="K138" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7115,7 +7085,7 @@
         <v>17</v>
       </c>
       <c r="K139" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -7150,7 +7120,7 @@
         <v>17</v>
       </c>
       <c r="K140" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7185,7 +7155,7 @@
         <v>17</v>
       </c>
       <c r="K141" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7220,7 +7190,7 @@
         <v>17</v>
       </c>
       <c r="K142" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7255,7 +7225,7 @@
         <v>17</v>
       </c>
       <c r="K143" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7290,7 +7260,7 @@
         <v>17</v>
       </c>
       <c r="K144" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7325,7 +7295,7 @@
         <v>17</v>
       </c>
       <c r="K145" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7360,7 +7330,7 @@
         <v>17</v>
       </c>
       <c r="K146" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7395,7 +7365,7 @@
         <v>17</v>
       </c>
       <c r="K147" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7430,7 +7400,7 @@
         <v>17</v>
       </c>
       <c r="K148" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7465,7 +7435,7 @@
         <v>17</v>
       </c>
       <c r="K149" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7500,7 +7470,7 @@
         <v>17</v>
       </c>
       <c r="K150" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7535,7 +7505,7 @@
         <v>17</v>
       </c>
       <c r="K151" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7570,7 +7540,7 @@
         <v>17</v>
       </c>
       <c r="K152" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7605,7 +7575,7 @@
         <v>17</v>
       </c>
       <c r="K153" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7640,7 +7610,7 @@
         <v>17</v>
       </c>
       <c r="K154" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7675,7 +7645,7 @@
         <v>17</v>
       </c>
       <c r="K155" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7710,7 +7680,7 @@
         <v>17</v>
       </c>
       <c r="K156" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7745,7 +7715,7 @@
         <v>17</v>
       </c>
       <c r="K157" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7780,7 +7750,7 @@
         <v>17</v>
       </c>
       <c r="K158" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7815,7 +7785,7 @@
         <v>17</v>
       </c>
       <c r="K159" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7850,7 +7820,7 @@
         <v>17</v>
       </c>
       <c r="K160" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7885,7 +7855,7 @@
         <v>17</v>
       </c>
       <c r="K161" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7920,7 +7890,7 @@
         <v>17</v>
       </c>
       <c r="K162" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -7955,7 +7925,7 @@
         <v>17</v>
       </c>
       <c r="K163" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7990,7 +7960,7 @@
         <v>17</v>
       </c>
       <c r="K164" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -8025,7 +7995,7 @@
         <v>17</v>
       </c>
       <c r="K165" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -8060,7 +8030,7 @@
         <v>17</v>
       </c>
       <c r="K166" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8095,7 +8065,7 @@
         <v>17</v>
       </c>
       <c r="K167" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8130,7 +8100,7 @@
         <v>17</v>
       </c>
       <c r="K168" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8165,7 +8135,7 @@
         <v>17</v>
       </c>
       <c r="K169" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8200,7 +8170,7 @@
         <v>17</v>
       </c>
       <c r="K170" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -8235,7 +8205,7 @@
         <v>17</v>
       </c>
       <c r="K171" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -8270,7 +8240,7 @@
         <v>17</v>
       </c>
       <c r="K172" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8305,7 +8275,7 @@
         <v>17</v>
       </c>
       <c r="K173" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8340,7 +8310,7 @@
         <v>17</v>
       </c>
       <c r="K174" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8375,7 +8345,7 @@
         <v>17</v>
       </c>
       <c r="K175" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8410,7 +8380,7 @@
         <v>17</v>
       </c>
       <c r="K176" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8445,7 +8415,7 @@
         <v>17</v>
       </c>
       <c r="K177" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8480,7 +8450,7 @@
         <v>17</v>
       </c>
       <c r="K178" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8515,7 +8485,7 @@
         <v>17</v>
       </c>
       <c r="K179" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8550,7 +8520,7 @@
         <v>17</v>
       </c>
       <c r="K180" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8585,7 +8555,7 @@
         <v>17</v>
       </c>
       <c r="K181" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8620,7 +8590,7 @@
         <v>17</v>
       </c>
       <c r="K182" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8655,7 +8625,7 @@
         <v>17</v>
       </c>
       <c r="K183" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8690,7 +8660,7 @@
         <v>17</v>
       </c>
       <c r="K184" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8725,7 +8695,7 @@
         <v>17</v>
       </c>
       <c r="K185" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,7 +8730,7 @@
         <v>17</v>
       </c>
       <c r="K186" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8795,7 +8765,7 @@
         <v>17</v>
       </c>
       <c r="K187" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8830,7 +8800,7 @@
         <v>17</v>
       </c>
       <c r="K188" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8865,7 +8835,7 @@
         <v>17</v>
       </c>
       <c r="K189" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8900,7 +8870,7 @@
         <v>17</v>
       </c>
       <c r="K190" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8935,7 +8905,7 @@
         <v>17</v>
       </c>
       <c r="K191" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8970,7 +8940,7 @@
         <v>17</v>
       </c>
       <c r="K192" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -9005,7 +8975,7 @@
         <v>17</v>
       </c>
       <c r="K193" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -9040,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="K194" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -9075,7 +9045,7 @@
         <v>17</v>
       </c>
       <c r="K195" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9110,7 +9080,7 @@
         <v>17</v>
       </c>
       <c r="K196" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9145,7 +9115,7 @@
         <v>17</v>
       </c>
       <c r="K197" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9180,7 +9150,7 @@
         <v>17</v>
       </c>
       <c r="K198" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9215,7 +9185,7 @@
         <v>17</v>
       </c>
       <c r="K199" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9250,7 +9220,7 @@
         <v>17</v>
       </c>
       <c r="K200" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9285,7 +9255,7 @@
         <v>17</v>
       </c>
       <c r="K201" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9320,7 +9290,7 @@
         <v>17</v>
       </c>
       <c r="K202" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9355,7 +9325,7 @@
         <v>17</v>
       </c>
       <c r="K203" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9390,7 +9360,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9425,7 +9395,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9460,7 +9430,7 @@
         <v>17</v>
       </c>
       <c r="K206" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9495,7 +9465,7 @@
         <v>17</v>
       </c>
       <c r="K207" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9530,7 +9500,7 @@
         <v>17</v>
       </c>
       <c r="K208" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9565,7 +9535,7 @@
         <v>17</v>
       </c>
       <c r="K209" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9600,7 +9570,7 @@
         <v>17</v>
       </c>
       <c r="K210" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9635,7 +9605,7 @@
         <v>17</v>
       </c>
       <c r="K211" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9670,7 +9640,7 @@
         <v>17</v>
       </c>
       <c r="K212" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9705,7 +9675,7 @@
         <v>17</v>
       </c>
       <c r="K213" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9740,7 +9710,7 @@
         <v>17</v>
       </c>
       <c r="K214" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9775,7 +9745,7 @@
         <v>17</v>
       </c>
       <c r="K215" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9810,7 +9780,7 @@
         <v>17</v>
       </c>
       <c r="K216" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9845,7 +9815,7 @@
         <v>17</v>
       </c>
       <c r="K217" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9880,7 +9850,7 @@
         <v>17</v>
       </c>
       <c r="K218" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9915,7 +9885,7 @@
         <v>17</v>
       </c>
       <c r="K219" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9950,7 +9920,7 @@
         <v>17</v>
       </c>
       <c r="K220" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9985,7 +9955,7 @@
         <v>17</v>
       </c>
       <c r="K221" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -10020,7 +9990,7 @@
         <v>17</v>
       </c>
       <c r="K222" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -10055,7 +10025,7 @@
         <v>17</v>
       </c>
       <c r="K223" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -10090,7 +10060,7 @@
         <v>17</v>
       </c>
       <c r="K224" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -10125,7 +10095,7 @@
         <v>17</v>
       </c>
       <c r="K225" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -10160,7 +10130,7 @@
         <v>17</v>
       </c>
       <c r="K226" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -10195,7 +10165,7 @@
         <v>17</v>
       </c>
       <c r="K227" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10230,7 +10200,7 @@
         <v>17</v>
       </c>
       <c r="K228" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10265,7 +10235,7 @@
         <v>17</v>
       </c>
       <c r="K229" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -10300,7 +10270,7 @@
         <v>17</v>
       </c>
       <c r="K230" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -10335,7 +10305,7 @@
         <v>17</v>
       </c>
       <c r="K231" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -10370,7 +10340,7 @@
         <v>17</v>
       </c>
       <c r="K232" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -10405,7 +10375,7 @@
         <v>17</v>
       </c>
       <c r="K233" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10440,7 +10410,7 @@
         <v>17</v>
       </c>
       <c r="K234" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -10475,7 +10445,7 @@
         <v>17</v>
       </c>
       <c r="K235" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -10510,7 +10480,7 @@
         <v>17</v>
       </c>
       <c r="K236" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -10545,7 +10515,7 @@
         <v>17</v>
       </c>
       <c r="K237" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10580,7 +10550,7 @@
         <v>17</v>
       </c>
       <c r="K238" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -10615,7 +10585,7 @@
         <v>17</v>
       </c>
       <c r="K239" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -10650,7 +10620,7 @@
         <v>17</v>
       </c>
       <c r="K240" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -10685,7 +10655,7 @@
         <v>17</v>
       </c>
       <c r="K241" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10720,7 +10690,7 @@
         <v>17</v>
       </c>
       <c r="K242" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10755,7 +10725,7 @@
         <v>17</v>
       </c>
       <c r="K243" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10790,7 +10760,7 @@
         <v>17</v>
       </c>
       <c r="K244" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10825,7 +10795,7 @@
         <v>17</v>
       </c>
       <c r="K245" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10860,7 +10830,7 @@
         <v>17</v>
       </c>
       <c r="K246" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10895,7 +10865,7 @@
         <v>17</v>
       </c>
       <c r="K247" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10930,7 +10900,7 @@
         <v>17</v>
       </c>
       <c r="K248" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10965,7 +10935,7 @@
         <v>17</v>
       </c>
       <c r="K249" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -11000,7 +10970,7 @@
         <v>17</v>
       </c>
       <c r="K250" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -11035,7 +11005,7 @@
         <v>17</v>
       </c>
       <c r="K251" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -11070,7 +11040,7 @@
         <v>17</v>
       </c>
       <c r="K252" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -11105,7 +11075,7 @@
         <v>17</v>
       </c>
       <c r="K253" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -11140,7 +11110,7 @@
         <v>17</v>
       </c>
       <c r="K254" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -11175,7 +11145,7 @@
         <v>17</v>
       </c>
       <c r="K255" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11201,7 +11171,7 @@
         <v>506</v>
       </c>
       <c r="K256" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11227,7 +11197,7 @@
         <v>506</v>
       </c>
       <c r="K257" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11253,7 +11223,7 @@
         <v>506</v>
       </c>
       <c r="K258" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11279,7 +11249,7 @@
         <v>506</v>
       </c>
       <c r="K259" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11305,7 +11275,7 @@
         <v>506</v>
       </c>
       <c r="K260" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11331,7 +11301,7 @@
         <v>506</v>
       </c>
       <c r="K261" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -11357,7 +11327,7 @@
         <v>506</v>
       </c>
       <c r="K262" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -11383,7 +11353,7 @@
         <v>506</v>
       </c>
       <c r="K263" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -11409,7 +11379,7 @@
         <v>506</v>
       </c>
       <c r="K264" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -11435,7 +11405,7 @@
         <v>506</v>
       </c>
       <c r="K265" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -11461,7 +11431,7 @@
         <v>506</v>
       </c>
       <c r="K266" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -11487,7 +11457,7 @@
         <v>506</v>
       </c>
       <c r="K267" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -11513,7 +11483,7 @@
         <v>506</v>
       </c>
       <c r="K268" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -11539,7 +11509,7 @@
         <v>506</v>
       </c>
       <c r="K269" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -11565,7 +11535,7 @@
         <v>506</v>
       </c>
       <c r="K270" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -11579,7 +11549,7 @@
         <v>539</v>
       </c>
       <c r="D271">
-        <v>2.343</v>
+        <v>2.4460000000000002</v>
       </c>
       <c r="E271" t="s">
         <v>51</v>
@@ -11591,21 +11561,21 @@
         <v>506</v>
       </c>
       <c r="K271" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B272" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C272" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D272">
-        <v>2.4460000000000002</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="E272" t="s">
         <v>51</v>
@@ -11617,12 +11587,12 @@
         <v>506</v>
       </c>
       <c r="K272" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B273" t="s">
         <v>543</v>
@@ -11630,6 +11600,9 @@
       <c r="C273" t="s">
         <v>544</v>
       </c>
+      <c r="D273">
+        <v>2.1890000000000001</v>
+      </c>
       <c r="E273" t="s">
         <v>51</v>
       </c>
@@ -11640,12 +11613,12 @@
         <v>506</v>
       </c>
       <c r="K273" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B274" t="s">
         <v>545</v>
@@ -11653,6 +11626,9 @@
       <c r="C274" t="s">
         <v>546</v>
       </c>
+      <c r="D274">
+        <v>2.1840000000000002</v>
+      </c>
       <c r="E274" t="s">
         <v>51</v>
       </c>
@@ -11663,12 +11639,12 @@
         <v>506</v>
       </c>
       <c r="K274" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B275" t="s">
         <v>547</v>
@@ -11676,6 +11652,9 @@
       <c r="C275" t="s">
         <v>548</v>
       </c>
+      <c r="D275">
+        <v>4.343</v>
+      </c>
       <c r="E275" t="s">
         <v>51</v>
       </c>
@@ -11686,12 +11665,12 @@
         <v>506</v>
       </c>
       <c r="K275" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B276" t="s">
         <v>549</v>
@@ -11699,6 +11678,9 @@
       <c r="C276" t="s">
         <v>550</v>
       </c>
+      <c r="D276">
+        <v>2.1469999999999998</v>
+      </c>
       <c r="E276" t="s">
         <v>51</v>
       </c>
@@ -11709,12 +11691,12 @@
         <v>506</v>
       </c>
       <c r="K276" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B277" t="s">
         <v>551</v>
@@ -11722,6 +11704,9 @@
       <c r="C277" t="s">
         <v>552</v>
       </c>
+      <c r="D277">
+        <v>2.3490000000000002</v>
+      </c>
       <c r="E277" t="s">
         <v>51</v>
       </c>
@@ -11732,12 +11717,12 @@
         <v>506</v>
       </c>
       <c r="K277" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B278" t="s">
         <v>553</v>
@@ -11745,6 +11730,9 @@
       <c r="C278" t="s">
         <v>554</v>
       </c>
+      <c r="D278">
+        <v>2.2909999999999999</v>
+      </c>
       <c r="E278" t="s">
         <v>51</v>
       </c>
@@ -11755,12 +11743,12 @@
         <v>506</v>
       </c>
       <c r="K278" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B279" t="s">
         <v>555</v>
@@ -11768,6 +11756,9 @@
       <c r="C279" t="s">
         <v>556</v>
       </c>
+      <c r="D279">
+        <v>2.444</v>
+      </c>
       <c r="E279" t="s">
         <v>51</v>
       </c>
@@ -11778,12 +11769,12 @@
         <v>506</v>
       </c>
       <c r="K279" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B280" t="s">
         <v>557</v>
@@ -11791,6 +11782,9 @@
       <c r="C280" t="s">
         <v>558</v>
       </c>
+      <c r="D280">
+        <v>2.9380000000000002</v>
+      </c>
       <c r="E280" t="s">
         <v>51</v>
       </c>
@@ -11801,18 +11795,21 @@
         <v>506</v>
       </c>
       <c r="K280" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B281" t="s">
         <v>559</v>
       </c>
       <c r="C281" t="s">
-        <v>560</v>
+        <v>550</v>
+      </c>
+      <c r="D281">
+        <v>2.15</v>
       </c>
       <c r="E281" t="s">
         <v>51</v>
@@ -11824,18 +11821,21 @@
         <v>506</v>
       </c>
       <c r="K281" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="B282" t="s">
         <v>561</v>
       </c>
       <c r="C282" t="s">
-        <v>552</v>
+        <v>562</v>
+      </c>
+      <c r="D282">
+        <v>2.39</v>
       </c>
       <c r="E282" t="s">
         <v>51</v>
@@ -11847,12 +11847,12 @@
         <v>506</v>
       </c>
       <c r="K282" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B283" t="s">
         <v>563</v>
@@ -11861,7 +11861,7 @@
         <v>564</v>
       </c>
       <c r="D283">
-        <v>2.39</v>
+        <v>2.008</v>
       </c>
       <c r="E283" t="s">
         <v>51</v>
@@ -11873,12 +11873,12 @@
         <v>506</v>
       </c>
       <c r="K283" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B284" t="s">
         <v>565</v>
@@ -11887,7 +11887,7 @@
         <v>566</v>
       </c>
       <c r="D284">
-        <v>2.008</v>
+        <v>2.028</v>
       </c>
       <c r="E284" t="s">
         <v>51</v>
@@ -11899,12 +11899,12 @@
         <v>506</v>
       </c>
       <c r="K284" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B285" t="s">
         <v>567</v>
@@ -11913,7 +11913,7 @@
         <v>568</v>
       </c>
       <c r="D285">
-        <v>2.028</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="E285" t="s">
         <v>51</v>
@@ -11925,12 +11925,12 @@
         <v>506</v>
       </c>
       <c r="K285" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B286" t="s">
         <v>569</v>
@@ -11939,7 +11939,7 @@
         <v>570</v>
       </c>
       <c r="D286">
-        <v>1.6639999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E286" t="s">
         <v>51</v>
@@ -11951,12 +11951,12 @@
         <v>506</v>
       </c>
       <c r="K286" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B287" t="s">
         <v>571</v>
@@ -11965,7 +11965,7 @@
         <v>572</v>
       </c>
       <c r="D287">
-        <v>1.024</v>
+        <v>2.0049999999999999</v>
       </c>
       <c r="E287" t="s">
         <v>51</v>
@@ -11977,12 +11977,12 @@
         <v>506</v>
       </c>
       <c r="K287" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B288" t="s">
         <v>573</v>
@@ -11991,7 +11991,7 @@
         <v>574</v>
       </c>
       <c r="D288">
-        <v>2.0049999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="E288" t="s">
         <v>51</v>
@@ -12003,12 +12003,12 @@
         <v>506</v>
       </c>
       <c r="K288" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B289" t="s">
         <v>575</v>
@@ -12017,7 +12017,7 @@
         <v>576</v>
       </c>
       <c r="D289">
-        <v>1.0309999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="E289" t="s">
         <v>51</v>
@@ -12029,12 +12029,12 @@
         <v>506</v>
       </c>
       <c r="K289" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B290" t="s">
         <v>577</v>
@@ -12043,7 +12043,7 @@
         <v>578</v>
       </c>
       <c r="D290">
-        <v>1.0009999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="E290" t="s">
         <v>51</v>
@@ -12055,12 +12055,12 @@
         <v>506</v>
       </c>
       <c r="K290" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B291" t="s">
         <v>579</v>
@@ -12069,7 +12069,7 @@
         <v>580</v>
       </c>
       <c r="D291">
-        <v>1.0169999999999999</v>
+        <v>1.248</v>
       </c>
       <c r="E291" t="s">
         <v>51</v>
@@ -12081,12 +12081,12 @@
         <v>506</v>
       </c>
       <c r="K291" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B292" t="s">
         <v>581</v>
@@ -12095,7 +12095,7 @@
         <v>582</v>
       </c>
       <c r="D292">
-        <v>1.89</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E292" t="s">
         <v>51</v>
@@ -12107,21 +12107,21 @@
         <v>506</v>
       </c>
       <c r="K292" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B293" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C293" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D293">
-        <v>2.9</v>
+        <v>2.1659999999999999</v>
       </c>
       <c r="E293" t="s">
         <v>51</v>
@@ -12133,21 +12133,21 @@
         <v>506</v>
       </c>
       <c r="K293" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B294" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C294" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D294">
-        <v>1.248</v>
+        <v>2.4159999999999999</v>
       </c>
       <c r="E294" t="s">
         <v>51</v>
@@ -12159,21 +12159,21 @@
         <v>506</v>
       </c>
       <c r="K294" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B295" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C295" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D295">
-        <v>1.0309999999999999</v>
+        <v>2.863</v>
       </c>
       <c r="E295" t="s">
         <v>51</v>
@@ -12185,21 +12185,21 @@
         <v>506</v>
       </c>
       <c r="K295" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B296" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C296" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D296">
-        <v>2.1659999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="E296" t="s">
         <v>51</v>
@@ -12211,21 +12211,21 @@
         <v>506</v>
       </c>
       <c r="K296" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B297" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C297" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D297">
-        <v>2.4159999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="E297" t="s">
         <v>51</v>
@@ -12237,21 +12237,21 @@
         <v>506</v>
       </c>
       <c r="K297" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B298" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C298" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D298">
-        <v>2.863</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="E298" t="s">
         <v>51</v>
@@ -12263,21 +12263,21 @@
         <v>506</v>
       </c>
       <c r="K298" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B299" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C299" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D299">
-        <v>1.27</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="E299" t="s">
         <v>51</v>
@@ -12289,7 +12289,7 @@
         <v>506</v>
       </c>
       <c r="K299" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12303,19 +12303,19 @@
         <v>601</v>
       </c>
       <c r="D300">
-        <v>2.391</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="E300" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H300" t="s">
         <v>77</v>
       </c>
       <c r="J300" t="s">
-        <v>506</v>
+        <v>602</v>
       </c>
       <c r="K300" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12323,25 +12323,25 @@
         <v>599</v>
       </c>
       <c r="B301" t="s">
+        <v>603</v>
+      </c>
+      <c r="C301" t="s">
+        <v>604</v>
+      </c>
+      <c r="D301">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="E301" t="s">
+        <v>22</v>
+      </c>
+      <c r="H301" t="s">
+        <v>77</v>
+      </c>
+      <c r="J301" t="s">
         <v>602</v>
       </c>
-      <c r="C301" t="s">
-        <v>603</v>
-      </c>
-      <c r="D301">
-        <v>1.579</v>
-      </c>
-      <c r="E301" t="s">
-        <v>51</v>
-      </c>
-      <c r="H301" t="s">
-        <v>77</v>
-      </c>
-      <c r="J301" t="s">
-        <v>506</v>
-      </c>
       <c r="K301" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12349,207 +12349,77 @@
         <v>599</v>
       </c>
       <c r="B302" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C302" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D302">
-        <v>0.96</v>
+        <v>1.883</v>
       </c>
       <c r="E302" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H302" t="s">
         <v>77</v>
       </c>
       <c r="J302" t="s">
-        <v>506</v>
+        <v>602</v>
       </c>
       <c r="K302" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B303" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C303" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D303">
-        <v>1.8540000000000001</v>
+        <v>1.034</v>
       </c>
       <c r="E303" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H303" t="s">
         <v>77</v>
       </c>
       <c r="J303" t="s">
-        <v>506</v>
+        <v>602</v>
       </c>
       <c r="K303" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B304" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C304" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D304">
-        <v>0.95199999999999996</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="E304" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H304" t="s">
         <v>77</v>
       </c>
       <c r="J304" t="s">
-        <v>506</v>
+        <v>602</v>
       </c>
       <c r="K304" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>609</v>
-      </c>
-      <c r="B305" t="s">
-        <v>610</v>
-      </c>
-      <c r="C305" t="s">
-        <v>611</v>
-      </c>
-      <c r="D305">
-        <v>1.0029999999999999</v>
-      </c>
-      <c r="E305" t="s">
-        <v>22</v>
-      </c>
-      <c r="H305" t="s">
-        <v>77</v>
-      </c>
-      <c r="J305" t="s">
-        <v>612</v>
-      </c>
-      <c r="K305" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>609</v>
-      </c>
-      <c r="B306" t="s">
-        <v>613</v>
-      </c>
-      <c r="C306" t="s">
-        <v>614</v>
-      </c>
-      <c r="D306">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="E306" t="s">
-        <v>22</v>
-      </c>
-      <c r="H306" t="s">
-        <v>77</v>
-      </c>
-      <c r="J306" t="s">
-        <v>612</v>
-      </c>
-      <c r="K306" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>609</v>
-      </c>
-      <c r="B307" t="s">
-        <v>615</v>
-      </c>
-      <c r="C307" t="s">
-        <v>616</v>
-      </c>
-      <c r="D307">
-        <v>1.883</v>
-      </c>
-      <c r="E307" t="s">
-        <v>22</v>
-      </c>
-      <c r="H307" t="s">
-        <v>77</v>
-      </c>
-      <c r="J307" t="s">
-        <v>612</v>
-      </c>
-      <c r="K307" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>617</v>
-      </c>
-      <c r="B308" t="s">
-        <v>618</v>
-      </c>
-      <c r="C308" t="s">
-        <v>619</v>
-      </c>
-      <c r="D308">
-        <v>1.034</v>
-      </c>
-      <c r="E308" t="s">
-        <v>22</v>
-      </c>
-      <c r="H308" t="s">
-        <v>77</v>
-      </c>
-      <c r="J308" t="s">
-        <v>612</v>
-      </c>
-      <c r="K308" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>617</v>
-      </c>
-      <c r="B309" t="s">
-        <v>620</v>
-      </c>
-      <c r="C309" t="s">
-        <v>621</v>
-      </c>
-      <c r="D309">
-        <v>2.0350000000000001</v>
-      </c>
-      <c r="E309" t="s">
-        <v>22</v>
-      </c>
-      <c r="H309" t="s">
-        <v>77</v>
-      </c>
-      <c r="J309" t="s">
-        <v>612</v>
-      </c>
-      <c r="K309" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -5664,7 +5664,7 @@
         <v>103</v>
       </c>
       <c r="D99">
-        <v>1.48</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="E99" t="s">
         <v>22</v>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -1876,6 +1876,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6819,7 +6820,7 @@
         <v>276</v>
       </c>
       <c r="D132">
-        <v>3.0009999999999999</v>
+        <v>3.032</v>
       </c>
       <c r="E132" t="s">
         <v>14</v>
@@ -6854,7 +6855,7 @@
         <v>278</v>
       </c>
       <c r="D133">
-        <v>3.0019999999999998</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E133" t="s">
         <v>14</v>
@@ -6889,7 +6890,7 @@
         <v>280</v>
       </c>
       <c r="D134">
-        <v>3.0009999999999999</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="E134" t="s">
         <v>14</v>
@@ -6924,7 +6925,7 @@
         <v>282</v>
       </c>
       <c r="D135">
-        <v>3.004</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="E135" t="s">
         <v>14</v>
@@ -6959,7 +6960,7 @@
         <v>284</v>
       </c>
       <c r="D136">
-        <v>3.0009999999999999</v>
+        <v>3.044</v>
       </c>
       <c r="E136" t="s">
         <v>14</v>
@@ -6994,7 +6995,7 @@
         <v>286</v>
       </c>
       <c r="D137">
-        <v>3.0009999999999999</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E137" t="s">
         <v>14</v>
@@ -7029,7 +7030,7 @@
         <v>288</v>
       </c>
       <c r="D138">
-        <v>3.0030000000000001</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E138" t="s">
         <v>14</v>
@@ -7064,7 +7065,7 @@
         <v>103</v>
       </c>
       <c r="D139">
-        <v>2.1339999999999999</v>
+        <v>1.6679999999999999</v>
       </c>
       <c r="E139" t="s">
         <v>14</v>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -1803,21 +1803,12 @@
     <t>LF10000</t>
   </si>
   <si>
-    <t>LF1003</t>
-  </si>
-  <si>
     <t>Luka  Mndelemani</t>
   </si>
   <si>
-    <t>LF1005</t>
-  </si>
-  <si>
     <t>Joseph Banda</t>
   </si>
   <si>
-    <t>LF1012</t>
-  </si>
-  <si>
     <t>MP04000</t>
   </si>
   <si>
@@ -1858,6 +1849,15 @@
   </si>
   <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>LF10003</t>
+  </si>
+  <si>
+    <t>LF10005</t>
+  </si>
+  <si>
+    <t>LF10012</t>
   </si>
 </sst>
 </file>
@@ -2291,7 +2291,7 @@
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2326,7 +2326,7 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2361,7 +2361,7 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2396,7 +2396,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2431,7 +2431,7 @@
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2466,7 +2466,7 @@
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2501,7 +2501,7 @@
         <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2536,7 +2536,7 @@
         <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2571,7 +2571,7 @@
         <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2606,7 +2606,7 @@
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2641,7 +2641,7 @@
         <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2676,7 +2676,7 @@
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2711,7 +2711,7 @@
         <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2781,7 +2781,7 @@
         <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2816,7 +2816,7 @@
         <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2851,7 +2851,7 @@
         <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2886,7 +2886,7 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2921,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2956,7 +2956,7 @@
         <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2991,7 +2991,7 @@
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3026,7 +3026,7 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3061,7 +3061,7 @@
         <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3096,7 +3096,7 @@
         <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3131,7 +3131,7 @@
         <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3166,7 +3166,7 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3201,7 +3201,7 @@
         <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3271,7 +3271,7 @@
         <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3306,7 +3306,7 @@
         <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3341,7 +3341,7 @@
         <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3376,7 +3376,7 @@
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3446,7 +3446,7 @@
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3481,7 +3481,7 @@
         <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3516,7 +3516,7 @@
         <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3551,7 +3551,7 @@
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3586,7 +3586,7 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3621,7 +3621,7 @@
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3656,7 +3656,7 @@
         <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3691,7 +3691,7 @@
         <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3726,7 +3726,7 @@
         <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3761,7 +3761,7 @@
         <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3796,7 +3796,7 @@
         <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3831,7 +3831,7 @@
         <v>17</v>
       </c>
       <c r="K46" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3866,7 +3866,7 @@
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3901,7 +3901,7 @@
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3936,7 +3936,7 @@
         <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3971,7 +3971,7 @@
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4006,7 +4006,7 @@
         <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4041,7 +4041,7 @@
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4111,7 +4111,7 @@
         <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
         <v>17</v>
       </c>
       <c r="K55" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4181,7 +4181,7 @@
         <v>17</v>
       </c>
       <c r="K56" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4216,7 +4216,7 @@
         <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4251,7 +4251,7 @@
         <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4286,7 +4286,7 @@
         <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4321,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4356,7 +4356,7 @@
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4391,7 +4391,7 @@
         <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4426,7 +4426,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4496,7 +4496,7 @@
         <v>17</v>
       </c>
       <c r="K65" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4531,7 +4531,7 @@
         <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4566,7 +4566,7 @@
         <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4601,7 +4601,7 @@
         <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4636,7 +4636,7 @@
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4671,7 +4671,7 @@
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4706,7 +4706,7 @@
         <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4776,7 +4776,7 @@
         <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4811,7 +4811,7 @@
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4846,7 +4846,7 @@
         <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4881,7 +4881,7 @@
         <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4916,7 +4916,7 @@
         <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4951,7 +4951,7 @@
         <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4986,7 +4986,7 @@
         <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5021,7 +5021,7 @@
         <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5056,7 +5056,7 @@
         <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5091,7 +5091,7 @@
         <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5126,7 +5126,7 @@
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5161,7 +5161,7 @@
         <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5196,7 +5196,7 @@
         <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5231,7 +5231,7 @@
         <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -5266,7 +5266,7 @@
         <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5336,7 +5336,7 @@
         <v>17</v>
       </c>
       <c r="K89" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5371,7 +5371,7 @@
         <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5406,7 +5406,7 @@
         <v>17</v>
       </c>
       <c r="K91" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5441,7 +5441,7 @@
         <v>17</v>
       </c>
       <c r="K92" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5511,7 +5511,7 @@
         <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5546,7 +5546,7 @@
         <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5616,7 +5616,7 @@
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5651,7 +5651,7 @@
         <v>17</v>
       </c>
       <c r="K98" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5686,7 +5686,7 @@
         <v>17</v>
       </c>
       <c r="K99" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5721,7 +5721,7 @@
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5756,7 +5756,7 @@
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5791,7 +5791,7 @@
         <v>17</v>
       </c>
       <c r="K102" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5826,7 +5826,7 @@
         <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5861,7 +5861,7 @@
         <v>17</v>
       </c>
       <c r="K104" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5896,7 +5896,7 @@
         <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5931,7 +5931,7 @@
         <v>17</v>
       </c>
       <c r="K106" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>17</v>
       </c>
       <c r="K107" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6001,7 +6001,7 @@
         <v>17</v>
       </c>
       <c r="K108" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6036,7 +6036,7 @@
         <v>17</v>
       </c>
       <c r="K109" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6071,7 +6071,7 @@
         <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6106,7 +6106,7 @@
         <v>17</v>
       </c>
       <c r="K111" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6141,7 +6141,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6176,7 +6176,7 @@
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6211,7 +6211,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6246,7 +6246,7 @@
         <v>17</v>
       </c>
       <c r="K115" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6281,7 +6281,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6316,7 +6316,7 @@
         <v>17</v>
       </c>
       <c r="K117" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6351,7 +6351,7 @@
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6386,7 +6386,7 @@
         <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6421,7 +6421,7 @@
         <v>17</v>
       </c>
       <c r="K120" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6456,7 +6456,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6491,7 +6491,7 @@
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6526,7 +6526,7 @@
         <v>17</v>
       </c>
       <c r="K123" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6561,7 +6561,7 @@
         <v>17</v>
       </c>
       <c r="K124" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6596,7 +6596,7 @@
         <v>17</v>
       </c>
       <c r="K125" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6631,7 +6631,7 @@
         <v>17</v>
       </c>
       <c r="K126" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6666,7 +6666,7 @@
         <v>17</v>
       </c>
       <c r="K127" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6701,7 +6701,7 @@
         <v>17</v>
       </c>
       <c r="K128" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6736,7 +6736,7 @@
         <v>17</v>
       </c>
       <c r="K129" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6771,7 +6771,7 @@
         <v>17</v>
       </c>
       <c r="K130" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6806,7 +6806,7 @@
         <v>17</v>
       </c>
       <c r="K131" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6841,7 +6841,7 @@
         <v>17</v>
       </c>
       <c r="K132" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6876,7 +6876,7 @@
         <v>17</v>
       </c>
       <c r="K133" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6911,7 +6911,7 @@
         <v>17</v>
       </c>
       <c r="K134" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6946,7 +6946,7 @@
         <v>17</v>
       </c>
       <c r="K135" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6981,7 +6981,7 @@
         <v>17</v>
       </c>
       <c r="K136" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7016,7 +7016,7 @@
         <v>17</v>
       </c>
       <c r="K137" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7051,7 +7051,7 @@
         <v>17</v>
       </c>
       <c r="K138" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7086,7 +7086,7 @@
         <v>17</v>
       </c>
       <c r="K139" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -7121,7 +7121,7 @@
         <v>17</v>
       </c>
       <c r="K140" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>17</v>
       </c>
       <c r="K141" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7191,7 +7191,7 @@
         <v>17</v>
       </c>
       <c r="K142" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7226,7 +7226,7 @@
         <v>17</v>
       </c>
       <c r="K143" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>17</v>
       </c>
       <c r="K144" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7296,7 +7296,7 @@
         <v>17</v>
       </c>
       <c r="K145" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7331,7 +7331,7 @@
         <v>17</v>
       </c>
       <c r="K146" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7366,7 +7366,7 @@
         <v>17</v>
       </c>
       <c r="K147" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>17</v>
       </c>
       <c r="K148" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7436,7 +7436,7 @@
         <v>17</v>
       </c>
       <c r="K149" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7471,7 +7471,7 @@
         <v>17</v>
       </c>
       <c r="K150" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7506,7 +7506,7 @@
         <v>17</v>
       </c>
       <c r="K151" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7541,7 +7541,7 @@
         <v>17</v>
       </c>
       <c r="K152" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7576,7 +7576,7 @@
         <v>17</v>
       </c>
       <c r="K153" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7611,7 +7611,7 @@
         <v>17</v>
       </c>
       <c r="K154" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7646,7 +7646,7 @@
         <v>17</v>
       </c>
       <c r="K155" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7681,7 +7681,7 @@
         <v>17</v>
       </c>
       <c r="K156" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7716,7 +7716,7 @@
         <v>17</v>
       </c>
       <c r="K157" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7751,7 +7751,7 @@
         <v>17</v>
       </c>
       <c r="K158" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7786,7 +7786,7 @@
         <v>17</v>
       </c>
       <c r="K159" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7821,7 +7821,7 @@
         <v>17</v>
       </c>
       <c r="K160" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7856,7 +7856,7 @@
         <v>17</v>
       </c>
       <c r="K161" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
         <v>17</v>
       </c>
       <c r="K162" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -7926,7 +7926,7 @@
         <v>17</v>
       </c>
       <c r="K163" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7961,7 +7961,7 @@
         <v>17</v>
       </c>
       <c r="K164" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7996,7 +7996,7 @@
         <v>17</v>
       </c>
       <c r="K165" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -8031,7 +8031,7 @@
         <v>17</v>
       </c>
       <c r="K166" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8066,7 +8066,7 @@
         <v>17</v>
       </c>
       <c r="K167" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8101,7 +8101,7 @@
         <v>17</v>
       </c>
       <c r="K168" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8136,7 +8136,7 @@
         <v>17</v>
       </c>
       <c r="K169" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8171,7 +8171,7 @@
         <v>17</v>
       </c>
       <c r="K170" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>17</v>
       </c>
       <c r="K171" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -8241,7 +8241,7 @@
         <v>17</v>
       </c>
       <c r="K172" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8276,7 +8276,7 @@
         <v>17</v>
       </c>
       <c r="K173" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8311,7 +8311,7 @@
         <v>17</v>
       </c>
       <c r="K174" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8346,7 +8346,7 @@
         <v>17</v>
       </c>
       <c r="K175" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8381,7 +8381,7 @@
         <v>17</v>
       </c>
       <c r="K176" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8416,7 +8416,7 @@
         <v>17</v>
       </c>
       <c r="K177" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8451,7 +8451,7 @@
         <v>17</v>
       </c>
       <c r="K178" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8486,7 +8486,7 @@
         <v>17</v>
       </c>
       <c r="K179" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8521,7 +8521,7 @@
         <v>17</v>
       </c>
       <c r="K180" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8556,7 +8556,7 @@
         <v>17</v>
       </c>
       <c r="K181" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8591,7 +8591,7 @@
         <v>17</v>
       </c>
       <c r="K182" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8626,7 +8626,7 @@
         <v>17</v>
       </c>
       <c r="K183" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8661,7 +8661,7 @@
         <v>17</v>
       </c>
       <c r="K184" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8696,7 +8696,7 @@
         <v>17</v>
       </c>
       <c r="K185" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8731,7 +8731,7 @@
         <v>17</v>
       </c>
       <c r="K186" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8766,7 +8766,7 @@
         <v>17</v>
       </c>
       <c r="K187" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8801,7 +8801,7 @@
         <v>17</v>
       </c>
       <c r="K188" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8836,7 +8836,7 @@
         <v>17</v>
       </c>
       <c r="K189" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8871,7 +8871,7 @@
         <v>17</v>
       </c>
       <c r="K190" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8906,7 +8906,7 @@
         <v>17</v>
       </c>
       <c r="K191" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8941,7 +8941,7 @@
         <v>17</v>
       </c>
       <c r="K192" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8976,7 +8976,7 @@
         <v>17</v>
       </c>
       <c r="K193" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -9011,7 +9011,7 @@
         <v>17</v>
       </c>
       <c r="K194" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -9046,7 +9046,7 @@
         <v>17</v>
       </c>
       <c r="K195" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9081,7 +9081,7 @@
         <v>17</v>
       </c>
       <c r="K196" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9116,7 +9116,7 @@
         <v>17</v>
       </c>
       <c r="K197" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9151,7 +9151,7 @@
         <v>17</v>
       </c>
       <c r="K198" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9186,7 +9186,7 @@
         <v>17</v>
       </c>
       <c r="K199" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9221,7 +9221,7 @@
         <v>17</v>
       </c>
       <c r="K200" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9256,7 +9256,7 @@
         <v>17</v>
       </c>
       <c r="K201" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9291,7 +9291,7 @@
         <v>17</v>
       </c>
       <c r="K202" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9326,7 +9326,7 @@
         <v>17</v>
       </c>
       <c r="K203" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9361,7 +9361,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9396,7 +9396,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9431,7 +9431,7 @@
         <v>17</v>
       </c>
       <c r="K206" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9466,7 +9466,7 @@
         <v>17</v>
       </c>
       <c r="K207" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9501,7 +9501,7 @@
         <v>17</v>
       </c>
       <c r="K208" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9536,7 +9536,7 @@
         <v>17</v>
       </c>
       <c r="K209" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9571,7 +9571,7 @@
         <v>17</v>
       </c>
       <c r="K210" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9606,7 +9606,7 @@
         <v>17</v>
       </c>
       <c r="K211" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
         <v>17</v>
       </c>
       <c r="K212" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9676,7 +9676,7 @@
         <v>17</v>
       </c>
       <c r="K213" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9711,7 +9711,7 @@
         <v>17</v>
       </c>
       <c r="K214" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9746,7 +9746,7 @@
         <v>17</v>
       </c>
       <c r="K215" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9781,7 +9781,7 @@
         <v>17</v>
       </c>
       <c r="K216" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9816,7 +9816,7 @@
         <v>17</v>
       </c>
       <c r="K217" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9851,7 +9851,7 @@
         <v>17</v>
       </c>
       <c r="K218" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9886,7 +9886,7 @@
         <v>17</v>
       </c>
       <c r="K219" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9921,7 +9921,7 @@
         <v>17</v>
       </c>
       <c r="K220" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9956,7 +9956,7 @@
         <v>17</v>
       </c>
       <c r="K221" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -9991,7 +9991,7 @@
         <v>17</v>
       </c>
       <c r="K222" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -10026,7 +10026,7 @@
         <v>17</v>
       </c>
       <c r="K223" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -10061,7 +10061,7 @@
         <v>17</v>
       </c>
       <c r="K224" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -10096,7 +10096,7 @@
         <v>17</v>
       </c>
       <c r="K225" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -10131,7 +10131,7 @@
         <v>17</v>
       </c>
       <c r="K226" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -10166,7 +10166,7 @@
         <v>17</v>
       </c>
       <c r="K227" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10201,7 +10201,7 @@
         <v>17</v>
       </c>
       <c r="K228" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10236,7 +10236,7 @@
         <v>17</v>
       </c>
       <c r="K229" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -10271,7 +10271,7 @@
         <v>17</v>
       </c>
       <c r="K230" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -10306,7 +10306,7 @@
         <v>17</v>
       </c>
       <c r="K231" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
         <v>17</v>
       </c>
       <c r="K232" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -10376,7 +10376,7 @@
         <v>17</v>
       </c>
       <c r="K233" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10411,7 +10411,7 @@
         <v>17</v>
       </c>
       <c r="K234" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -10446,7 +10446,7 @@
         <v>17</v>
       </c>
       <c r="K235" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -10481,7 +10481,7 @@
         <v>17</v>
       </c>
       <c r="K236" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -10516,7 +10516,7 @@
         <v>17</v>
       </c>
       <c r="K237" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10551,7 +10551,7 @@
         <v>17</v>
       </c>
       <c r="K238" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -10586,7 +10586,7 @@
         <v>17</v>
       </c>
       <c r="K239" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -10621,7 +10621,7 @@
         <v>17</v>
       </c>
       <c r="K240" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -10656,7 +10656,7 @@
         <v>17</v>
       </c>
       <c r="K241" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10691,7 +10691,7 @@
         <v>17</v>
       </c>
       <c r="K242" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10726,7 +10726,7 @@
         <v>17</v>
       </c>
       <c r="K243" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10761,7 +10761,7 @@
         <v>17</v>
       </c>
       <c r="K244" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10796,7 +10796,7 @@
         <v>17</v>
       </c>
       <c r="K245" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10831,7 +10831,7 @@
         <v>17</v>
       </c>
       <c r="K246" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10866,7 +10866,7 @@
         <v>17</v>
       </c>
       <c r="K247" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10901,7 +10901,7 @@
         <v>17</v>
       </c>
       <c r="K248" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10936,7 +10936,7 @@
         <v>17</v>
       </c>
       <c r="K249" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10971,7 +10971,7 @@
         <v>17</v>
       </c>
       <c r="K250" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -11006,7 +11006,7 @@
         <v>17</v>
       </c>
       <c r="K251" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -11041,7 +11041,7 @@
         <v>17</v>
       </c>
       <c r="K252" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -11076,7 +11076,7 @@
         <v>17</v>
       </c>
       <c r="K253" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -11111,7 +11111,7 @@
         <v>17</v>
       </c>
       <c r="K254" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -11146,7 +11146,7 @@
         <v>17</v>
       </c>
       <c r="K255" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11172,7 +11172,7 @@
         <v>506</v>
       </c>
       <c r="K256" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11198,7 +11198,7 @@
         <v>506</v>
       </c>
       <c r="K257" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11224,7 +11224,7 @@
         <v>506</v>
       </c>
       <c r="K258" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11250,7 +11250,7 @@
         <v>506</v>
       </c>
       <c r="K259" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11276,7 +11276,7 @@
         <v>506</v>
       </c>
       <c r="K260" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11302,7 +11302,7 @@
         <v>506</v>
       </c>
       <c r="K261" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -11328,7 +11328,7 @@
         <v>506</v>
       </c>
       <c r="K262" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -11354,7 +11354,7 @@
         <v>506</v>
       </c>
       <c r="K263" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -11380,7 +11380,7 @@
         <v>506</v>
       </c>
       <c r="K264" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -11406,7 +11406,7 @@
         <v>506</v>
       </c>
       <c r="K265" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -11432,7 +11432,7 @@
         <v>506</v>
       </c>
       <c r="K266" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -11458,7 +11458,7 @@
         <v>506</v>
       </c>
       <c r="K267" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -11484,7 +11484,7 @@
         <v>506</v>
       </c>
       <c r="K268" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -11510,7 +11510,7 @@
         <v>506</v>
       </c>
       <c r="K269" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -11536,7 +11536,7 @@
         <v>506</v>
       </c>
       <c r="K270" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -11562,7 +11562,7 @@
         <v>506</v>
       </c>
       <c r="K271" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -11588,7 +11588,7 @@
         <v>506</v>
       </c>
       <c r="K272" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
@@ -11614,7 +11614,7 @@
         <v>506</v>
       </c>
       <c r="K273" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -11640,7 +11640,7 @@
         <v>506</v>
       </c>
       <c r="K274" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
@@ -11666,7 +11666,7 @@
         <v>506</v>
       </c>
       <c r="K275" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11692,7 +11692,7 @@
         <v>506</v>
       </c>
       <c r="K276" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11718,7 +11718,7 @@
         <v>506</v>
       </c>
       <c r="K277" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11744,7 +11744,7 @@
         <v>506</v>
       </c>
       <c r="K278" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11770,7 +11770,7 @@
         <v>506</v>
       </c>
       <c r="K279" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11796,7 +11796,7 @@
         <v>506</v>
       </c>
       <c r="K280" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11822,7 +11822,7 @@
         <v>506</v>
       </c>
       <c r="K281" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11848,7 +11848,7 @@
         <v>506</v>
       </c>
       <c r="K282" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11874,7 +11874,7 @@
         <v>506</v>
       </c>
       <c r="K283" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11900,7 +11900,7 @@
         <v>506</v>
       </c>
       <c r="K284" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11926,7 +11926,7 @@
         <v>506</v>
       </c>
       <c r="K285" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -11952,7 +11952,7 @@
         <v>506</v>
       </c>
       <c r="K286" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -11978,7 +11978,7 @@
         <v>506</v>
       </c>
       <c r="K287" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12004,7 +12004,7 @@
         <v>506</v>
       </c>
       <c r="K288" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12030,7 +12030,7 @@
         <v>506</v>
       </c>
       <c r="K289" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12056,7 +12056,7 @@
         <v>506</v>
       </c>
       <c r="K290" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12082,7 +12082,7 @@
         <v>506</v>
       </c>
       <c r="K291" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12108,7 +12108,7 @@
         <v>506</v>
       </c>
       <c r="K292" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12134,7 +12134,7 @@
         <v>506</v>
       </c>
       <c r="K293" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12160,7 +12160,7 @@
         <v>506</v>
       </c>
       <c r="K294" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12186,7 +12186,7 @@
         <v>506</v>
       </c>
       <c r="K295" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12212,7 +12212,7 @@
         <v>506</v>
       </c>
       <c r="K296" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12220,10 +12220,10 @@
         <v>593</v>
       </c>
       <c r="B297" t="s">
+        <v>610</v>
+      </c>
+      <c r="C297" t="s">
         <v>594</v>
-      </c>
-      <c r="C297" t="s">
-        <v>595</v>
       </c>
       <c r="D297">
         <v>0.96</v>
@@ -12238,7 +12238,7 @@
         <v>506</v>
       </c>
       <c r="K297" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12246,10 +12246,10 @@
         <v>593</v>
       </c>
       <c r="B298" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="C298" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D298">
         <v>1.8540000000000001</v>
@@ -12264,7 +12264,7 @@
         <v>506</v>
       </c>
       <c r="K298" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12272,10 +12272,10 @@
         <v>593</v>
       </c>
       <c r="B299" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="C299" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D299">
         <v>0.95199999999999996</v>
@@ -12290,18 +12290,18 @@
         <v>506</v>
       </c>
       <c r="K299" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B300" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C300" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D300">
         <v>1.0029999999999999</v>
@@ -12313,21 +12313,21 @@
         <v>77</v>
       </c>
       <c r="J300" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K300" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B301" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C301" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D301">
         <v>1.0389999999999999</v>
@@ -12339,21 +12339,21 @@
         <v>77</v>
       </c>
       <c r="J301" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K301" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B302" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C302" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D302">
         <v>1.883</v>
@@ -12365,21 +12365,21 @@
         <v>77</v>
       </c>
       <c r="J302" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K302" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B303" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C303" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D303">
         <v>1.034</v>
@@ -12391,21 +12391,21 @@
         <v>77</v>
       </c>
       <c r="J303" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K303" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>604</v>
+      </c>
+      <c r="B304" t="s">
         <v>607</v>
       </c>
-      <c r="B304" t="s">
-        <v>610</v>
-      </c>
       <c r="C304" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D304">
         <v>2.0350000000000001</v>
@@ -12417,10 +12417,10 @@
         <v>77</v>
       </c>
       <c r="J304" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K304" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4450" uniqueCount="614">
   <si>
     <t>Main Field</t>
   </si>
@@ -1855,6 +1855,12 @@
   </si>
   <si>
     <t>LF10012</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>DG04001</t>
   </si>
 </sst>
 </file>
@@ -2218,7 +2224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K303"/>
+  <dimension ref="A1:K606"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -12385,6 +12391,9261 @@
         <v>608</v>
       </c>
     </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>11</v>
+      </c>
+      <c r="B304" t="s">
+        <v>12</v>
+      </c>
+      <c r="C304" t="s">
+        <v>13</v>
+      </c>
+      <c r="D304">
+        <v>3.008</v>
+      </c>
+      <c r="E304" t="s">
+        <v>14</v>
+      </c>
+      <c r="F304">
+        <v>6</v>
+      </c>
+      <c r="G304">
+        <v>100</v>
+      </c>
+      <c r="I304" t="s">
+        <v>16</v>
+      </c>
+      <c r="J304" t="s">
+        <v>17</v>
+      </c>
+      <c r="K304" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>11</v>
+      </c>
+      <c r="B305" t="s">
+        <v>18</v>
+      </c>
+      <c r="C305" t="s">
+        <v>19</v>
+      </c>
+      <c r="D305">
+        <v>3.0870000000000002</v>
+      </c>
+      <c r="E305" t="s">
+        <v>14</v>
+      </c>
+      <c r="F305">
+        <v>6</v>
+      </c>
+      <c r="G305">
+        <v>100</v>
+      </c>
+      <c r="I305" t="s">
+        <v>16</v>
+      </c>
+      <c r="J305" t="s">
+        <v>17</v>
+      </c>
+      <c r="K305" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>11</v>
+      </c>
+      <c r="B306" t="s">
+        <v>20</v>
+      </c>
+      <c r="C306" t="s">
+        <v>21</v>
+      </c>
+      <c r="D306">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E306" t="s">
+        <v>22</v>
+      </c>
+      <c r="F306">
+        <v>6</v>
+      </c>
+      <c r="G306">
+        <v>100</v>
+      </c>
+      <c r="I306" t="s">
+        <v>16</v>
+      </c>
+      <c r="J306" t="s">
+        <v>17</v>
+      </c>
+      <c r="K306" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>11</v>
+      </c>
+      <c r="B307" t="s">
+        <v>23</v>
+      </c>
+      <c r="C307" t="s">
+        <v>24</v>
+      </c>
+      <c r="D307">
+        <v>3.0219999999999998</v>
+      </c>
+      <c r="E307" t="s">
+        <v>22</v>
+      </c>
+      <c r="F307">
+        <v>6</v>
+      </c>
+      <c r="G307">
+        <v>100</v>
+      </c>
+      <c r="I307" t="s">
+        <v>25</v>
+      </c>
+      <c r="J307" t="s">
+        <v>17</v>
+      </c>
+      <c r="K307" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>11</v>
+      </c>
+      <c r="B308" t="s">
+        <v>26</v>
+      </c>
+      <c r="C308" t="s">
+        <v>27</v>
+      </c>
+      <c r="D308">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E308" t="s">
+        <v>22</v>
+      </c>
+      <c r="F308">
+        <v>6</v>
+      </c>
+      <c r="G308">
+        <v>100</v>
+      </c>
+      <c r="I308" t="s">
+        <v>25</v>
+      </c>
+      <c r="J308" t="s">
+        <v>17</v>
+      </c>
+      <c r="K308" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>11</v>
+      </c>
+      <c r="B309" t="s">
+        <v>28</v>
+      </c>
+      <c r="C309" t="s">
+        <v>29</v>
+      </c>
+      <c r="D309">
+        <v>3.04</v>
+      </c>
+      <c r="E309" t="s">
+        <v>22</v>
+      </c>
+      <c r="F309">
+        <v>6</v>
+      </c>
+      <c r="G309">
+        <v>100</v>
+      </c>
+      <c r="I309" t="s">
+        <v>16</v>
+      </c>
+      <c r="J309" t="s">
+        <v>17</v>
+      </c>
+      <c r="K309" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>11</v>
+      </c>
+      <c r="B310" t="s">
+        <v>30</v>
+      </c>
+      <c r="C310" t="s">
+        <v>31</v>
+      </c>
+      <c r="D310">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="E310" t="s">
+        <v>22</v>
+      </c>
+      <c r="F310">
+        <v>6</v>
+      </c>
+      <c r="G310">
+        <v>100</v>
+      </c>
+      <c r="I310" t="s">
+        <v>16</v>
+      </c>
+      <c r="J310" t="s">
+        <v>17</v>
+      </c>
+      <c r="K310" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>32</v>
+      </c>
+      <c r="B311" t="s">
+        <v>33</v>
+      </c>
+      <c r="C311" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E311" t="s">
+        <v>14</v>
+      </c>
+      <c r="F311">
+        <v>5</v>
+      </c>
+      <c r="G311">
+        <v>100</v>
+      </c>
+      <c r="I311" t="s">
+        <v>16</v>
+      </c>
+      <c r="J311" t="s">
+        <v>17</v>
+      </c>
+      <c r="K311" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>32</v>
+      </c>
+      <c r="B312" t="s">
+        <v>36</v>
+      </c>
+      <c r="C312" t="s">
+        <v>37</v>
+      </c>
+      <c r="D312">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="E312" t="s">
+        <v>14</v>
+      </c>
+      <c r="F312">
+        <v>5</v>
+      </c>
+      <c r="G312">
+        <v>100</v>
+      </c>
+      <c r="I312" t="s">
+        <v>16</v>
+      </c>
+      <c r="J312" t="s">
+        <v>17</v>
+      </c>
+      <c r="K312" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>32</v>
+      </c>
+      <c r="B313" t="s">
+        <v>38</v>
+      </c>
+      <c r="C313" t="s">
+        <v>39</v>
+      </c>
+      <c r="D313">
+        <v>3.05</v>
+      </c>
+      <c r="E313" t="s">
+        <v>14</v>
+      </c>
+      <c r="F313">
+        <v>5</v>
+      </c>
+      <c r="G313">
+        <v>100</v>
+      </c>
+      <c r="I313" t="s">
+        <v>16</v>
+      </c>
+      <c r="J313" t="s">
+        <v>17</v>
+      </c>
+      <c r="K313" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>40</v>
+      </c>
+      <c r="B314" t="s">
+        <v>41</v>
+      </c>
+      <c r="C314" t="s">
+        <v>42</v>
+      </c>
+      <c r="D314">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E314" t="s">
+        <v>22</v>
+      </c>
+      <c r="F314">
+        <v>3</v>
+      </c>
+      <c r="G314">
+        <v>100</v>
+      </c>
+      <c r="I314" t="s">
+        <v>16</v>
+      </c>
+      <c r="J314" t="s">
+        <v>17</v>
+      </c>
+      <c r="K314" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>40</v>
+      </c>
+      <c r="B315" t="s">
+        <v>44</v>
+      </c>
+      <c r="C315" t="s">
+        <v>45</v>
+      </c>
+      <c r="D315">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="E315" t="s">
+        <v>22</v>
+      </c>
+      <c r="F315">
+        <v>3</v>
+      </c>
+      <c r="G315">
+        <v>100</v>
+      </c>
+      <c r="I315" t="s">
+        <v>16</v>
+      </c>
+      <c r="J315" t="s">
+        <v>17</v>
+      </c>
+      <c r="K315" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>40</v>
+      </c>
+      <c r="B316" t="s">
+        <v>46</v>
+      </c>
+      <c r="C316" t="s">
+        <v>47</v>
+      </c>
+      <c r="D316">
+        <v>3.02</v>
+      </c>
+      <c r="E316" t="s">
+        <v>22</v>
+      </c>
+      <c r="F316">
+        <v>3</v>
+      </c>
+      <c r="G316">
+        <v>100</v>
+      </c>
+      <c r="I316" t="s">
+        <v>16</v>
+      </c>
+      <c r="J316" t="s">
+        <v>17</v>
+      </c>
+      <c r="K316" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>40</v>
+      </c>
+      <c r="B317" t="s">
+        <v>48</v>
+      </c>
+      <c r="C317" t="s">
+        <v>31</v>
+      </c>
+      <c r="D317">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E317" t="s">
+        <v>22</v>
+      </c>
+      <c r="F317">
+        <v>3</v>
+      </c>
+      <c r="G317">
+        <v>100</v>
+      </c>
+      <c r="I317" t="s">
+        <v>16</v>
+      </c>
+      <c r="J317" t="s">
+        <v>17</v>
+      </c>
+      <c r="K317" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>49</v>
+      </c>
+      <c r="B318" t="s">
+        <v>613</v>
+      </c>
+      <c r="C318" t="s">
+        <v>31</v>
+      </c>
+      <c r="D318">
+        <v>3.0960000000000001</v>
+      </c>
+      <c r="E318" t="s">
+        <v>50</v>
+      </c>
+      <c r="F318">
+        <v>7</v>
+      </c>
+      <c r="G318">
+        <v>100</v>
+      </c>
+      <c r="I318" t="s">
+        <v>52</v>
+      </c>
+      <c r="J318" t="s">
+        <v>17</v>
+      </c>
+      <c r="K318" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>49</v>
+      </c>
+      <c r="B319" t="s">
+        <v>53</v>
+      </c>
+      <c r="C319" t="s">
+        <v>31</v>
+      </c>
+      <c r="D319">
+        <v>3.105</v>
+      </c>
+      <c r="E319" t="s">
+        <v>50</v>
+      </c>
+      <c r="F319">
+        <v>7</v>
+      </c>
+      <c r="G319">
+        <v>100</v>
+      </c>
+      <c r="I319" t="s">
+        <v>52</v>
+      </c>
+      <c r="J319" t="s">
+        <v>17</v>
+      </c>
+      <c r="K319" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>49</v>
+      </c>
+      <c r="B320" t="s">
+        <v>54</v>
+      </c>
+      <c r="C320" t="s">
+        <v>31</v>
+      </c>
+      <c r="D320">
+        <v>3.1</v>
+      </c>
+      <c r="E320" t="s">
+        <v>50</v>
+      </c>
+      <c r="F320">
+        <v>7</v>
+      </c>
+      <c r="G320">
+        <v>100</v>
+      </c>
+      <c r="I320" t="s">
+        <v>52</v>
+      </c>
+      <c r="J320" t="s">
+        <v>17</v>
+      </c>
+      <c r="K320" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>49</v>
+      </c>
+      <c r="B321" t="s">
+        <v>56</v>
+      </c>
+      <c r="C321" t="s">
+        <v>31</v>
+      </c>
+      <c r="D321">
+        <v>3.093</v>
+      </c>
+      <c r="E321" t="s">
+        <v>50</v>
+      </c>
+      <c r="F321">
+        <v>7</v>
+      </c>
+      <c r="G321">
+        <v>100</v>
+      </c>
+      <c r="I321" t="s">
+        <v>52</v>
+      </c>
+      <c r="J321" t="s">
+        <v>17</v>
+      </c>
+      <c r="K321" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>49</v>
+      </c>
+      <c r="B322" t="s">
+        <v>57</v>
+      </c>
+      <c r="C322" t="s">
+        <v>31</v>
+      </c>
+      <c r="D322">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E322" t="s">
+        <v>50</v>
+      </c>
+      <c r="F322">
+        <v>7</v>
+      </c>
+      <c r="G322">
+        <v>100</v>
+      </c>
+      <c r="I322" t="s">
+        <v>52</v>
+      </c>
+      <c r="J322" t="s">
+        <v>17</v>
+      </c>
+      <c r="K322" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>49</v>
+      </c>
+      <c r="B323" t="s">
+        <v>58</v>
+      </c>
+      <c r="C323" t="s">
+        <v>31</v>
+      </c>
+      <c r="D323">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="E323" t="s">
+        <v>50</v>
+      </c>
+      <c r="F323">
+        <v>7</v>
+      </c>
+      <c r="G323">
+        <v>100</v>
+      </c>
+      <c r="I323" t="s">
+        <v>52</v>
+      </c>
+      <c r="J323" t="s">
+        <v>17</v>
+      </c>
+      <c r="K323" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>59</v>
+      </c>
+      <c r="B324" t="s">
+        <v>60</v>
+      </c>
+      <c r="C324" t="s">
+        <v>61</v>
+      </c>
+      <c r="D324">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E324" t="s">
+        <v>14</v>
+      </c>
+      <c r="F324">
+        <v>5</v>
+      </c>
+      <c r="G324">
+        <v>100</v>
+      </c>
+      <c r="I324" t="s">
+        <v>16</v>
+      </c>
+      <c r="J324" t="s">
+        <v>17</v>
+      </c>
+      <c r="K324" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>59</v>
+      </c>
+      <c r="B325" t="s">
+        <v>63</v>
+      </c>
+      <c r="C325" t="s">
+        <v>64</v>
+      </c>
+      <c r="D325">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E325" t="s">
+        <v>14</v>
+      </c>
+      <c r="F325">
+        <v>5</v>
+      </c>
+      <c r="G325">
+        <v>100</v>
+      </c>
+      <c r="I325" t="s">
+        <v>65</v>
+      </c>
+      <c r="J325" t="s">
+        <v>17</v>
+      </c>
+      <c r="K325" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>59</v>
+      </c>
+      <c r="B326" t="s">
+        <v>66</v>
+      </c>
+      <c r="C326" t="s">
+        <v>67</v>
+      </c>
+      <c r="D326">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E326" t="s">
+        <v>14</v>
+      </c>
+      <c r="F326">
+        <v>5</v>
+      </c>
+      <c r="G326">
+        <v>100</v>
+      </c>
+      <c r="I326" t="s">
+        <v>16</v>
+      </c>
+      <c r="J326" t="s">
+        <v>17</v>
+      </c>
+      <c r="K326" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>59</v>
+      </c>
+      <c r="B327" t="s">
+        <v>68</v>
+      </c>
+      <c r="C327" t="s">
+        <v>69</v>
+      </c>
+      <c r="D327">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E327" t="s">
+        <v>14</v>
+      </c>
+      <c r="F327">
+        <v>5</v>
+      </c>
+      <c r="G327">
+        <v>100</v>
+      </c>
+      <c r="I327" t="s">
+        <v>16</v>
+      </c>
+      <c r="J327" t="s">
+        <v>17</v>
+      </c>
+      <c r="K327" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>59</v>
+      </c>
+      <c r="B328" t="s">
+        <v>70</v>
+      </c>
+      <c r="C328" t="s">
+        <v>71</v>
+      </c>
+      <c r="D328">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E328" t="s">
+        <v>14</v>
+      </c>
+      <c r="F328">
+        <v>5</v>
+      </c>
+      <c r="G328">
+        <v>100</v>
+      </c>
+      <c r="I328" t="s">
+        <v>16</v>
+      </c>
+      <c r="J328" t="s">
+        <v>17</v>
+      </c>
+      <c r="K328" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>59</v>
+      </c>
+      <c r="B329" t="s">
+        <v>72</v>
+      </c>
+      <c r="C329" t="s">
+        <v>31</v>
+      </c>
+      <c r="D329">
+        <v>2.2269999999999999</v>
+      </c>
+      <c r="E329" t="s">
+        <v>14</v>
+      </c>
+      <c r="F329">
+        <v>5</v>
+      </c>
+      <c r="G329">
+        <v>100</v>
+      </c>
+      <c r="I329" t="s">
+        <v>16</v>
+      </c>
+      <c r="J329" t="s">
+        <v>17</v>
+      </c>
+      <c r="K329" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>73</v>
+      </c>
+      <c r="B330" t="s">
+        <v>74</v>
+      </c>
+      <c r="C330" t="s">
+        <v>75</v>
+      </c>
+      <c r="D330">
+        <v>3.036</v>
+      </c>
+      <c r="E330" t="s">
+        <v>22</v>
+      </c>
+      <c r="F330">
+        <v>1</v>
+      </c>
+      <c r="G330">
+        <v>100</v>
+      </c>
+      <c r="I330" t="s">
+        <v>16</v>
+      </c>
+      <c r="J330" t="s">
+        <v>17</v>
+      </c>
+      <c r="K330" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>73</v>
+      </c>
+      <c r="B331" t="s">
+        <v>77</v>
+      </c>
+      <c r="C331" t="s">
+        <v>78</v>
+      </c>
+      <c r="D331">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E331" t="s">
+        <v>22</v>
+      </c>
+      <c r="F331">
+        <v>1</v>
+      </c>
+      <c r="G331">
+        <v>100</v>
+      </c>
+      <c r="I331" t="s">
+        <v>16</v>
+      </c>
+      <c r="J331" t="s">
+        <v>17</v>
+      </c>
+      <c r="K331" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>73</v>
+      </c>
+      <c r="B332" t="s">
+        <v>79</v>
+      </c>
+      <c r="C332" t="s">
+        <v>80</v>
+      </c>
+      <c r="D332">
+        <v>3.0430000000000001</v>
+      </c>
+      <c r="E332" t="s">
+        <v>22</v>
+      </c>
+      <c r="F332">
+        <v>1</v>
+      </c>
+      <c r="G332">
+        <v>100</v>
+      </c>
+      <c r="I332" t="s">
+        <v>16</v>
+      </c>
+      <c r="J332" t="s">
+        <v>17</v>
+      </c>
+      <c r="K332" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>73</v>
+      </c>
+      <c r="B333" t="s">
+        <v>81</v>
+      </c>
+      <c r="C333" t="s">
+        <v>82</v>
+      </c>
+      <c r="D333">
+        <v>3.052</v>
+      </c>
+      <c r="E333" t="s">
+        <v>22</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+      <c r="G333">
+        <v>100</v>
+      </c>
+      <c r="I333" t="s">
+        <v>16</v>
+      </c>
+      <c r="J333" t="s">
+        <v>17</v>
+      </c>
+      <c r="K333" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>73</v>
+      </c>
+      <c r="B334" t="s">
+        <v>83</v>
+      </c>
+      <c r="C334" t="s">
+        <v>84</v>
+      </c>
+      <c r="D334">
+        <v>3.044</v>
+      </c>
+      <c r="E334" t="s">
+        <v>22</v>
+      </c>
+      <c r="F334">
+        <v>1</v>
+      </c>
+      <c r="G334">
+        <v>100</v>
+      </c>
+      <c r="I334" t="s">
+        <v>16</v>
+      </c>
+      <c r="J334" t="s">
+        <v>17</v>
+      </c>
+      <c r="K334" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>73</v>
+      </c>
+      <c r="B335" t="s">
+        <v>85</v>
+      </c>
+      <c r="C335" t="s">
+        <v>86</v>
+      </c>
+      <c r="D335">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="E335" t="s">
+        <v>22</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+      <c r="G335">
+        <v>100</v>
+      </c>
+      <c r="I335" t="s">
+        <v>16</v>
+      </c>
+      <c r="J335" t="s">
+        <v>17</v>
+      </c>
+      <c r="K335" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>87</v>
+      </c>
+      <c r="B336" t="s">
+        <v>88</v>
+      </c>
+      <c r="C336" t="s">
+        <v>89</v>
+      </c>
+      <c r="D336">
+        <v>3.024</v>
+      </c>
+      <c r="E336" t="s">
+        <v>90</v>
+      </c>
+      <c r="F336">
+        <v>1</v>
+      </c>
+      <c r="G336">
+        <v>100</v>
+      </c>
+      <c r="I336" t="s">
+        <v>16</v>
+      </c>
+      <c r="J336" t="s">
+        <v>17</v>
+      </c>
+      <c r="K336" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>87</v>
+      </c>
+      <c r="B337" t="s">
+        <v>91</v>
+      </c>
+      <c r="C337" t="s">
+        <v>92</v>
+      </c>
+      <c r="D337">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E337" t="s">
+        <v>90</v>
+      </c>
+      <c r="F337">
+        <v>1</v>
+      </c>
+      <c r="G337">
+        <v>100</v>
+      </c>
+      <c r="I337" t="s">
+        <v>16</v>
+      </c>
+      <c r="J337" t="s">
+        <v>17</v>
+      </c>
+      <c r="K337" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>87</v>
+      </c>
+      <c r="B338" t="s">
+        <v>93</v>
+      </c>
+      <c r="C338" t="s">
+        <v>94</v>
+      </c>
+      <c r="D338">
+        <v>3.008</v>
+      </c>
+      <c r="E338" t="s">
+        <v>90</v>
+      </c>
+      <c r="F338">
+        <v>1</v>
+      </c>
+      <c r="G338">
+        <v>100</v>
+      </c>
+      <c r="I338" t="s">
+        <v>16</v>
+      </c>
+      <c r="J338" t="s">
+        <v>17</v>
+      </c>
+      <c r="K338" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>87</v>
+      </c>
+      <c r="B339" t="s">
+        <v>95</v>
+      </c>
+      <c r="C339" t="s">
+        <v>96</v>
+      </c>
+      <c r="D339">
+        <v>3.0329999999999999</v>
+      </c>
+      <c r="E339" t="s">
+        <v>90</v>
+      </c>
+      <c r="F339">
+        <v>1</v>
+      </c>
+      <c r="G339">
+        <v>100</v>
+      </c>
+      <c r="I339" t="s">
+        <v>16</v>
+      </c>
+      <c r="J339" t="s">
+        <v>17</v>
+      </c>
+      <c r="K339" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>87</v>
+      </c>
+      <c r="B340" t="s">
+        <v>97</v>
+      </c>
+      <c r="C340" t="s">
+        <v>98</v>
+      </c>
+      <c r="D340">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E340" t="s">
+        <v>90</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+      <c r="G340">
+        <v>100</v>
+      </c>
+      <c r="I340" t="s">
+        <v>16</v>
+      </c>
+      <c r="J340" t="s">
+        <v>17</v>
+      </c>
+      <c r="K340" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>87</v>
+      </c>
+      <c r="B341" t="s">
+        <v>99</v>
+      </c>
+      <c r="C341" t="s">
+        <v>100</v>
+      </c>
+      <c r="D341">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E341" t="s">
+        <v>90</v>
+      </c>
+      <c r="F341">
+        <v>1</v>
+      </c>
+      <c r="G341">
+        <v>100</v>
+      </c>
+      <c r="I341" t="s">
+        <v>16</v>
+      </c>
+      <c r="J341" t="s">
+        <v>17</v>
+      </c>
+      <c r="K341" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>87</v>
+      </c>
+      <c r="B342" t="s">
+        <v>101</v>
+      </c>
+      <c r="C342" t="s">
+        <v>102</v>
+      </c>
+      <c r="D342">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="E342" t="s">
+        <v>90</v>
+      </c>
+      <c r="F342">
+        <v>1</v>
+      </c>
+      <c r="G342">
+        <v>100</v>
+      </c>
+      <c r="I342" t="s">
+        <v>16</v>
+      </c>
+      <c r="J342" t="s">
+        <v>17</v>
+      </c>
+      <c r="K342" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>103</v>
+      </c>
+      <c r="B343" t="s">
+        <v>104</v>
+      </c>
+      <c r="C343" t="s">
+        <v>105</v>
+      </c>
+      <c r="D343">
+        <v>3.081</v>
+      </c>
+      <c r="E343" t="s">
+        <v>22</v>
+      </c>
+      <c r="F343">
+        <v>3</v>
+      </c>
+      <c r="G343">
+        <v>100</v>
+      </c>
+      <c r="I343" t="s">
+        <v>16</v>
+      </c>
+      <c r="J343" t="s">
+        <v>17</v>
+      </c>
+      <c r="K343" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>103</v>
+      </c>
+      <c r="B344" t="s">
+        <v>106</v>
+      </c>
+      <c r="C344" t="s">
+        <v>107</v>
+      </c>
+      <c r="D344">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E344" t="s">
+        <v>22</v>
+      </c>
+      <c r="F344">
+        <v>3</v>
+      </c>
+      <c r="G344">
+        <v>100</v>
+      </c>
+      <c r="I344" t="s">
+        <v>16</v>
+      </c>
+      <c r="J344" t="s">
+        <v>17</v>
+      </c>
+      <c r="K344" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>103</v>
+      </c>
+      <c r="B345" t="s">
+        <v>108</v>
+      </c>
+      <c r="C345" t="s">
+        <v>109</v>
+      </c>
+      <c r="D345">
+        <v>3.048</v>
+      </c>
+      <c r="E345" t="s">
+        <v>22</v>
+      </c>
+      <c r="F345">
+        <v>3</v>
+      </c>
+      <c r="G345">
+        <v>100</v>
+      </c>
+      <c r="I345" t="s">
+        <v>16</v>
+      </c>
+      <c r="J345" t="s">
+        <v>17</v>
+      </c>
+      <c r="K345" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>103</v>
+      </c>
+      <c r="B346" t="s">
+        <v>110</v>
+      </c>
+      <c r="C346" t="s">
+        <v>111</v>
+      </c>
+      <c r="D346">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E346" t="s">
+        <v>22</v>
+      </c>
+      <c r="F346">
+        <v>3</v>
+      </c>
+      <c r="G346">
+        <v>100</v>
+      </c>
+      <c r="I346" t="s">
+        <v>16</v>
+      </c>
+      <c r="J346" t="s">
+        <v>17</v>
+      </c>
+      <c r="K346" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>103</v>
+      </c>
+      <c r="B347" t="s">
+        <v>112</v>
+      </c>
+      <c r="C347" t="s">
+        <v>113</v>
+      </c>
+      <c r="D347">
+        <v>3.0459999999999998</v>
+      </c>
+      <c r="E347" t="s">
+        <v>22</v>
+      </c>
+      <c r="F347">
+        <v>3</v>
+      </c>
+      <c r="G347">
+        <v>100</v>
+      </c>
+      <c r="I347" t="s">
+        <v>16</v>
+      </c>
+      <c r="J347" t="s">
+        <v>17</v>
+      </c>
+      <c r="K347" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>103</v>
+      </c>
+      <c r="B348" t="s">
+        <v>114</v>
+      </c>
+      <c r="C348" t="s">
+        <v>115</v>
+      </c>
+      <c r="D348">
+        <v>1.855</v>
+      </c>
+      <c r="E348" t="s">
+        <v>22</v>
+      </c>
+      <c r="F348">
+        <v>3</v>
+      </c>
+      <c r="G348">
+        <v>100</v>
+      </c>
+      <c r="I348" t="s">
+        <v>16</v>
+      </c>
+      <c r="J348" t="s">
+        <v>17</v>
+      </c>
+      <c r="K348" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>116</v>
+      </c>
+      <c r="B349" t="s">
+        <v>117</v>
+      </c>
+      <c r="C349" t="s">
+        <v>118</v>
+      </c>
+      <c r="D349">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E349" t="s">
+        <v>14</v>
+      </c>
+      <c r="F349">
+        <v>5</v>
+      </c>
+      <c r="G349">
+        <v>100</v>
+      </c>
+      <c r="I349" t="s">
+        <v>16</v>
+      </c>
+      <c r="J349" t="s">
+        <v>17</v>
+      </c>
+      <c r="K349" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>116</v>
+      </c>
+      <c r="B350" t="s">
+        <v>119</v>
+      </c>
+      <c r="C350" t="s">
+        <v>120</v>
+      </c>
+      <c r="D350">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E350" t="s">
+        <v>14</v>
+      </c>
+      <c r="F350">
+        <v>5</v>
+      </c>
+      <c r="G350">
+        <v>100</v>
+      </c>
+      <c r="I350" t="s">
+        <v>16</v>
+      </c>
+      <c r="J350" t="s">
+        <v>17</v>
+      </c>
+      <c r="K350" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>116</v>
+      </c>
+      <c r="B351" t="s">
+        <v>121</v>
+      </c>
+      <c r="C351" t="s">
+        <v>122</v>
+      </c>
+      <c r="D351">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E351" t="s">
+        <v>14</v>
+      </c>
+      <c r="F351">
+        <v>5</v>
+      </c>
+      <c r="G351">
+        <v>100</v>
+      </c>
+      <c r="I351" t="s">
+        <v>16</v>
+      </c>
+      <c r="J351" t="s">
+        <v>17</v>
+      </c>
+      <c r="K351" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>116</v>
+      </c>
+      <c r="B352" t="s">
+        <v>123</v>
+      </c>
+      <c r="C352" t="s">
+        <v>124</v>
+      </c>
+      <c r="D352">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E352" t="s">
+        <v>14</v>
+      </c>
+      <c r="F352">
+        <v>5</v>
+      </c>
+      <c r="G352">
+        <v>100</v>
+      </c>
+      <c r="I352" t="s">
+        <v>16</v>
+      </c>
+      <c r="J352" t="s">
+        <v>17</v>
+      </c>
+      <c r="K352" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>116</v>
+      </c>
+      <c r="B353" t="s">
+        <v>125</v>
+      </c>
+      <c r="C353" t="s">
+        <v>126</v>
+      </c>
+      <c r="D353">
+        <v>3.02</v>
+      </c>
+      <c r="E353" t="s">
+        <v>14</v>
+      </c>
+      <c r="F353">
+        <v>5</v>
+      </c>
+      <c r="G353">
+        <v>100</v>
+      </c>
+      <c r="I353" t="s">
+        <v>16</v>
+      </c>
+      <c r="J353" t="s">
+        <v>17</v>
+      </c>
+      <c r="K353" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>116</v>
+      </c>
+      <c r="B354" t="s">
+        <v>127</v>
+      </c>
+      <c r="C354" t="s">
+        <v>128</v>
+      </c>
+      <c r="D354">
+        <v>2.3460000000000001</v>
+      </c>
+      <c r="E354" t="s">
+        <v>14</v>
+      </c>
+      <c r="F354">
+        <v>5</v>
+      </c>
+      <c r="G354">
+        <v>100</v>
+      </c>
+      <c r="I354" t="s">
+        <v>16</v>
+      </c>
+      <c r="J354" t="s">
+        <v>17</v>
+      </c>
+      <c r="K354" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>116</v>
+      </c>
+      <c r="B355" t="s">
+        <v>129</v>
+      </c>
+      <c r="C355" t="s">
+        <v>130</v>
+      </c>
+      <c r="D355">
+        <v>3.0659999999999998</v>
+      </c>
+      <c r="E355" t="s">
+        <v>14</v>
+      </c>
+      <c r="F355">
+        <v>5</v>
+      </c>
+      <c r="G355">
+        <v>100</v>
+      </c>
+      <c r="I355" t="s">
+        <v>16</v>
+      </c>
+      <c r="J355" t="s">
+        <v>17</v>
+      </c>
+      <c r="K355" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>116</v>
+      </c>
+      <c r="B356" t="s">
+        <v>131</v>
+      </c>
+      <c r="C356" t="s">
+        <v>132</v>
+      </c>
+      <c r="D356">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E356" t="s">
+        <v>14</v>
+      </c>
+      <c r="F356">
+        <v>5</v>
+      </c>
+      <c r="G356">
+        <v>100</v>
+      </c>
+      <c r="I356" t="s">
+        <v>16</v>
+      </c>
+      <c r="J356" t="s">
+        <v>17</v>
+      </c>
+      <c r="K356" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>116</v>
+      </c>
+      <c r="B357" t="s">
+        <v>133</v>
+      </c>
+      <c r="C357" t="s">
+        <v>134</v>
+      </c>
+      <c r="D357">
+        <v>3.0739999999999998</v>
+      </c>
+      <c r="E357" t="s">
+        <v>14</v>
+      </c>
+      <c r="F357">
+        <v>5</v>
+      </c>
+      <c r="G357">
+        <v>100</v>
+      </c>
+      <c r="I357" t="s">
+        <v>16</v>
+      </c>
+      <c r="J357" t="s">
+        <v>17</v>
+      </c>
+      <c r="K357" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>116</v>
+      </c>
+      <c r="B358" t="s">
+        <v>135</v>
+      </c>
+      <c r="C358" t="s">
+        <v>136</v>
+      </c>
+      <c r="D358">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="E358" t="s">
+        <v>14</v>
+      </c>
+      <c r="F358">
+        <v>5</v>
+      </c>
+      <c r="G358">
+        <v>100</v>
+      </c>
+      <c r="I358" t="s">
+        <v>16</v>
+      </c>
+      <c r="J358" t="s">
+        <v>17</v>
+      </c>
+      <c r="K358" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>116</v>
+      </c>
+      <c r="B359" t="s">
+        <v>137</v>
+      </c>
+      <c r="C359" t="s">
+        <v>115</v>
+      </c>
+      <c r="D359">
+        <v>1.89</v>
+      </c>
+      <c r="E359" t="s">
+        <v>14</v>
+      </c>
+      <c r="F359">
+        <v>5</v>
+      </c>
+      <c r="G359">
+        <v>100</v>
+      </c>
+      <c r="I359" t="s">
+        <v>16</v>
+      </c>
+      <c r="J359" t="s">
+        <v>17</v>
+      </c>
+      <c r="K359" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>138</v>
+      </c>
+      <c r="B360" t="s">
+        <v>139</v>
+      </c>
+      <c r="C360" t="s">
+        <v>140</v>
+      </c>
+      <c r="D360">
+        <v>3.0489999999999999</v>
+      </c>
+      <c r="E360" t="s">
+        <v>14</v>
+      </c>
+      <c r="F360">
+        <v>5</v>
+      </c>
+      <c r="G360">
+        <v>100</v>
+      </c>
+      <c r="I360" t="s">
+        <v>16</v>
+      </c>
+      <c r="J360" t="s">
+        <v>17</v>
+      </c>
+      <c r="K360" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>138</v>
+      </c>
+      <c r="B361" t="s">
+        <v>141</v>
+      </c>
+      <c r="C361" t="s">
+        <v>142</v>
+      </c>
+      <c r="D361">
+        <v>3.004</v>
+      </c>
+      <c r="E361" t="s">
+        <v>14</v>
+      </c>
+      <c r="F361">
+        <v>5</v>
+      </c>
+      <c r="G361">
+        <v>100</v>
+      </c>
+      <c r="I361" t="s">
+        <v>16</v>
+      </c>
+      <c r="J361" t="s">
+        <v>17</v>
+      </c>
+      <c r="K361" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>138</v>
+      </c>
+      <c r="B362" t="s">
+        <v>143</v>
+      </c>
+      <c r="C362" t="s">
+        <v>144</v>
+      </c>
+      <c r="D362">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E362" t="s">
+        <v>14</v>
+      </c>
+      <c r="F362">
+        <v>5</v>
+      </c>
+      <c r="G362">
+        <v>100</v>
+      </c>
+      <c r="I362" t="s">
+        <v>16</v>
+      </c>
+      <c r="J362" t="s">
+        <v>17</v>
+      </c>
+      <c r="K362" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>138</v>
+      </c>
+      <c r="B363" t="s">
+        <v>145</v>
+      </c>
+      <c r="C363" t="s">
+        <v>146</v>
+      </c>
+      <c r="D363">
+        <v>3.004</v>
+      </c>
+      <c r="E363" t="s">
+        <v>14</v>
+      </c>
+      <c r="F363">
+        <v>5</v>
+      </c>
+      <c r="G363">
+        <v>100</v>
+      </c>
+      <c r="I363" t="s">
+        <v>16</v>
+      </c>
+      <c r="J363" t="s">
+        <v>17</v>
+      </c>
+      <c r="K363" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>138</v>
+      </c>
+      <c r="B364" t="s">
+        <v>147</v>
+      </c>
+      <c r="C364" t="s">
+        <v>148</v>
+      </c>
+      <c r="D364">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="E364" t="s">
+        <v>14</v>
+      </c>
+      <c r="F364">
+        <v>5</v>
+      </c>
+      <c r="G364">
+        <v>100</v>
+      </c>
+      <c r="I364" t="s">
+        <v>16</v>
+      </c>
+      <c r="J364" t="s">
+        <v>17</v>
+      </c>
+      <c r="K364" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>138</v>
+      </c>
+      <c r="B365" t="s">
+        <v>149</v>
+      </c>
+      <c r="C365" t="s">
+        <v>150</v>
+      </c>
+      <c r="D365">
+        <v>3.004</v>
+      </c>
+      <c r="E365" t="s">
+        <v>14</v>
+      </c>
+      <c r="F365">
+        <v>5</v>
+      </c>
+      <c r="G365">
+        <v>100</v>
+      </c>
+      <c r="I365" t="s">
+        <v>16</v>
+      </c>
+      <c r="J365" t="s">
+        <v>17</v>
+      </c>
+      <c r="K365" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>138</v>
+      </c>
+      <c r="B366" t="s">
+        <v>151</v>
+      </c>
+      <c r="C366" t="s">
+        <v>102</v>
+      </c>
+      <c r="D366">
+        <v>3.3980000000000001</v>
+      </c>
+      <c r="E366" t="s">
+        <v>14</v>
+      </c>
+      <c r="F366">
+        <v>12</v>
+      </c>
+      <c r="G366">
+        <v>100</v>
+      </c>
+      <c r="I366" t="s">
+        <v>16</v>
+      </c>
+      <c r="J366" t="s">
+        <v>17</v>
+      </c>
+      <c r="K366" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>152</v>
+      </c>
+      <c r="B367" t="s">
+        <v>153</v>
+      </c>
+      <c r="C367" t="s">
+        <v>154</v>
+      </c>
+      <c r="D367">
+        <v>3.056</v>
+      </c>
+      <c r="E367" t="s">
+        <v>155</v>
+      </c>
+      <c r="F367">
+        <v>12</v>
+      </c>
+      <c r="G367">
+        <v>100</v>
+      </c>
+      <c r="I367" t="s">
+        <v>16</v>
+      </c>
+      <c r="J367" t="s">
+        <v>17</v>
+      </c>
+      <c r="K367" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>152</v>
+      </c>
+      <c r="B368" t="s">
+        <v>156</v>
+      </c>
+      <c r="C368" t="s">
+        <v>157</v>
+      </c>
+      <c r="D368">
+        <v>3.0739999999999998</v>
+      </c>
+      <c r="E368" t="s">
+        <v>155</v>
+      </c>
+      <c r="F368">
+        <v>12</v>
+      </c>
+      <c r="G368">
+        <v>100</v>
+      </c>
+      <c r="I368" t="s">
+        <v>16</v>
+      </c>
+      <c r="J368" t="s">
+        <v>17</v>
+      </c>
+      <c r="K368" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>152</v>
+      </c>
+      <c r="B369" t="s">
+        <v>158</v>
+      </c>
+      <c r="C369" t="s">
+        <v>159</v>
+      </c>
+      <c r="D369">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E369" t="s">
+        <v>155</v>
+      </c>
+      <c r="F369">
+        <v>12</v>
+      </c>
+      <c r="G369">
+        <v>100</v>
+      </c>
+      <c r="I369" t="s">
+        <v>16</v>
+      </c>
+      <c r="J369" t="s">
+        <v>17</v>
+      </c>
+      <c r="K369" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>152</v>
+      </c>
+      <c r="B370" t="s">
+        <v>160</v>
+      </c>
+      <c r="C370" t="s">
+        <v>102</v>
+      </c>
+      <c r="D370">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="E370" t="s">
+        <v>155</v>
+      </c>
+      <c r="F370">
+        <v>12</v>
+      </c>
+      <c r="G370">
+        <v>100</v>
+      </c>
+      <c r="I370" t="s">
+        <v>16</v>
+      </c>
+      <c r="J370" t="s">
+        <v>17</v>
+      </c>
+      <c r="K370" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>152</v>
+      </c>
+      <c r="B371" t="s">
+        <v>161</v>
+      </c>
+      <c r="C371" t="s">
+        <v>162</v>
+      </c>
+      <c r="D371">
+        <v>3.0960000000000001</v>
+      </c>
+      <c r="E371" t="s">
+        <v>155</v>
+      </c>
+      <c r="F371">
+        <v>12</v>
+      </c>
+      <c r="G371">
+        <v>100</v>
+      </c>
+      <c r="I371" t="s">
+        <v>16</v>
+      </c>
+      <c r="J371" t="s">
+        <v>17</v>
+      </c>
+      <c r="K371" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>152</v>
+      </c>
+      <c r="B372" t="s">
+        <v>163</v>
+      </c>
+      <c r="C372" t="s">
+        <v>164</v>
+      </c>
+      <c r="D372">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="E372" t="s">
+        <v>155</v>
+      </c>
+      <c r="F372">
+        <v>12</v>
+      </c>
+      <c r="G372">
+        <v>100</v>
+      </c>
+      <c r="I372" t="s">
+        <v>16</v>
+      </c>
+      <c r="J372" t="s">
+        <v>17</v>
+      </c>
+      <c r="K372" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>152</v>
+      </c>
+      <c r="B373" t="s">
+        <v>165</v>
+      </c>
+      <c r="C373" t="s">
+        <v>166</v>
+      </c>
+      <c r="D373">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E373" t="s">
+        <v>155</v>
+      </c>
+      <c r="F373">
+        <v>12</v>
+      </c>
+      <c r="G373">
+        <v>100</v>
+      </c>
+      <c r="I373" t="s">
+        <v>16</v>
+      </c>
+      <c r="J373" t="s">
+        <v>17</v>
+      </c>
+      <c r="K373" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>152</v>
+      </c>
+      <c r="B374" t="s">
+        <v>167</v>
+      </c>
+      <c r="C374" t="s">
+        <v>168</v>
+      </c>
+      <c r="D374">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E374" t="s">
+        <v>155</v>
+      </c>
+      <c r="F374">
+        <v>12</v>
+      </c>
+      <c r="G374">
+        <v>100</v>
+      </c>
+      <c r="I374" t="s">
+        <v>16</v>
+      </c>
+      <c r="J374" t="s">
+        <v>17</v>
+      </c>
+      <c r="K374" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>152</v>
+      </c>
+      <c r="B375" t="s">
+        <v>169</v>
+      </c>
+      <c r="C375" t="s">
+        <v>170</v>
+      </c>
+      <c r="D375">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E375" t="s">
+        <v>155</v>
+      </c>
+      <c r="F375">
+        <v>12</v>
+      </c>
+      <c r="G375">
+        <v>100</v>
+      </c>
+      <c r="I375" t="s">
+        <v>16</v>
+      </c>
+      <c r="J375" t="s">
+        <v>17</v>
+      </c>
+      <c r="K375" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>152</v>
+      </c>
+      <c r="B376" t="s">
+        <v>171</v>
+      </c>
+      <c r="C376" t="s">
+        <v>172</v>
+      </c>
+      <c r="D376">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E376" t="s">
+        <v>155</v>
+      </c>
+      <c r="F376">
+        <v>12</v>
+      </c>
+      <c r="G376">
+        <v>100</v>
+      </c>
+      <c r="I376" t="s">
+        <v>16</v>
+      </c>
+      <c r="J376" t="s">
+        <v>17</v>
+      </c>
+      <c r="K376" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>152</v>
+      </c>
+      <c r="B377" t="s">
+        <v>173</v>
+      </c>
+      <c r="C377" t="s">
+        <v>174</v>
+      </c>
+      <c r="D377">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E377" t="s">
+        <v>155</v>
+      </c>
+      <c r="F377">
+        <v>12</v>
+      </c>
+      <c r="G377">
+        <v>100</v>
+      </c>
+      <c r="I377" t="s">
+        <v>16</v>
+      </c>
+      <c r="J377" t="s">
+        <v>17</v>
+      </c>
+      <c r="K377" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>152</v>
+      </c>
+      <c r="B378" t="s">
+        <v>175</v>
+      </c>
+      <c r="C378" t="s">
+        <v>176</v>
+      </c>
+      <c r="D378">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E378" t="s">
+        <v>155</v>
+      </c>
+      <c r="F378">
+        <v>12</v>
+      </c>
+      <c r="G378">
+        <v>100</v>
+      </c>
+      <c r="I378" t="s">
+        <v>16</v>
+      </c>
+      <c r="J378" t="s">
+        <v>17</v>
+      </c>
+      <c r="K378" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>152</v>
+      </c>
+      <c r="B379" t="s">
+        <v>177</v>
+      </c>
+      <c r="C379" t="s">
+        <v>178</v>
+      </c>
+      <c r="D379">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E379" t="s">
+        <v>155</v>
+      </c>
+      <c r="F379">
+        <v>12</v>
+      </c>
+      <c r="G379">
+        <v>100</v>
+      </c>
+      <c r="I379" t="s">
+        <v>16</v>
+      </c>
+      <c r="J379" t="s">
+        <v>17</v>
+      </c>
+      <c r="K379" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>152</v>
+      </c>
+      <c r="B380" t="s">
+        <v>179</v>
+      </c>
+      <c r="C380" t="s">
+        <v>180</v>
+      </c>
+      <c r="D380">
+        <v>3.036</v>
+      </c>
+      <c r="E380" t="s">
+        <v>155</v>
+      </c>
+      <c r="F380">
+        <v>12</v>
+      </c>
+      <c r="G380">
+        <v>100</v>
+      </c>
+      <c r="I380" t="s">
+        <v>16</v>
+      </c>
+      <c r="J380" t="s">
+        <v>17</v>
+      </c>
+      <c r="K380" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>152</v>
+      </c>
+      <c r="B381" t="s">
+        <v>181</v>
+      </c>
+      <c r="C381" t="s">
+        <v>115</v>
+      </c>
+      <c r="D381">
+        <v>0.45</v>
+      </c>
+      <c r="E381" t="s">
+        <v>155</v>
+      </c>
+      <c r="F381">
+        <v>12</v>
+      </c>
+      <c r="G381">
+        <v>100</v>
+      </c>
+      <c r="I381" t="s">
+        <v>16</v>
+      </c>
+      <c r="J381" t="s">
+        <v>17</v>
+      </c>
+      <c r="K381" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>182</v>
+      </c>
+      <c r="B382" t="s">
+        <v>183</v>
+      </c>
+      <c r="C382" t="s">
+        <v>184</v>
+      </c>
+      <c r="D382">
+        <v>3.1230000000000002</v>
+      </c>
+      <c r="E382" t="s">
+        <v>14</v>
+      </c>
+      <c r="F382">
+        <v>4</v>
+      </c>
+      <c r="G382">
+        <v>100</v>
+      </c>
+      <c r="I382" t="s">
+        <v>16</v>
+      </c>
+      <c r="J382" t="s">
+        <v>17</v>
+      </c>
+      <c r="K382" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>182</v>
+      </c>
+      <c r="B383" t="s">
+        <v>185</v>
+      </c>
+      <c r="C383" t="s">
+        <v>186</v>
+      </c>
+      <c r="D383">
+        <v>3.1219999999999999</v>
+      </c>
+      <c r="E383" t="s">
+        <v>14</v>
+      </c>
+      <c r="F383">
+        <v>4</v>
+      </c>
+      <c r="G383">
+        <v>100</v>
+      </c>
+      <c r="I383" t="s">
+        <v>16</v>
+      </c>
+      <c r="J383" t="s">
+        <v>17</v>
+      </c>
+      <c r="K383" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>182</v>
+      </c>
+      <c r="B384" t="s">
+        <v>187</v>
+      </c>
+      <c r="C384" t="s">
+        <v>188</v>
+      </c>
+      <c r="D384">
+        <v>3.145</v>
+      </c>
+      <c r="E384" t="s">
+        <v>14</v>
+      </c>
+      <c r="F384">
+        <v>4</v>
+      </c>
+      <c r="G384">
+        <v>100</v>
+      </c>
+      <c r="I384" t="s">
+        <v>16</v>
+      </c>
+      <c r="J384" t="s">
+        <v>17</v>
+      </c>
+      <c r="K384" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>182</v>
+      </c>
+      <c r="B385" t="s">
+        <v>189</v>
+      </c>
+      <c r="C385" t="s">
+        <v>190</v>
+      </c>
+      <c r="D385">
+        <v>3.14</v>
+      </c>
+      <c r="E385" t="s">
+        <v>22</v>
+      </c>
+      <c r="F385">
+        <v>4</v>
+      </c>
+      <c r="G385">
+        <v>100</v>
+      </c>
+      <c r="I385" t="s">
+        <v>16</v>
+      </c>
+      <c r="J385" t="s">
+        <v>17</v>
+      </c>
+      <c r="K385" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>182</v>
+      </c>
+      <c r="B386" t="s">
+        <v>191</v>
+      </c>
+      <c r="C386" t="s">
+        <v>192</v>
+      </c>
+      <c r="D386">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E386" t="s">
+        <v>22</v>
+      </c>
+      <c r="F386">
+        <v>4</v>
+      </c>
+      <c r="G386">
+        <v>100</v>
+      </c>
+      <c r="I386" t="s">
+        <v>16</v>
+      </c>
+      <c r="J386" t="s">
+        <v>17</v>
+      </c>
+      <c r="K386" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>182</v>
+      </c>
+      <c r="B387" t="s">
+        <v>193</v>
+      </c>
+      <c r="C387" t="s">
+        <v>194</v>
+      </c>
+      <c r="D387">
+        <v>3.077</v>
+      </c>
+      <c r="E387" t="s">
+        <v>22</v>
+      </c>
+      <c r="F387">
+        <v>4</v>
+      </c>
+      <c r="G387">
+        <v>100</v>
+      </c>
+      <c r="I387" t="s">
+        <v>16</v>
+      </c>
+      <c r="J387" t="s">
+        <v>17</v>
+      </c>
+      <c r="K387" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>182</v>
+      </c>
+      <c r="B388" t="s">
+        <v>195</v>
+      </c>
+      <c r="C388" t="s">
+        <v>196</v>
+      </c>
+      <c r="D388">
+        <v>3.1579999999999999</v>
+      </c>
+      <c r="E388" t="s">
+        <v>22</v>
+      </c>
+      <c r="F388">
+        <v>4</v>
+      </c>
+      <c r="G388">
+        <v>100</v>
+      </c>
+      <c r="I388" t="s">
+        <v>16</v>
+      </c>
+      <c r="J388" t="s">
+        <v>17</v>
+      </c>
+      <c r="K388" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>182</v>
+      </c>
+      <c r="B389" t="s">
+        <v>197</v>
+      </c>
+      <c r="C389" t="s">
+        <v>115</v>
+      </c>
+      <c r="D389">
+        <v>1.8149999999999999</v>
+      </c>
+      <c r="E389" t="s">
+        <v>22</v>
+      </c>
+      <c r="F389">
+        <v>4</v>
+      </c>
+      <c r="G389">
+        <v>100</v>
+      </c>
+      <c r="I389" t="s">
+        <v>16</v>
+      </c>
+      <c r="J389" t="s">
+        <v>17</v>
+      </c>
+      <c r="K389" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>198</v>
+      </c>
+      <c r="B390" t="s">
+        <v>199</v>
+      </c>
+      <c r="C390" t="s">
+        <v>200</v>
+      </c>
+      <c r="D390">
+        <v>3.024</v>
+      </c>
+      <c r="E390" t="s">
+        <v>22</v>
+      </c>
+      <c r="F390">
+        <v>1</v>
+      </c>
+      <c r="G390">
+        <v>100</v>
+      </c>
+      <c r="I390" t="s">
+        <v>16</v>
+      </c>
+      <c r="J390" t="s">
+        <v>17</v>
+      </c>
+      <c r="K390" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>198</v>
+      </c>
+      <c r="B391" t="s">
+        <v>201</v>
+      </c>
+      <c r="C391" t="s">
+        <v>202</v>
+      </c>
+      <c r="D391">
+        <v>3.016</v>
+      </c>
+      <c r="E391" t="s">
+        <v>22</v>
+      </c>
+      <c r="F391">
+        <v>1</v>
+      </c>
+      <c r="G391">
+        <v>100</v>
+      </c>
+      <c r="I391" t="s">
+        <v>16</v>
+      </c>
+      <c r="J391" t="s">
+        <v>17</v>
+      </c>
+      <c r="K391" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>198</v>
+      </c>
+      <c r="B392" t="s">
+        <v>203</v>
+      </c>
+      <c r="C392" t="s">
+        <v>204</v>
+      </c>
+      <c r="D392">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E392" t="s">
+        <v>22</v>
+      </c>
+      <c r="F392">
+        <v>1</v>
+      </c>
+      <c r="G392">
+        <v>100</v>
+      </c>
+      <c r="I392" t="s">
+        <v>16</v>
+      </c>
+      <c r="J392" t="s">
+        <v>17</v>
+      </c>
+      <c r="K392" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>198</v>
+      </c>
+      <c r="B393" t="s">
+        <v>205</v>
+      </c>
+      <c r="C393" t="s">
+        <v>206</v>
+      </c>
+      <c r="D393">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E393" t="s">
+        <v>22</v>
+      </c>
+      <c r="F393">
+        <v>1</v>
+      </c>
+      <c r="G393">
+        <v>100</v>
+      </c>
+      <c r="I393" t="s">
+        <v>16</v>
+      </c>
+      <c r="J393" t="s">
+        <v>17</v>
+      </c>
+      <c r="K393" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>198</v>
+      </c>
+      <c r="B394" t="s">
+        <v>207</v>
+      </c>
+      <c r="C394" t="s">
+        <v>208</v>
+      </c>
+      <c r="D394">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E394" t="s">
+        <v>22</v>
+      </c>
+      <c r="F394">
+        <v>1</v>
+      </c>
+      <c r="G394">
+        <v>100</v>
+      </c>
+      <c r="I394" t="s">
+        <v>16</v>
+      </c>
+      <c r="J394" t="s">
+        <v>17</v>
+      </c>
+      <c r="K394" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>198</v>
+      </c>
+      <c r="B395" t="s">
+        <v>209</v>
+      </c>
+      <c r="C395" t="s">
+        <v>210</v>
+      </c>
+      <c r="D395">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E395" t="s">
+        <v>22</v>
+      </c>
+      <c r="F395">
+        <v>1</v>
+      </c>
+      <c r="G395">
+        <v>100</v>
+      </c>
+      <c r="I395" t="s">
+        <v>16</v>
+      </c>
+      <c r="J395" t="s">
+        <v>17</v>
+      </c>
+      <c r="K395" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>198</v>
+      </c>
+      <c r="B396" t="s">
+        <v>211</v>
+      </c>
+      <c r="C396" t="s">
+        <v>212</v>
+      </c>
+      <c r="D396">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E396" t="s">
+        <v>22</v>
+      </c>
+      <c r="F396">
+        <v>1</v>
+      </c>
+      <c r="G396">
+        <v>100</v>
+      </c>
+      <c r="I396" t="s">
+        <v>16</v>
+      </c>
+      <c r="J396" t="s">
+        <v>17</v>
+      </c>
+      <c r="K396" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>198</v>
+      </c>
+      <c r="B397" t="s">
+        <v>213</v>
+      </c>
+      <c r="C397" t="s">
+        <v>214</v>
+      </c>
+      <c r="D397">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E397" t="s">
+        <v>22</v>
+      </c>
+      <c r="F397">
+        <v>1</v>
+      </c>
+      <c r="G397">
+        <v>100</v>
+      </c>
+      <c r="I397" t="s">
+        <v>16</v>
+      </c>
+      <c r="J397" t="s">
+        <v>17</v>
+      </c>
+      <c r="K397" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>198</v>
+      </c>
+      <c r="B398" t="s">
+        <v>215</v>
+      </c>
+      <c r="C398" t="s">
+        <v>216</v>
+      </c>
+      <c r="D398">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E398" t="s">
+        <v>22</v>
+      </c>
+      <c r="F398">
+        <v>1</v>
+      </c>
+      <c r="G398">
+        <v>100</v>
+      </c>
+      <c r="I398" t="s">
+        <v>16</v>
+      </c>
+      <c r="J398" t="s">
+        <v>17</v>
+      </c>
+      <c r="K398" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>198</v>
+      </c>
+      <c r="B399" t="s">
+        <v>217</v>
+      </c>
+      <c r="C399" t="s">
+        <v>218</v>
+      </c>
+      <c r="D399">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E399" t="s">
+        <v>22</v>
+      </c>
+      <c r="F399">
+        <v>1</v>
+      </c>
+      <c r="G399">
+        <v>100</v>
+      </c>
+      <c r="I399" t="s">
+        <v>16</v>
+      </c>
+      <c r="J399" t="s">
+        <v>17</v>
+      </c>
+      <c r="K399" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>198</v>
+      </c>
+      <c r="B400" t="s">
+        <v>219</v>
+      </c>
+      <c r="C400" t="s">
+        <v>220</v>
+      </c>
+      <c r="D400">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E400" t="s">
+        <v>22</v>
+      </c>
+      <c r="F400">
+        <v>1</v>
+      </c>
+      <c r="G400">
+        <v>100</v>
+      </c>
+      <c r="I400" t="s">
+        <v>16</v>
+      </c>
+      <c r="J400" t="s">
+        <v>17</v>
+      </c>
+      <c r="K400" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>198</v>
+      </c>
+      <c r="B401" t="s">
+        <v>221</v>
+      </c>
+      <c r="C401" t="s">
+        <v>102</v>
+      </c>
+      <c r="D401">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="E401" t="s">
+        <v>22</v>
+      </c>
+      <c r="F401">
+        <v>1</v>
+      </c>
+      <c r="G401">
+        <v>100</v>
+      </c>
+      <c r="I401" t="s">
+        <v>16</v>
+      </c>
+      <c r="J401" t="s">
+        <v>17</v>
+      </c>
+      <c r="K401" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>222</v>
+      </c>
+      <c r="B402" t="s">
+        <v>223</v>
+      </c>
+      <c r="C402" t="s">
+        <v>102</v>
+      </c>
+      <c r="D402">
+        <v>3.012</v>
+      </c>
+      <c r="E402" t="s">
+        <v>22</v>
+      </c>
+      <c r="F402">
+        <v>5</v>
+      </c>
+      <c r="G402">
+        <v>100</v>
+      </c>
+      <c r="I402" t="s">
+        <v>16</v>
+      </c>
+      <c r="J402" t="s">
+        <v>17</v>
+      </c>
+      <c r="K402" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>222</v>
+      </c>
+      <c r="B403" t="s">
+        <v>224</v>
+      </c>
+      <c r="C403" t="s">
+        <v>102</v>
+      </c>
+      <c r="D403">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="E403" t="s">
+        <v>22</v>
+      </c>
+      <c r="F403">
+        <v>5</v>
+      </c>
+      <c r="G403">
+        <v>100</v>
+      </c>
+      <c r="I403" t="s">
+        <v>16</v>
+      </c>
+      <c r="J403" t="s">
+        <v>17</v>
+      </c>
+      <c r="K403" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>222</v>
+      </c>
+      <c r="B404" t="s">
+        <v>225</v>
+      </c>
+      <c r="C404" t="s">
+        <v>102</v>
+      </c>
+      <c r="D404">
+        <v>3.05</v>
+      </c>
+      <c r="E404" t="s">
+        <v>22</v>
+      </c>
+      <c r="F404">
+        <v>5</v>
+      </c>
+      <c r="G404">
+        <v>100</v>
+      </c>
+      <c r="I404" t="s">
+        <v>16</v>
+      </c>
+      <c r="J404" t="s">
+        <v>17</v>
+      </c>
+      <c r="K404" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>222</v>
+      </c>
+      <c r="B405" t="s">
+        <v>226</v>
+      </c>
+      <c r="C405" t="s">
+        <v>102</v>
+      </c>
+      <c r="D405">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E405" t="s">
+        <v>22</v>
+      </c>
+      <c r="F405">
+        <v>5</v>
+      </c>
+      <c r="G405">
+        <v>100</v>
+      </c>
+      <c r="I405" t="s">
+        <v>16</v>
+      </c>
+      <c r="J405" t="s">
+        <v>17</v>
+      </c>
+      <c r="K405" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>222</v>
+      </c>
+      <c r="B406" t="s">
+        <v>227</v>
+      </c>
+      <c r="C406" t="s">
+        <v>102</v>
+      </c>
+      <c r="D406">
+        <v>2.3879999999999999</v>
+      </c>
+      <c r="E406" t="s">
+        <v>22</v>
+      </c>
+      <c r="F406">
+        <v>5</v>
+      </c>
+      <c r="G406">
+        <v>100</v>
+      </c>
+      <c r="I406" t="s">
+        <v>16</v>
+      </c>
+      <c r="J406" t="s">
+        <v>17</v>
+      </c>
+      <c r="K406" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>228</v>
+      </c>
+      <c r="B407" t="s">
+        <v>229</v>
+      </c>
+      <c r="C407" t="s">
+        <v>102</v>
+      </c>
+      <c r="D407">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E407" t="s">
+        <v>22</v>
+      </c>
+      <c r="F407">
+        <v>1</v>
+      </c>
+      <c r="G407">
+        <v>100</v>
+      </c>
+      <c r="I407" t="s">
+        <v>16</v>
+      </c>
+      <c r="J407" t="s">
+        <v>17</v>
+      </c>
+      <c r="K407" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>228</v>
+      </c>
+      <c r="B408" t="s">
+        <v>230</v>
+      </c>
+      <c r="C408" t="s">
+        <v>102</v>
+      </c>
+      <c r="D408">
+        <v>3.024</v>
+      </c>
+      <c r="E408" t="s">
+        <v>22</v>
+      </c>
+      <c r="F408">
+        <v>1</v>
+      </c>
+      <c r="G408">
+        <v>100</v>
+      </c>
+      <c r="I408" t="s">
+        <v>16</v>
+      </c>
+      <c r="J408" t="s">
+        <v>17</v>
+      </c>
+      <c r="K408" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>228</v>
+      </c>
+      <c r="B409" t="s">
+        <v>231</v>
+      </c>
+      <c r="C409" t="s">
+        <v>102</v>
+      </c>
+      <c r="D409">
+        <v>3.004</v>
+      </c>
+      <c r="E409" t="s">
+        <v>22</v>
+      </c>
+      <c r="F409">
+        <v>1</v>
+      </c>
+      <c r="G409">
+        <v>100</v>
+      </c>
+      <c r="I409" t="s">
+        <v>16</v>
+      </c>
+      <c r="J409" t="s">
+        <v>17</v>
+      </c>
+      <c r="K409" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>228</v>
+      </c>
+      <c r="B410" t="s">
+        <v>232</v>
+      </c>
+      <c r="C410" t="s">
+        <v>102</v>
+      </c>
+      <c r="D410">
+        <v>3.032</v>
+      </c>
+      <c r="E410" t="s">
+        <v>22</v>
+      </c>
+      <c r="F410">
+        <v>1</v>
+      </c>
+      <c r="G410">
+        <v>100</v>
+      </c>
+      <c r="I410" t="s">
+        <v>16</v>
+      </c>
+      <c r="J410" t="s">
+        <v>17</v>
+      </c>
+      <c r="K410" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>228</v>
+      </c>
+      <c r="B411" t="s">
+        <v>233</v>
+      </c>
+      <c r="C411" t="s">
+        <v>102</v>
+      </c>
+      <c r="D411">
+        <v>3.032</v>
+      </c>
+      <c r="E411" t="s">
+        <v>22</v>
+      </c>
+      <c r="F411">
+        <v>1</v>
+      </c>
+      <c r="G411">
+        <v>100</v>
+      </c>
+      <c r="I411" t="s">
+        <v>16</v>
+      </c>
+      <c r="J411" t="s">
+        <v>17</v>
+      </c>
+      <c r="K411" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>228</v>
+      </c>
+      <c r="B412" t="s">
+        <v>234</v>
+      </c>
+      <c r="C412" t="s">
+        <v>102</v>
+      </c>
+      <c r="D412">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E412" t="s">
+        <v>22</v>
+      </c>
+      <c r="F412">
+        <v>1</v>
+      </c>
+      <c r="G412">
+        <v>100</v>
+      </c>
+      <c r="I412" t="s">
+        <v>16</v>
+      </c>
+      <c r="J412" t="s">
+        <v>17</v>
+      </c>
+      <c r="K412" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>228</v>
+      </c>
+      <c r="B413" t="s">
+        <v>235</v>
+      </c>
+      <c r="C413" t="s">
+        <v>102</v>
+      </c>
+      <c r="D413">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E413" t="s">
+        <v>22</v>
+      </c>
+      <c r="F413">
+        <v>1</v>
+      </c>
+      <c r="G413">
+        <v>100</v>
+      </c>
+      <c r="I413" t="s">
+        <v>16</v>
+      </c>
+      <c r="J413" t="s">
+        <v>17</v>
+      </c>
+      <c r="K413" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>228</v>
+      </c>
+      <c r="B414" t="s">
+        <v>236</v>
+      </c>
+      <c r="C414" t="s">
+        <v>102</v>
+      </c>
+      <c r="D414">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="E414" t="s">
+        <v>22</v>
+      </c>
+      <c r="F414">
+        <v>1</v>
+      </c>
+      <c r="G414">
+        <v>100</v>
+      </c>
+      <c r="I414" t="s">
+        <v>16</v>
+      </c>
+      <c r="J414" t="s">
+        <v>17</v>
+      </c>
+      <c r="K414" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>228</v>
+      </c>
+      <c r="B415" t="s">
+        <v>237</v>
+      </c>
+      <c r="C415" t="s">
+        <v>102</v>
+      </c>
+      <c r="D415">
+        <v>0.95</v>
+      </c>
+      <c r="E415" t="s">
+        <v>22</v>
+      </c>
+      <c r="F415">
+        <v>1</v>
+      </c>
+      <c r="G415">
+        <v>100</v>
+      </c>
+      <c r="I415" t="s">
+        <v>16</v>
+      </c>
+      <c r="J415" t="s">
+        <v>17</v>
+      </c>
+      <c r="K415" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>238</v>
+      </c>
+      <c r="B416" t="s">
+        <v>238</v>
+      </c>
+      <c r="C416" t="s">
+        <v>31</v>
+      </c>
+      <c r="D416">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E416" t="s">
+        <v>90</v>
+      </c>
+      <c r="F416">
+        <v>1</v>
+      </c>
+      <c r="G416">
+        <v>100</v>
+      </c>
+      <c r="I416" t="s">
+        <v>16</v>
+      </c>
+      <c r="J416" t="s">
+        <v>17</v>
+      </c>
+      <c r="K416" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>239</v>
+      </c>
+      <c r="B417" t="s">
+        <v>240</v>
+      </c>
+      <c r="C417" t="s">
+        <v>241</v>
+      </c>
+      <c r="D417">
+        <v>3.077</v>
+      </c>
+      <c r="E417" t="s">
+        <v>50</v>
+      </c>
+      <c r="F417">
+        <v>2</v>
+      </c>
+      <c r="G417">
+        <v>100</v>
+      </c>
+      <c r="I417" t="s">
+        <v>16</v>
+      </c>
+      <c r="J417" t="s">
+        <v>17</v>
+      </c>
+      <c r="K417" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>239</v>
+      </c>
+      <c r="B418" t="s">
+        <v>242</v>
+      </c>
+      <c r="C418" t="s">
+        <v>243</v>
+      </c>
+      <c r="D418">
+        <v>3.08</v>
+      </c>
+      <c r="E418" t="s">
+        <v>50</v>
+      </c>
+      <c r="F418">
+        <v>2</v>
+      </c>
+      <c r="G418">
+        <v>100</v>
+      </c>
+      <c r="I418" t="s">
+        <v>16</v>
+      </c>
+      <c r="J418" t="s">
+        <v>17</v>
+      </c>
+      <c r="K418" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>239</v>
+      </c>
+      <c r="B419" t="s">
+        <v>244</v>
+      </c>
+      <c r="C419" t="s">
+        <v>245</v>
+      </c>
+      <c r="D419">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E419" t="s">
+        <v>50</v>
+      </c>
+      <c r="F419">
+        <v>2</v>
+      </c>
+      <c r="G419">
+        <v>100</v>
+      </c>
+      <c r="I419" t="s">
+        <v>16</v>
+      </c>
+      <c r="J419" t="s">
+        <v>17</v>
+      </c>
+      <c r="K419" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>239</v>
+      </c>
+      <c r="B420" t="s">
+        <v>246</v>
+      </c>
+      <c r="C420" t="s">
+        <v>247</v>
+      </c>
+      <c r="D420">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E420" t="s">
+        <v>50</v>
+      </c>
+      <c r="F420">
+        <v>2</v>
+      </c>
+      <c r="G420">
+        <v>100</v>
+      </c>
+      <c r="I420" t="s">
+        <v>16</v>
+      </c>
+      <c r="J420" t="s">
+        <v>17</v>
+      </c>
+      <c r="K420" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>239</v>
+      </c>
+      <c r="B421" t="s">
+        <v>248</v>
+      </c>
+      <c r="C421" t="s">
+        <v>249</v>
+      </c>
+      <c r="D421">
+        <v>3.0510000000000002</v>
+      </c>
+      <c r="E421" t="s">
+        <v>50</v>
+      </c>
+      <c r="F421">
+        <v>2</v>
+      </c>
+      <c r="G421">
+        <v>100</v>
+      </c>
+      <c r="I421" t="s">
+        <v>16</v>
+      </c>
+      <c r="J421" t="s">
+        <v>17</v>
+      </c>
+      <c r="K421" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>239</v>
+      </c>
+      <c r="B422" t="s">
+        <v>250</v>
+      </c>
+      <c r="C422" t="s">
+        <v>102</v>
+      </c>
+      <c r="D422">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="E422" t="s">
+        <v>50</v>
+      </c>
+      <c r="F422">
+        <v>2</v>
+      </c>
+      <c r="G422">
+        <v>100</v>
+      </c>
+      <c r="I422" t="s">
+        <v>16</v>
+      </c>
+      <c r="J422" t="s">
+        <v>17</v>
+      </c>
+      <c r="K422" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>251</v>
+      </c>
+      <c r="B423" t="s">
+        <v>252</v>
+      </c>
+      <c r="C423" t="s">
+        <v>102</v>
+      </c>
+      <c r="D423">
+        <v>1.7470000000000001</v>
+      </c>
+      <c r="E423" t="s">
+        <v>22</v>
+      </c>
+      <c r="F423">
+        <v>2</v>
+      </c>
+      <c r="G423">
+        <v>100</v>
+      </c>
+      <c r="I423" t="s">
+        <v>16</v>
+      </c>
+      <c r="J423" t="s">
+        <v>17</v>
+      </c>
+      <c r="K423" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>251</v>
+      </c>
+      <c r="B424" t="s">
+        <v>253</v>
+      </c>
+      <c r="C424" t="s">
+        <v>254</v>
+      </c>
+      <c r="D424">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E424" t="s">
+        <v>22</v>
+      </c>
+      <c r="F424">
+        <v>2</v>
+      </c>
+      <c r="G424">
+        <v>100</v>
+      </c>
+      <c r="I424" t="s">
+        <v>16</v>
+      </c>
+      <c r="J424" t="s">
+        <v>17</v>
+      </c>
+      <c r="K424" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>251</v>
+      </c>
+      <c r="B425" t="s">
+        <v>255</v>
+      </c>
+      <c r="C425" t="s">
+        <v>256</v>
+      </c>
+      <c r="D425">
+        <v>3.101</v>
+      </c>
+      <c r="E425" t="s">
+        <v>22</v>
+      </c>
+      <c r="F425">
+        <v>2</v>
+      </c>
+      <c r="G425">
+        <v>100</v>
+      </c>
+      <c r="I425" t="s">
+        <v>16</v>
+      </c>
+      <c r="J425" t="s">
+        <v>17</v>
+      </c>
+      <c r="K425" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>251</v>
+      </c>
+      <c r="B426" t="s">
+        <v>257</v>
+      </c>
+      <c r="C426" t="s">
+        <v>258</v>
+      </c>
+      <c r="D426">
+        <v>3.109</v>
+      </c>
+      <c r="E426" t="s">
+        <v>22</v>
+      </c>
+      <c r="F426">
+        <v>2</v>
+      </c>
+      <c r="G426">
+        <v>100</v>
+      </c>
+      <c r="I426" t="s">
+        <v>16</v>
+      </c>
+      <c r="J426" t="s">
+        <v>17</v>
+      </c>
+      <c r="K426" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>251</v>
+      </c>
+      <c r="B427" t="s">
+        <v>259</v>
+      </c>
+      <c r="C427" t="s">
+        <v>260</v>
+      </c>
+      <c r="D427">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="E427" t="s">
+        <v>22</v>
+      </c>
+      <c r="F427">
+        <v>2</v>
+      </c>
+      <c r="G427">
+        <v>100</v>
+      </c>
+      <c r="I427" t="s">
+        <v>16</v>
+      </c>
+      <c r="J427" t="s">
+        <v>17</v>
+      </c>
+      <c r="K427" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>261</v>
+      </c>
+      <c r="B428" t="s">
+        <v>262</v>
+      </c>
+      <c r="C428" t="s">
+        <v>263</v>
+      </c>
+      <c r="D428">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E428" t="s">
+        <v>22</v>
+      </c>
+      <c r="F428">
+        <v>2</v>
+      </c>
+      <c r="G428">
+        <v>100</v>
+      </c>
+      <c r="I428" t="s">
+        <v>16</v>
+      </c>
+      <c r="J428" t="s">
+        <v>17</v>
+      </c>
+      <c r="K428" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>261</v>
+      </c>
+      <c r="B429" t="s">
+        <v>264</v>
+      </c>
+      <c r="C429" t="s">
+        <v>265</v>
+      </c>
+      <c r="D429">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="E429" t="s">
+        <v>22</v>
+      </c>
+      <c r="F429">
+        <v>2</v>
+      </c>
+      <c r="G429">
+        <v>100</v>
+      </c>
+      <c r="I429" t="s">
+        <v>16</v>
+      </c>
+      <c r="J429" t="s">
+        <v>17</v>
+      </c>
+      <c r="K429" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>261</v>
+      </c>
+      <c r="B430" t="s">
+        <v>266</v>
+      </c>
+      <c r="C430" t="s">
+        <v>267</v>
+      </c>
+      <c r="D430">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="E430" t="s">
+        <v>22</v>
+      </c>
+      <c r="F430">
+        <v>2</v>
+      </c>
+      <c r="G430">
+        <v>100</v>
+      </c>
+      <c r="I430" t="s">
+        <v>16</v>
+      </c>
+      <c r="J430" t="s">
+        <v>17</v>
+      </c>
+      <c r="K430" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>261</v>
+      </c>
+      <c r="B431" t="s">
+        <v>268</v>
+      </c>
+      <c r="C431" t="s">
+        <v>269</v>
+      </c>
+      <c r="D431">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="E431" t="s">
+        <v>22</v>
+      </c>
+      <c r="F431">
+        <v>2</v>
+      </c>
+      <c r="G431">
+        <v>100</v>
+      </c>
+      <c r="I431" t="s">
+        <v>16</v>
+      </c>
+      <c r="J431" t="s">
+        <v>17</v>
+      </c>
+      <c r="K431" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>261</v>
+      </c>
+      <c r="B432" t="s">
+        <v>270</v>
+      </c>
+      <c r="C432" t="s">
+        <v>271</v>
+      </c>
+      <c r="D432">
+        <v>3.0289999999999999</v>
+      </c>
+      <c r="E432" t="s">
+        <v>22</v>
+      </c>
+      <c r="F432">
+        <v>2</v>
+      </c>
+      <c r="G432">
+        <v>100</v>
+      </c>
+      <c r="I432" t="s">
+        <v>16</v>
+      </c>
+      <c r="J432" t="s">
+        <v>17</v>
+      </c>
+      <c r="K432" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>261</v>
+      </c>
+      <c r="B433" t="s">
+        <v>272</v>
+      </c>
+      <c r="C433" t="s">
+        <v>102</v>
+      </c>
+      <c r="D433">
+        <v>1.8340000000000001</v>
+      </c>
+      <c r="E433" t="s">
+        <v>22</v>
+      </c>
+      <c r="F433">
+        <v>2</v>
+      </c>
+      <c r="G433">
+        <v>100</v>
+      </c>
+      <c r="I433" t="s">
+        <v>16</v>
+      </c>
+      <c r="J433" t="s">
+        <v>17</v>
+      </c>
+      <c r="K433" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>273</v>
+      </c>
+      <c r="B434" t="s">
+        <v>274</v>
+      </c>
+      <c r="C434" t="s">
+        <v>275</v>
+      </c>
+      <c r="D434">
+        <v>3.032</v>
+      </c>
+      <c r="E434" t="s">
+        <v>14</v>
+      </c>
+      <c r="F434">
+        <v>6</v>
+      </c>
+      <c r="G434">
+        <v>100</v>
+      </c>
+      <c r="I434" t="s">
+        <v>16</v>
+      </c>
+      <c r="J434" t="s">
+        <v>17</v>
+      </c>
+      <c r="K434" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>273</v>
+      </c>
+      <c r="B435" t="s">
+        <v>276</v>
+      </c>
+      <c r="C435" t="s">
+        <v>277</v>
+      </c>
+      <c r="D435">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E435" t="s">
+        <v>14</v>
+      </c>
+      <c r="F435">
+        <v>6</v>
+      </c>
+      <c r="G435">
+        <v>100</v>
+      </c>
+      <c r="I435" t="s">
+        <v>16</v>
+      </c>
+      <c r="J435" t="s">
+        <v>17</v>
+      </c>
+      <c r="K435" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>273</v>
+      </c>
+      <c r="B436" t="s">
+        <v>278</v>
+      </c>
+      <c r="C436" t="s">
+        <v>279</v>
+      </c>
+      <c r="D436">
+        <v>3.0430000000000001</v>
+      </c>
+      <c r="E436" t="s">
+        <v>14</v>
+      </c>
+      <c r="F436">
+        <v>6</v>
+      </c>
+      <c r="G436">
+        <v>100</v>
+      </c>
+      <c r="I436" t="s">
+        <v>16</v>
+      </c>
+      <c r="J436" t="s">
+        <v>17</v>
+      </c>
+      <c r="K436" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>273</v>
+      </c>
+      <c r="B437" t="s">
+        <v>280</v>
+      </c>
+      <c r="C437" t="s">
+        <v>281</v>
+      </c>
+      <c r="D437">
+        <v>3.0430000000000001</v>
+      </c>
+      <c r="E437" t="s">
+        <v>14</v>
+      </c>
+      <c r="F437">
+        <v>6</v>
+      </c>
+      <c r="G437">
+        <v>100</v>
+      </c>
+      <c r="I437" t="s">
+        <v>16</v>
+      </c>
+      <c r="J437" t="s">
+        <v>17</v>
+      </c>
+      <c r="K437" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>273</v>
+      </c>
+      <c r="B438" t="s">
+        <v>282</v>
+      </c>
+      <c r="C438" t="s">
+        <v>283</v>
+      </c>
+      <c r="D438">
+        <v>3.044</v>
+      </c>
+      <c r="E438" t="s">
+        <v>14</v>
+      </c>
+      <c r="F438">
+        <v>6</v>
+      </c>
+      <c r="G438">
+        <v>100</v>
+      </c>
+      <c r="I438" t="s">
+        <v>16</v>
+      </c>
+      <c r="J438" t="s">
+        <v>17</v>
+      </c>
+      <c r="K438" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>273</v>
+      </c>
+      <c r="B439" t="s">
+        <v>284</v>
+      </c>
+      <c r="C439" t="s">
+        <v>285</v>
+      </c>
+      <c r="D439">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E439" t="s">
+        <v>14</v>
+      </c>
+      <c r="F439">
+        <v>6</v>
+      </c>
+      <c r="G439">
+        <v>100</v>
+      </c>
+      <c r="I439" t="s">
+        <v>16</v>
+      </c>
+      <c r="J439" t="s">
+        <v>17</v>
+      </c>
+      <c r="K439" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>273</v>
+      </c>
+      <c r="B440" t="s">
+        <v>286</v>
+      </c>
+      <c r="C440" t="s">
+        <v>287</v>
+      </c>
+      <c r="D440">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E440" t="s">
+        <v>14</v>
+      </c>
+      <c r="F440">
+        <v>6</v>
+      </c>
+      <c r="G440">
+        <v>100</v>
+      </c>
+      <c r="I440" t="s">
+        <v>16</v>
+      </c>
+      <c r="J440" t="s">
+        <v>17</v>
+      </c>
+      <c r="K440" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>273</v>
+      </c>
+      <c r="B441" t="s">
+        <v>288</v>
+      </c>
+      <c r="C441" t="s">
+        <v>102</v>
+      </c>
+      <c r="D441">
+        <v>1.6679999999999999</v>
+      </c>
+      <c r="E441" t="s">
+        <v>14</v>
+      </c>
+      <c r="F441">
+        <v>6</v>
+      </c>
+      <c r="G441">
+        <v>100</v>
+      </c>
+      <c r="I441" t="s">
+        <v>16</v>
+      </c>
+      <c r="J441" t="s">
+        <v>17</v>
+      </c>
+      <c r="K441" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>289</v>
+      </c>
+      <c r="B442" t="s">
+        <v>290</v>
+      </c>
+      <c r="C442" t="s">
+        <v>115</v>
+      </c>
+      <c r="D442">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E442" t="s">
+        <v>22</v>
+      </c>
+      <c r="F442">
+        <v>0</v>
+      </c>
+      <c r="G442">
+        <v>100</v>
+      </c>
+      <c r="I442" t="s">
+        <v>16</v>
+      </c>
+      <c r="J442" t="s">
+        <v>17</v>
+      </c>
+      <c r="K442" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>289</v>
+      </c>
+      <c r="B443" t="s">
+        <v>291</v>
+      </c>
+      <c r="C443" t="s">
+        <v>292</v>
+      </c>
+      <c r="D443">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E443" t="s">
+        <v>22</v>
+      </c>
+      <c r="F443">
+        <v>0</v>
+      </c>
+      <c r="G443">
+        <v>100</v>
+      </c>
+      <c r="I443" t="s">
+        <v>16</v>
+      </c>
+      <c r="J443" t="s">
+        <v>17</v>
+      </c>
+      <c r="K443" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>289</v>
+      </c>
+      <c r="B444" t="s">
+        <v>293</v>
+      </c>
+      <c r="C444" t="s">
+        <v>294</v>
+      </c>
+      <c r="D444">
+        <v>3.141</v>
+      </c>
+      <c r="E444" t="s">
+        <v>22</v>
+      </c>
+      <c r="F444">
+        <v>0</v>
+      </c>
+      <c r="G444">
+        <v>100</v>
+      </c>
+      <c r="I444" t="s">
+        <v>16</v>
+      </c>
+      <c r="J444" t="s">
+        <v>17</v>
+      </c>
+      <c r="K444" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>289</v>
+      </c>
+      <c r="B445" t="s">
+        <v>295</v>
+      </c>
+      <c r="C445" t="s">
+        <v>296</v>
+      </c>
+      <c r="D445">
+        <v>3.12</v>
+      </c>
+      <c r="E445" t="s">
+        <v>22</v>
+      </c>
+      <c r="F445">
+        <v>0</v>
+      </c>
+      <c r="G445">
+        <v>100</v>
+      </c>
+      <c r="I445" t="s">
+        <v>16</v>
+      </c>
+      <c r="J445" t="s">
+        <v>17</v>
+      </c>
+      <c r="K445" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>289</v>
+      </c>
+      <c r="B446" t="s">
+        <v>297</v>
+      </c>
+      <c r="C446" t="s">
+        <v>115</v>
+      </c>
+      <c r="D446">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E446" t="s">
+        <v>22</v>
+      </c>
+      <c r="F446">
+        <v>0</v>
+      </c>
+      <c r="G446">
+        <v>100</v>
+      </c>
+      <c r="I446" t="s">
+        <v>16</v>
+      </c>
+      <c r="J446" t="s">
+        <v>17</v>
+      </c>
+      <c r="K446" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>289</v>
+      </c>
+      <c r="B447" t="s">
+        <v>298</v>
+      </c>
+      <c r="C447" t="s">
+        <v>299</v>
+      </c>
+      <c r="D447">
+        <v>3.004</v>
+      </c>
+      <c r="E447" t="s">
+        <v>22</v>
+      </c>
+      <c r="F447">
+        <v>0</v>
+      </c>
+      <c r="G447">
+        <v>100</v>
+      </c>
+      <c r="I447" t="s">
+        <v>16</v>
+      </c>
+      <c r="J447" t="s">
+        <v>17</v>
+      </c>
+      <c r="K447" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>289</v>
+      </c>
+      <c r="B448" t="s">
+        <v>300</v>
+      </c>
+      <c r="C448" t="s">
+        <v>102</v>
+      </c>
+      <c r="D448">
+        <v>0.114</v>
+      </c>
+      <c r="E448" t="s">
+        <v>22</v>
+      </c>
+      <c r="F448">
+        <v>0</v>
+      </c>
+      <c r="G448">
+        <v>100</v>
+      </c>
+      <c r="I448" t="s">
+        <v>16</v>
+      </c>
+      <c r="J448" t="s">
+        <v>17</v>
+      </c>
+      <c r="K448" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>301</v>
+      </c>
+      <c r="B449" t="s">
+        <v>302</v>
+      </c>
+      <c r="C449" t="s">
+        <v>303</v>
+      </c>
+      <c r="D449">
+        <v>3.05</v>
+      </c>
+      <c r="E449" t="s">
+        <v>50</v>
+      </c>
+      <c r="F449">
+        <v>11</v>
+      </c>
+      <c r="G449">
+        <v>100</v>
+      </c>
+      <c r="I449" t="s">
+        <v>16</v>
+      </c>
+      <c r="J449" t="s">
+        <v>17</v>
+      </c>
+      <c r="K449" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>301</v>
+      </c>
+      <c r="B450" t="s">
+        <v>304</v>
+      </c>
+      <c r="C450" t="s">
+        <v>305</v>
+      </c>
+      <c r="D450">
+        <v>3.0529999999999999</v>
+      </c>
+      <c r="E450" t="s">
+        <v>50</v>
+      </c>
+      <c r="F450">
+        <v>11</v>
+      </c>
+      <c r="G450">
+        <v>100</v>
+      </c>
+      <c r="I450" t="s">
+        <v>16</v>
+      </c>
+      <c r="J450" t="s">
+        <v>17</v>
+      </c>
+      <c r="K450" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>301</v>
+      </c>
+      <c r="B451" t="s">
+        <v>306</v>
+      </c>
+      <c r="C451" t="s">
+        <v>307</v>
+      </c>
+      <c r="D451">
+        <v>3.0459999999999998</v>
+      </c>
+      <c r="E451" t="s">
+        <v>50</v>
+      </c>
+      <c r="F451">
+        <v>11</v>
+      </c>
+      <c r="G451">
+        <v>100</v>
+      </c>
+      <c r="I451" t="s">
+        <v>16</v>
+      </c>
+      <c r="J451" t="s">
+        <v>17</v>
+      </c>
+      <c r="K451" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>301</v>
+      </c>
+      <c r="B452" t="s">
+        <v>308</v>
+      </c>
+      <c r="C452" t="s">
+        <v>309</v>
+      </c>
+      <c r="D452">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E452" t="s">
+        <v>50</v>
+      </c>
+      <c r="F452">
+        <v>11</v>
+      </c>
+      <c r="G452">
+        <v>100</v>
+      </c>
+      <c r="I452" t="s">
+        <v>16</v>
+      </c>
+      <c r="J452" t="s">
+        <v>17</v>
+      </c>
+      <c r="K452" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>301</v>
+      </c>
+      <c r="B453" t="s">
+        <v>310</v>
+      </c>
+      <c r="C453" t="s">
+        <v>311</v>
+      </c>
+      <c r="D453">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E453" t="s">
+        <v>50</v>
+      </c>
+      <c r="F453">
+        <v>11</v>
+      </c>
+      <c r="G453">
+        <v>100</v>
+      </c>
+      <c r="I453" t="s">
+        <v>16</v>
+      </c>
+      <c r="J453" t="s">
+        <v>17</v>
+      </c>
+      <c r="K453" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>301</v>
+      </c>
+      <c r="B454" t="s">
+        <v>312</v>
+      </c>
+      <c r="C454" t="s">
+        <v>313</v>
+      </c>
+      <c r="D454">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E454" t="s">
+        <v>50</v>
+      </c>
+      <c r="F454">
+        <v>11</v>
+      </c>
+      <c r="G454">
+        <v>100</v>
+      </c>
+      <c r="I454" t="s">
+        <v>16</v>
+      </c>
+      <c r="J454" t="s">
+        <v>17</v>
+      </c>
+      <c r="K454" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>301</v>
+      </c>
+      <c r="B455" t="s">
+        <v>314</v>
+      </c>
+      <c r="C455" t="s">
+        <v>315</v>
+      </c>
+      <c r="D455">
+        <v>3.0710000000000002</v>
+      </c>
+      <c r="E455" t="s">
+        <v>50</v>
+      </c>
+      <c r="F455">
+        <v>11</v>
+      </c>
+      <c r="G455">
+        <v>100</v>
+      </c>
+      <c r="I455" t="s">
+        <v>16</v>
+      </c>
+      <c r="J455" t="s">
+        <v>17</v>
+      </c>
+      <c r="K455" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>301</v>
+      </c>
+      <c r="B456" t="s">
+        <v>316</v>
+      </c>
+      <c r="C456" t="s">
+        <v>317</v>
+      </c>
+      <c r="D456">
+        <v>3.0489999999999999</v>
+      </c>
+      <c r="E456" t="s">
+        <v>50</v>
+      </c>
+      <c r="F456">
+        <v>11</v>
+      </c>
+      <c r="G456">
+        <v>100</v>
+      </c>
+      <c r="I456" t="s">
+        <v>16</v>
+      </c>
+      <c r="J456" t="s">
+        <v>17</v>
+      </c>
+      <c r="K456" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>301</v>
+      </c>
+      <c r="B457" t="s">
+        <v>318</v>
+      </c>
+      <c r="C457" t="s">
+        <v>102</v>
+      </c>
+      <c r="D457">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="E457" t="s">
+        <v>50</v>
+      </c>
+      <c r="F457">
+        <v>11</v>
+      </c>
+      <c r="G457">
+        <v>100</v>
+      </c>
+      <c r="I457" t="s">
+        <v>16</v>
+      </c>
+      <c r="J457" t="s">
+        <v>17</v>
+      </c>
+      <c r="K457" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>319</v>
+      </c>
+      <c r="B458" t="s">
+        <v>320</v>
+      </c>
+      <c r="C458" t="s">
+        <v>31</v>
+      </c>
+      <c r="D458">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E458" t="s">
+        <v>22</v>
+      </c>
+      <c r="F458">
+        <v>5</v>
+      </c>
+      <c r="G458">
+        <v>100</v>
+      </c>
+      <c r="I458" t="s">
+        <v>16</v>
+      </c>
+      <c r="J458" t="s">
+        <v>17</v>
+      </c>
+      <c r="K458" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>319</v>
+      </c>
+      <c r="B459" t="s">
+        <v>321</v>
+      </c>
+      <c r="C459" t="s">
+        <v>31</v>
+      </c>
+      <c r="D459">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E459" t="s">
+        <v>22</v>
+      </c>
+      <c r="F459">
+        <v>5</v>
+      </c>
+      <c r="G459">
+        <v>100</v>
+      </c>
+      <c r="I459" t="s">
+        <v>16</v>
+      </c>
+      <c r="J459" t="s">
+        <v>17</v>
+      </c>
+      <c r="K459" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>319</v>
+      </c>
+      <c r="B460" t="s">
+        <v>322</v>
+      </c>
+      <c r="C460" t="s">
+        <v>31</v>
+      </c>
+      <c r="D460">
+        <v>3.03</v>
+      </c>
+      <c r="E460" t="s">
+        <v>22</v>
+      </c>
+      <c r="F460">
+        <v>5</v>
+      </c>
+      <c r="G460">
+        <v>100</v>
+      </c>
+      <c r="I460" t="s">
+        <v>16</v>
+      </c>
+      <c r="J460" t="s">
+        <v>17</v>
+      </c>
+      <c r="K460" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>319</v>
+      </c>
+      <c r="B461" t="s">
+        <v>323</v>
+      </c>
+      <c r="C461" t="s">
+        <v>31</v>
+      </c>
+      <c r="D461">
+        <v>3.03</v>
+      </c>
+      <c r="E461" t="s">
+        <v>22</v>
+      </c>
+      <c r="F461">
+        <v>5</v>
+      </c>
+      <c r="G461">
+        <v>100</v>
+      </c>
+      <c r="I461" t="s">
+        <v>16</v>
+      </c>
+      <c r="J461" t="s">
+        <v>17</v>
+      </c>
+      <c r="K461" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>319</v>
+      </c>
+      <c r="B462" t="s">
+        <v>324</v>
+      </c>
+      <c r="C462" t="s">
+        <v>31</v>
+      </c>
+      <c r="D462">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="E462" t="s">
+        <v>22</v>
+      </c>
+      <c r="F462">
+        <v>5</v>
+      </c>
+      <c r="G462">
+        <v>100</v>
+      </c>
+      <c r="I462" t="s">
+        <v>16</v>
+      </c>
+      <c r="J462" t="s">
+        <v>17</v>
+      </c>
+      <c r="K462" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>319</v>
+      </c>
+      <c r="B463" t="s">
+        <v>325</v>
+      </c>
+      <c r="C463" t="s">
+        <v>31</v>
+      </c>
+      <c r="D463">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="E463" t="s">
+        <v>22</v>
+      </c>
+      <c r="F463">
+        <v>5</v>
+      </c>
+      <c r="G463">
+        <v>100</v>
+      </c>
+      <c r="I463" t="s">
+        <v>16</v>
+      </c>
+      <c r="J463" t="s">
+        <v>17</v>
+      </c>
+      <c r="K463" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>319</v>
+      </c>
+      <c r="B464" t="s">
+        <v>326</v>
+      </c>
+      <c r="C464" t="s">
+        <v>31</v>
+      </c>
+      <c r="D464">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="E464" t="s">
+        <v>22</v>
+      </c>
+      <c r="F464">
+        <v>5</v>
+      </c>
+      <c r="G464">
+        <v>100</v>
+      </c>
+      <c r="I464" t="s">
+        <v>16</v>
+      </c>
+      <c r="J464" t="s">
+        <v>17</v>
+      </c>
+      <c r="K464" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>327</v>
+      </c>
+      <c r="B465" t="s">
+        <v>328</v>
+      </c>
+      <c r="C465" t="s">
+        <v>31</v>
+      </c>
+      <c r="D465">
+        <v>4.0510000000000002</v>
+      </c>
+      <c r="E465" t="s">
+        <v>90</v>
+      </c>
+      <c r="F465">
+        <v>2</v>
+      </c>
+      <c r="G465">
+        <v>100</v>
+      </c>
+      <c r="I465" t="s">
+        <v>16</v>
+      </c>
+      <c r="J465" t="s">
+        <v>17</v>
+      </c>
+      <c r="K465" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>327</v>
+      </c>
+      <c r="B466" t="s">
+        <v>329</v>
+      </c>
+      <c r="C466" t="s">
+        <v>330</v>
+      </c>
+      <c r="D466">
+        <v>3.02</v>
+      </c>
+      <c r="E466" t="s">
+        <v>90</v>
+      </c>
+      <c r="F466">
+        <v>2</v>
+      </c>
+      <c r="G466">
+        <v>100</v>
+      </c>
+      <c r="I466" t="s">
+        <v>16</v>
+      </c>
+      <c r="J466" t="s">
+        <v>17</v>
+      </c>
+      <c r="K466" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>327</v>
+      </c>
+      <c r="B467" t="s">
+        <v>331</v>
+      </c>
+      <c r="C467" t="s">
+        <v>332</v>
+      </c>
+      <c r="D467">
+        <v>3.02</v>
+      </c>
+      <c r="E467" t="s">
+        <v>22</v>
+      </c>
+      <c r="F467">
+        <v>2</v>
+      </c>
+      <c r="G467">
+        <v>100</v>
+      </c>
+      <c r="I467" t="s">
+        <v>16</v>
+      </c>
+      <c r="J467" t="s">
+        <v>17</v>
+      </c>
+      <c r="K467" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>327</v>
+      </c>
+      <c r="B468" t="s">
+        <v>333</v>
+      </c>
+      <c r="C468" t="s">
+        <v>334</v>
+      </c>
+      <c r="D468">
+        <v>3.028</v>
+      </c>
+      <c r="E468" t="s">
+        <v>22</v>
+      </c>
+      <c r="F468">
+        <v>2</v>
+      </c>
+      <c r="G468">
+        <v>100</v>
+      </c>
+      <c r="I468" t="s">
+        <v>16</v>
+      </c>
+      <c r="J468" t="s">
+        <v>17</v>
+      </c>
+      <c r="K468" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>327</v>
+      </c>
+      <c r="B469" t="s">
+        <v>335</v>
+      </c>
+      <c r="C469" t="s">
+        <v>336</v>
+      </c>
+      <c r="D469">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="E469" t="s">
+        <v>22</v>
+      </c>
+      <c r="F469">
+        <v>2</v>
+      </c>
+      <c r="G469">
+        <v>100</v>
+      </c>
+      <c r="I469" t="s">
+        <v>16</v>
+      </c>
+      <c r="J469" t="s">
+        <v>17</v>
+      </c>
+      <c r="K469" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>327</v>
+      </c>
+      <c r="B470" t="s">
+        <v>337</v>
+      </c>
+      <c r="C470" t="s">
+        <v>338</v>
+      </c>
+      <c r="D470">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="E470" t="s">
+        <v>22</v>
+      </c>
+      <c r="F470">
+        <v>2</v>
+      </c>
+      <c r="G470">
+        <v>100</v>
+      </c>
+      <c r="I470" t="s">
+        <v>16</v>
+      </c>
+      <c r="J470" t="s">
+        <v>17</v>
+      </c>
+      <c r="K470" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>327</v>
+      </c>
+      <c r="B471" t="s">
+        <v>339</v>
+      </c>
+      <c r="C471" t="s">
+        <v>340</v>
+      </c>
+      <c r="D471">
+        <v>3.028</v>
+      </c>
+      <c r="E471" t="s">
+        <v>22</v>
+      </c>
+      <c r="F471">
+        <v>2</v>
+      </c>
+      <c r="G471">
+        <v>100</v>
+      </c>
+      <c r="I471" t="s">
+        <v>16</v>
+      </c>
+      <c r="J471" t="s">
+        <v>17</v>
+      </c>
+      <c r="K471" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>327</v>
+      </c>
+      <c r="B472" t="s">
+        <v>341</v>
+      </c>
+      <c r="C472" t="s">
+        <v>342</v>
+      </c>
+      <c r="D472">
+        <v>3.004</v>
+      </c>
+      <c r="E472" t="s">
+        <v>22</v>
+      </c>
+      <c r="F472">
+        <v>2</v>
+      </c>
+      <c r="G472">
+        <v>100</v>
+      </c>
+      <c r="I472" t="s">
+        <v>16</v>
+      </c>
+      <c r="J472" t="s">
+        <v>17</v>
+      </c>
+      <c r="K472" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>343</v>
+      </c>
+      <c r="B473" t="s">
+        <v>344</v>
+      </c>
+      <c r="C473" t="s">
+        <v>345</v>
+      </c>
+      <c r="D473">
+        <v>3.097</v>
+      </c>
+      <c r="E473" t="s">
+        <v>22</v>
+      </c>
+      <c r="F473">
+        <v>5</v>
+      </c>
+      <c r="G473">
+        <v>100</v>
+      </c>
+      <c r="I473" t="s">
+        <v>16</v>
+      </c>
+      <c r="J473" t="s">
+        <v>17</v>
+      </c>
+      <c r="K473" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>343</v>
+      </c>
+      <c r="B474" t="s">
+        <v>346</v>
+      </c>
+      <c r="C474" t="s">
+        <v>347</v>
+      </c>
+      <c r="D474">
+        <v>3.1179999999999999</v>
+      </c>
+      <c r="E474" t="s">
+        <v>22</v>
+      </c>
+      <c r="F474">
+        <v>5</v>
+      </c>
+      <c r="G474">
+        <v>100</v>
+      </c>
+      <c r="I474" t="s">
+        <v>16</v>
+      </c>
+      <c r="J474" t="s">
+        <v>17</v>
+      </c>
+      <c r="K474" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>343</v>
+      </c>
+      <c r="B475" t="s">
+        <v>348</v>
+      </c>
+      <c r="C475" t="s">
+        <v>349</v>
+      </c>
+      <c r="D475">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="E475" t="s">
+        <v>22</v>
+      </c>
+      <c r="F475">
+        <v>5</v>
+      </c>
+      <c r="G475">
+        <v>100</v>
+      </c>
+      <c r="I475" t="s">
+        <v>16</v>
+      </c>
+      <c r="J475" t="s">
+        <v>17</v>
+      </c>
+      <c r="K475" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>343</v>
+      </c>
+      <c r="B476" t="s">
+        <v>350</v>
+      </c>
+      <c r="C476" t="s">
+        <v>351</v>
+      </c>
+      <c r="D476">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="E476" t="s">
+        <v>22</v>
+      </c>
+      <c r="F476">
+        <v>5</v>
+      </c>
+      <c r="G476">
+        <v>100</v>
+      </c>
+      <c r="I476" t="s">
+        <v>16</v>
+      </c>
+      <c r="J476" t="s">
+        <v>17</v>
+      </c>
+      <c r="K476" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>343</v>
+      </c>
+      <c r="B477" t="s">
+        <v>352</v>
+      </c>
+      <c r="C477" t="s">
+        <v>353</v>
+      </c>
+      <c r="D477">
+        <v>3.141</v>
+      </c>
+      <c r="E477" t="s">
+        <v>22</v>
+      </c>
+      <c r="F477">
+        <v>5</v>
+      </c>
+      <c r="G477">
+        <v>100</v>
+      </c>
+      <c r="I477" t="s">
+        <v>16</v>
+      </c>
+      <c r="J477" t="s">
+        <v>17</v>
+      </c>
+      <c r="K477" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>343</v>
+      </c>
+      <c r="B478" t="s">
+        <v>354</v>
+      </c>
+      <c r="C478" t="s">
+        <v>355</v>
+      </c>
+      <c r="D478">
+        <v>2.6970000000000001</v>
+      </c>
+      <c r="E478" t="s">
+        <v>22</v>
+      </c>
+      <c r="F478">
+        <v>5</v>
+      </c>
+      <c r="G478">
+        <v>100</v>
+      </c>
+      <c r="I478" t="s">
+        <v>16</v>
+      </c>
+      <c r="J478" t="s">
+        <v>17</v>
+      </c>
+      <c r="K478" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>356</v>
+      </c>
+      <c r="B479" t="s">
+        <v>357</v>
+      </c>
+      <c r="C479" t="s">
+        <v>358</v>
+      </c>
+      <c r="D479">
+        <v>2.9940000000000002</v>
+      </c>
+      <c r="E479" t="s">
+        <v>14</v>
+      </c>
+      <c r="F479">
+        <v>6</v>
+      </c>
+      <c r="G479">
+        <v>100</v>
+      </c>
+      <c r="I479" t="s">
+        <v>16</v>
+      </c>
+      <c r="J479" t="s">
+        <v>17</v>
+      </c>
+      <c r="K479" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>356</v>
+      </c>
+      <c r="B480" t="s">
+        <v>359</v>
+      </c>
+      <c r="C480" t="s">
+        <v>360</v>
+      </c>
+      <c r="D480">
+        <v>2.992</v>
+      </c>
+      <c r="E480" t="s">
+        <v>14</v>
+      </c>
+      <c r="F480">
+        <v>6</v>
+      </c>
+      <c r="G480">
+        <v>100</v>
+      </c>
+      <c r="I480" t="s">
+        <v>16</v>
+      </c>
+      <c r="J480" t="s">
+        <v>17</v>
+      </c>
+      <c r="K480" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>356</v>
+      </c>
+      <c r="B481" t="s">
+        <v>361</v>
+      </c>
+      <c r="C481" t="s">
+        <v>362</v>
+      </c>
+      <c r="D481">
+        <v>2.996</v>
+      </c>
+      <c r="E481" t="s">
+        <v>14</v>
+      </c>
+      <c r="F481">
+        <v>6</v>
+      </c>
+      <c r="G481">
+        <v>100</v>
+      </c>
+      <c r="I481" t="s">
+        <v>16</v>
+      </c>
+      <c r="J481" t="s">
+        <v>17</v>
+      </c>
+      <c r="K481" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>356</v>
+      </c>
+      <c r="B482" t="s">
+        <v>363</v>
+      </c>
+      <c r="C482" t="s">
+        <v>364</v>
+      </c>
+      <c r="D482">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="E482" t="s">
+        <v>14</v>
+      </c>
+      <c r="F482">
+        <v>6</v>
+      </c>
+      <c r="G482">
+        <v>100</v>
+      </c>
+      <c r="I482" t="s">
+        <v>16</v>
+      </c>
+      <c r="J482" t="s">
+        <v>17</v>
+      </c>
+      <c r="K482" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>356</v>
+      </c>
+      <c r="B483" t="s">
+        <v>365</v>
+      </c>
+      <c r="C483" t="s">
+        <v>366</v>
+      </c>
+      <c r="D483">
+        <v>2.996</v>
+      </c>
+      <c r="E483" t="s">
+        <v>14</v>
+      </c>
+      <c r="F483">
+        <v>6</v>
+      </c>
+      <c r="G483">
+        <v>100</v>
+      </c>
+      <c r="I483" t="s">
+        <v>16</v>
+      </c>
+      <c r="J483" t="s">
+        <v>17</v>
+      </c>
+      <c r="K483" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>356</v>
+      </c>
+      <c r="B484" t="s">
+        <v>367</v>
+      </c>
+      <c r="C484" t="s">
+        <v>368</v>
+      </c>
+      <c r="D484">
+        <v>2.996</v>
+      </c>
+      <c r="E484" t="s">
+        <v>14</v>
+      </c>
+      <c r="F484">
+        <v>6</v>
+      </c>
+      <c r="G484">
+        <v>100</v>
+      </c>
+      <c r="I484" t="s">
+        <v>16</v>
+      </c>
+      <c r="J484" t="s">
+        <v>17</v>
+      </c>
+      <c r="K484" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>356</v>
+      </c>
+      <c r="B485" t="s">
+        <v>369</v>
+      </c>
+      <c r="C485" t="s">
+        <v>370</v>
+      </c>
+      <c r="D485">
+        <v>2.996</v>
+      </c>
+      <c r="E485" t="s">
+        <v>14</v>
+      </c>
+      <c r="F485">
+        <v>6</v>
+      </c>
+      <c r="G485">
+        <v>100</v>
+      </c>
+      <c r="I485" t="s">
+        <v>16</v>
+      </c>
+      <c r="J485" t="s">
+        <v>17</v>
+      </c>
+      <c r="K485" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>356</v>
+      </c>
+      <c r="B486" t="s">
+        <v>371</v>
+      </c>
+      <c r="C486" t="s">
+        <v>372</v>
+      </c>
+      <c r="D486">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="E486" t="s">
+        <v>14</v>
+      </c>
+      <c r="F486">
+        <v>6</v>
+      </c>
+      <c r="G486">
+        <v>100</v>
+      </c>
+      <c r="I486" t="s">
+        <v>16</v>
+      </c>
+      <c r="J486" t="s">
+        <v>17</v>
+      </c>
+      <c r="K486" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>356</v>
+      </c>
+      <c r="B487" t="s">
+        <v>373</v>
+      </c>
+      <c r="C487" t="s">
+        <v>102</v>
+      </c>
+      <c r="D487">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="E487" t="s">
+        <v>14</v>
+      </c>
+      <c r="F487">
+        <v>6</v>
+      </c>
+      <c r="G487">
+        <v>100</v>
+      </c>
+      <c r="I487" t="s">
+        <v>16</v>
+      </c>
+      <c r="J487" t="s">
+        <v>17</v>
+      </c>
+      <c r="K487" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>374</v>
+      </c>
+      <c r="B488" t="s">
+        <v>375</v>
+      </c>
+      <c r="C488" t="s">
+        <v>376</v>
+      </c>
+      <c r="D488">
+        <v>3.1080000000000001</v>
+      </c>
+      <c r="E488" t="s">
+        <v>50</v>
+      </c>
+      <c r="F488">
+        <v>7</v>
+      </c>
+      <c r="G488">
+        <v>100</v>
+      </c>
+      <c r="I488" t="s">
+        <v>16</v>
+      </c>
+      <c r="J488" t="s">
+        <v>17</v>
+      </c>
+      <c r="K488" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>374</v>
+      </c>
+      <c r="B489" t="s">
+        <v>377</v>
+      </c>
+      <c r="C489" t="s">
+        <v>378</v>
+      </c>
+      <c r="D489">
+        <v>3.1259999999999999</v>
+      </c>
+      <c r="E489" t="s">
+        <v>50</v>
+      </c>
+      <c r="F489">
+        <v>7</v>
+      </c>
+      <c r="G489">
+        <v>100</v>
+      </c>
+      <c r="I489" t="s">
+        <v>16</v>
+      </c>
+      <c r="J489" t="s">
+        <v>17</v>
+      </c>
+      <c r="K489" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>374</v>
+      </c>
+      <c r="B490" t="s">
+        <v>379</v>
+      </c>
+      <c r="C490" t="s">
+        <v>380</v>
+      </c>
+      <c r="D490">
+        <v>3.125</v>
+      </c>
+      <c r="E490" t="s">
+        <v>50</v>
+      </c>
+      <c r="F490">
+        <v>7</v>
+      </c>
+      <c r="G490">
+        <v>100</v>
+      </c>
+      <c r="I490" t="s">
+        <v>16</v>
+      </c>
+      <c r="J490" t="s">
+        <v>17</v>
+      </c>
+      <c r="K490" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>374</v>
+      </c>
+      <c r="B491" t="s">
+        <v>381</v>
+      </c>
+      <c r="C491" t="s">
+        <v>102</v>
+      </c>
+      <c r="D491">
+        <v>4.6340000000000003</v>
+      </c>
+      <c r="E491" t="s">
+        <v>50</v>
+      </c>
+      <c r="F491">
+        <v>7</v>
+      </c>
+      <c r="G491">
+        <v>100</v>
+      </c>
+      <c r="I491" t="s">
+        <v>16</v>
+      </c>
+      <c r="J491" t="s">
+        <v>17</v>
+      </c>
+      <c r="K491" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>382</v>
+      </c>
+      <c r="B492" t="s">
+        <v>383</v>
+      </c>
+      <c r="C492" t="s">
+        <v>384</v>
+      </c>
+      <c r="D492">
+        <v>3.016</v>
+      </c>
+      <c r="E492" t="s">
+        <v>22</v>
+      </c>
+      <c r="F492">
+        <v>8</v>
+      </c>
+      <c r="G492">
+        <v>100</v>
+      </c>
+      <c r="I492" t="s">
+        <v>16</v>
+      </c>
+      <c r="J492" t="s">
+        <v>17</v>
+      </c>
+      <c r="K492" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>382</v>
+      </c>
+      <c r="B493" t="s">
+        <v>385</v>
+      </c>
+      <c r="C493" t="s">
+        <v>386</v>
+      </c>
+      <c r="D493">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E493" t="s">
+        <v>22</v>
+      </c>
+      <c r="F493">
+        <v>8</v>
+      </c>
+      <c r="G493">
+        <v>100</v>
+      </c>
+      <c r="I493" t="s">
+        <v>16</v>
+      </c>
+      <c r="J493" t="s">
+        <v>17</v>
+      </c>
+      <c r="K493" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>382</v>
+      </c>
+      <c r="B494" t="s">
+        <v>387</v>
+      </c>
+      <c r="C494" t="s">
+        <v>388</v>
+      </c>
+      <c r="D494">
+        <v>3.024</v>
+      </c>
+      <c r="E494" t="s">
+        <v>22</v>
+      </c>
+      <c r="F494">
+        <v>8</v>
+      </c>
+      <c r="G494">
+        <v>100</v>
+      </c>
+      <c r="I494" t="s">
+        <v>16</v>
+      </c>
+      <c r="J494" t="s">
+        <v>17</v>
+      </c>
+      <c r="K494" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>382</v>
+      </c>
+      <c r="B495" t="s">
+        <v>389</v>
+      </c>
+      <c r="C495" t="s">
+        <v>390</v>
+      </c>
+      <c r="D495">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E495" t="s">
+        <v>22</v>
+      </c>
+      <c r="F495">
+        <v>8</v>
+      </c>
+      <c r="G495">
+        <v>100</v>
+      </c>
+      <c r="I495" t="s">
+        <v>16</v>
+      </c>
+      <c r="J495" t="s">
+        <v>17</v>
+      </c>
+      <c r="K495" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>382</v>
+      </c>
+      <c r="B496" t="s">
+        <v>391</v>
+      </c>
+      <c r="C496" t="s">
+        <v>392</v>
+      </c>
+      <c r="D496">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E496" t="s">
+        <v>22</v>
+      </c>
+      <c r="F496">
+        <v>8</v>
+      </c>
+      <c r="G496">
+        <v>100</v>
+      </c>
+      <c r="I496" t="s">
+        <v>16</v>
+      </c>
+      <c r="J496" t="s">
+        <v>17</v>
+      </c>
+      <c r="K496" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>382</v>
+      </c>
+      <c r="B497" t="s">
+        <v>393</v>
+      </c>
+      <c r="C497" t="s">
+        <v>394</v>
+      </c>
+      <c r="D497">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E497" t="s">
+        <v>22</v>
+      </c>
+      <c r="F497">
+        <v>8</v>
+      </c>
+      <c r="G497">
+        <v>100</v>
+      </c>
+      <c r="I497" t="s">
+        <v>16</v>
+      </c>
+      <c r="J497" t="s">
+        <v>17</v>
+      </c>
+      <c r="K497" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>382</v>
+      </c>
+      <c r="B498" t="s">
+        <v>395</v>
+      </c>
+      <c r="C498" t="s">
+        <v>102</v>
+      </c>
+      <c r="D498">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="E498" t="s">
+        <v>22</v>
+      </c>
+      <c r="F498">
+        <v>8</v>
+      </c>
+      <c r="G498">
+        <v>100</v>
+      </c>
+      <c r="I498" t="s">
+        <v>16</v>
+      </c>
+      <c r="J498" t="s">
+        <v>17</v>
+      </c>
+      <c r="K498" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>382</v>
+      </c>
+      <c r="B499" t="s">
+        <v>396</v>
+      </c>
+      <c r="C499" t="s">
+        <v>102</v>
+      </c>
+      <c r="D499">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="E499" t="s">
+        <v>22</v>
+      </c>
+      <c r="F499">
+        <v>8</v>
+      </c>
+      <c r="G499">
+        <v>100</v>
+      </c>
+      <c r="I499" t="s">
+        <v>16</v>
+      </c>
+      <c r="J499" t="s">
+        <v>17</v>
+      </c>
+      <c r="K499" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>397</v>
+      </c>
+      <c r="B500" t="s">
+        <v>398</v>
+      </c>
+      <c r="C500" t="s">
+        <v>399</v>
+      </c>
+      <c r="D500">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E500" t="s">
+        <v>22</v>
+      </c>
+      <c r="F500">
+        <v>1</v>
+      </c>
+      <c r="G500">
+        <v>100</v>
+      </c>
+      <c r="I500" t="s">
+        <v>16</v>
+      </c>
+      <c r="J500" t="s">
+        <v>17</v>
+      </c>
+      <c r="K500" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>397</v>
+      </c>
+      <c r="B501" t="s">
+        <v>400</v>
+      </c>
+      <c r="C501" t="s">
+        <v>401</v>
+      </c>
+      <c r="D501">
+        <v>2.8969999999999998</v>
+      </c>
+      <c r="E501" t="s">
+        <v>22</v>
+      </c>
+      <c r="F501">
+        <v>1</v>
+      </c>
+      <c r="G501">
+        <v>100</v>
+      </c>
+      <c r="I501" t="s">
+        <v>16</v>
+      </c>
+      <c r="J501" t="s">
+        <v>17</v>
+      </c>
+      <c r="K501" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>397</v>
+      </c>
+      <c r="B502" t="s">
+        <v>402</v>
+      </c>
+      <c r="C502" t="s">
+        <v>403</v>
+      </c>
+      <c r="D502">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="E502" t="s">
+        <v>22</v>
+      </c>
+      <c r="F502">
+        <v>1</v>
+      </c>
+      <c r="G502">
+        <v>100</v>
+      </c>
+      <c r="I502" t="s">
+        <v>16</v>
+      </c>
+      <c r="J502" t="s">
+        <v>17</v>
+      </c>
+      <c r="K502" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>404</v>
+      </c>
+      <c r="B503" t="s">
+        <v>405</v>
+      </c>
+      <c r="C503" t="s">
+        <v>31</v>
+      </c>
+      <c r="D503">
+        <v>3.036</v>
+      </c>
+      <c r="E503" t="s">
+        <v>22</v>
+      </c>
+      <c r="F503">
+        <v>0</v>
+      </c>
+      <c r="G503">
+        <v>100</v>
+      </c>
+      <c r="I503" t="s">
+        <v>16</v>
+      </c>
+      <c r="J503" t="s">
+        <v>17</v>
+      </c>
+      <c r="K503" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>404</v>
+      </c>
+      <c r="B504" t="s">
+        <v>406</v>
+      </c>
+      <c r="C504" t="s">
+        <v>31</v>
+      </c>
+      <c r="D504">
+        <v>3.01</v>
+      </c>
+      <c r="E504" t="s">
+        <v>22</v>
+      </c>
+      <c r="F504">
+        <v>0</v>
+      </c>
+      <c r="G504">
+        <v>100</v>
+      </c>
+      <c r="I504" t="s">
+        <v>16</v>
+      </c>
+      <c r="J504" t="s">
+        <v>17</v>
+      </c>
+      <c r="K504" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>404</v>
+      </c>
+      <c r="B505" t="s">
+        <v>407</v>
+      </c>
+      <c r="C505" t="s">
+        <v>31</v>
+      </c>
+      <c r="D505">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E505" t="s">
+        <v>22</v>
+      </c>
+      <c r="F505">
+        <v>0</v>
+      </c>
+      <c r="G505">
+        <v>100</v>
+      </c>
+      <c r="I505" t="s">
+        <v>16</v>
+      </c>
+      <c r="J505" t="s">
+        <v>17</v>
+      </c>
+      <c r="K505" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>404</v>
+      </c>
+      <c r="B506" t="s">
+        <v>408</v>
+      </c>
+      <c r="C506" t="s">
+        <v>31</v>
+      </c>
+      <c r="D506">
+        <v>3.0409999999999999</v>
+      </c>
+      <c r="E506" t="s">
+        <v>22</v>
+      </c>
+      <c r="F506">
+        <v>0</v>
+      </c>
+      <c r="G506">
+        <v>100</v>
+      </c>
+      <c r="I506" t="s">
+        <v>16</v>
+      </c>
+      <c r="J506" t="s">
+        <v>17</v>
+      </c>
+      <c r="K506" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>404</v>
+      </c>
+      <c r="B507" t="s">
+        <v>409</v>
+      </c>
+      <c r="C507" t="s">
+        <v>31</v>
+      </c>
+      <c r="D507">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E507" t="s">
+        <v>22</v>
+      </c>
+      <c r="F507">
+        <v>0</v>
+      </c>
+      <c r="G507">
+        <v>100</v>
+      </c>
+      <c r="I507" t="s">
+        <v>16</v>
+      </c>
+      <c r="J507" t="s">
+        <v>17</v>
+      </c>
+      <c r="K507" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>404</v>
+      </c>
+      <c r="B508" t="s">
+        <v>410</v>
+      </c>
+      <c r="C508" t="s">
+        <v>31</v>
+      </c>
+      <c r="D508">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E508" t="s">
+        <v>22</v>
+      </c>
+      <c r="F508">
+        <v>0</v>
+      </c>
+      <c r="G508">
+        <v>100</v>
+      </c>
+      <c r="I508" t="s">
+        <v>16</v>
+      </c>
+      <c r="J508" t="s">
+        <v>17</v>
+      </c>
+      <c r="K508" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>404</v>
+      </c>
+      <c r="B509" t="s">
+        <v>411</v>
+      </c>
+      <c r="C509" t="s">
+        <v>31</v>
+      </c>
+      <c r="D509">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E509" t="s">
+        <v>22</v>
+      </c>
+      <c r="F509">
+        <v>0</v>
+      </c>
+      <c r="G509">
+        <v>100</v>
+      </c>
+      <c r="I509" t="s">
+        <v>16</v>
+      </c>
+      <c r="J509" t="s">
+        <v>17</v>
+      </c>
+      <c r="K509" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>404</v>
+      </c>
+      <c r="B510" t="s">
+        <v>412</v>
+      </c>
+      <c r="C510" t="s">
+        <v>31</v>
+      </c>
+      <c r="D510">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="E510" t="s">
+        <v>22</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510">
+        <v>100</v>
+      </c>
+      <c r="I510" t="s">
+        <v>16</v>
+      </c>
+      <c r="J510" t="s">
+        <v>17</v>
+      </c>
+      <c r="K510" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>413</v>
+      </c>
+      <c r="B511" t="s">
+        <v>414</v>
+      </c>
+      <c r="C511" t="s">
+        <v>415</v>
+      </c>
+      <c r="D511">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E511" t="s">
+        <v>50</v>
+      </c>
+      <c r="F511">
+        <v>7</v>
+      </c>
+      <c r="G511">
+        <v>100</v>
+      </c>
+      <c r="I511" t="s">
+        <v>16</v>
+      </c>
+      <c r="J511" t="s">
+        <v>17</v>
+      </c>
+      <c r="K511" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>413</v>
+      </c>
+      <c r="B512" t="s">
+        <v>416</v>
+      </c>
+      <c r="C512" t="s">
+        <v>417</v>
+      </c>
+      <c r="D512">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E512" t="s">
+        <v>50</v>
+      </c>
+      <c r="F512">
+        <v>7</v>
+      </c>
+      <c r="G512">
+        <v>100</v>
+      </c>
+      <c r="I512" t="s">
+        <v>16</v>
+      </c>
+      <c r="J512" t="s">
+        <v>17</v>
+      </c>
+      <c r="K512" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>413</v>
+      </c>
+      <c r="B513" t="s">
+        <v>418</v>
+      </c>
+      <c r="C513" t="s">
+        <v>419</v>
+      </c>
+      <c r="D513">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E513" t="s">
+        <v>50</v>
+      </c>
+      <c r="F513">
+        <v>7</v>
+      </c>
+      <c r="G513">
+        <v>100</v>
+      </c>
+      <c r="I513" t="s">
+        <v>16</v>
+      </c>
+      <c r="J513" t="s">
+        <v>17</v>
+      </c>
+      <c r="K513" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>413</v>
+      </c>
+      <c r="B514" t="s">
+        <v>420</v>
+      </c>
+      <c r="C514" t="s">
+        <v>421</v>
+      </c>
+      <c r="D514">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E514" t="s">
+        <v>50</v>
+      </c>
+      <c r="F514">
+        <v>7</v>
+      </c>
+      <c r="G514">
+        <v>100</v>
+      </c>
+      <c r="I514" t="s">
+        <v>16</v>
+      </c>
+      <c r="J514" t="s">
+        <v>17</v>
+      </c>
+      <c r="K514" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>413</v>
+      </c>
+      <c r="B515" t="s">
+        <v>422</v>
+      </c>
+      <c r="C515" t="s">
+        <v>423</v>
+      </c>
+      <c r="D515">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E515" t="s">
+        <v>50</v>
+      </c>
+      <c r="F515">
+        <v>7</v>
+      </c>
+      <c r="G515">
+        <v>100</v>
+      </c>
+      <c r="I515" t="s">
+        <v>16</v>
+      </c>
+      <c r="J515" t="s">
+        <v>17</v>
+      </c>
+      <c r="K515" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>413</v>
+      </c>
+      <c r="B516" t="s">
+        <v>424</v>
+      </c>
+      <c r="C516" t="s">
+        <v>425</v>
+      </c>
+      <c r="D516">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E516" t="s">
+        <v>50</v>
+      </c>
+      <c r="F516">
+        <v>7</v>
+      </c>
+      <c r="G516">
+        <v>100</v>
+      </c>
+      <c r="I516" t="s">
+        <v>16</v>
+      </c>
+      <c r="J516" t="s">
+        <v>17</v>
+      </c>
+      <c r="K516" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>413</v>
+      </c>
+      <c r="B517" t="s">
+        <v>426</v>
+      </c>
+      <c r="C517" t="s">
+        <v>427</v>
+      </c>
+      <c r="D517">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E517" t="s">
+        <v>50</v>
+      </c>
+      <c r="F517">
+        <v>7</v>
+      </c>
+      <c r="G517">
+        <v>100</v>
+      </c>
+      <c r="I517" t="s">
+        <v>16</v>
+      </c>
+      <c r="J517" t="s">
+        <v>17</v>
+      </c>
+      <c r="K517" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>413</v>
+      </c>
+      <c r="B518" t="s">
+        <v>428</v>
+      </c>
+      <c r="C518" t="s">
+        <v>429</v>
+      </c>
+      <c r="D518">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E518" t="s">
+        <v>50</v>
+      </c>
+      <c r="F518">
+        <v>7</v>
+      </c>
+      <c r="G518">
+        <v>100</v>
+      </c>
+      <c r="I518" t="s">
+        <v>16</v>
+      </c>
+      <c r="J518" t="s">
+        <v>17</v>
+      </c>
+      <c r="K518" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>413</v>
+      </c>
+      <c r="B519" t="s">
+        <v>430</v>
+      </c>
+      <c r="C519" t="s">
+        <v>102</v>
+      </c>
+      <c r="D519">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="E519" t="s">
+        <v>50</v>
+      </c>
+      <c r="F519">
+        <v>7</v>
+      </c>
+      <c r="G519">
+        <v>100</v>
+      </c>
+      <c r="I519" t="s">
+        <v>16</v>
+      </c>
+      <c r="J519" t="s">
+        <v>17</v>
+      </c>
+      <c r="K519" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>431</v>
+      </c>
+      <c r="B520" t="s">
+        <v>432</v>
+      </c>
+      <c r="C520" t="s">
+        <v>433</v>
+      </c>
+      <c r="D520">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="E520" t="s">
+        <v>50</v>
+      </c>
+      <c r="F520">
+        <v>7</v>
+      </c>
+      <c r="G520">
+        <v>100</v>
+      </c>
+      <c r="I520" t="s">
+        <v>16</v>
+      </c>
+      <c r="J520" t="s">
+        <v>17</v>
+      </c>
+      <c r="K520" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>431</v>
+      </c>
+      <c r="B521" t="s">
+        <v>434</v>
+      </c>
+      <c r="C521" t="s">
+        <v>435</v>
+      </c>
+      <c r="D521">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="E521" t="s">
+        <v>50</v>
+      </c>
+      <c r="F521">
+        <v>7</v>
+      </c>
+      <c r="G521">
+        <v>100</v>
+      </c>
+      <c r="I521" t="s">
+        <v>16</v>
+      </c>
+      <c r="J521" t="s">
+        <v>17</v>
+      </c>
+      <c r="K521" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>431</v>
+      </c>
+      <c r="B522" t="s">
+        <v>436</v>
+      </c>
+      <c r="C522" t="s">
+        <v>437</v>
+      </c>
+      <c r="D522">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E522" t="s">
+        <v>50</v>
+      </c>
+      <c r="F522">
+        <v>7</v>
+      </c>
+      <c r="G522">
+        <v>100</v>
+      </c>
+      <c r="I522" t="s">
+        <v>16</v>
+      </c>
+      <c r="J522" t="s">
+        <v>17</v>
+      </c>
+      <c r="K522" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>431</v>
+      </c>
+      <c r="B523" t="s">
+        <v>438</v>
+      </c>
+      <c r="C523" t="s">
+        <v>439</v>
+      </c>
+      <c r="D523">
+        <v>3.012</v>
+      </c>
+      <c r="E523" t="s">
+        <v>50</v>
+      </c>
+      <c r="F523">
+        <v>7</v>
+      </c>
+      <c r="G523">
+        <v>100</v>
+      </c>
+      <c r="I523" t="s">
+        <v>16</v>
+      </c>
+      <c r="J523" t="s">
+        <v>17</v>
+      </c>
+      <c r="K523" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>431</v>
+      </c>
+      <c r="B524" t="s">
+        <v>440</v>
+      </c>
+      <c r="C524" t="s">
+        <v>441</v>
+      </c>
+      <c r="D524">
+        <v>3.012</v>
+      </c>
+      <c r="E524" t="s">
+        <v>50</v>
+      </c>
+      <c r="F524">
+        <v>7</v>
+      </c>
+      <c r="G524">
+        <v>100</v>
+      </c>
+      <c r="I524" t="s">
+        <v>16</v>
+      </c>
+      <c r="J524" t="s">
+        <v>17</v>
+      </c>
+      <c r="K524" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>431</v>
+      </c>
+      <c r="B525" t="s">
+        <v>442</v>
+      </c>
+      <c r="C525" t="s">
+        <v>443</v>
+      </c>
+      <c r="D525">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E525" t="s">
+        <v>50</v>
+      </c>
+      <c r="F525">
+        <v>7</v>
+      </c>
+      <c r="G525">
+        <v>100</v>
+      </c>
+      <c r="I525" t="s">
+        <v>16</v>
+      </c>
+      <c r="J525" t="s">
+        <v>17</v>
+      </c>
+      <c r="K525" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>431</v>
+      </c>
+      <c r="B526" t="s">
+        <v>444</v>
+      </c>
+      <c r="C526" t="s">
+        <v>445</v>
+      </c>
+      <c r="D526">
+        <v>3.0329999999999999</v>
+      </c>
+      <c r="E526" t="s">
+        <v>50</v>
+      </c>
+      <c r="F526">
+        <v>7</v>
+      </c>
+      <c r="G526">
+        <v>100</v>
+      </c>
+      <c r="I526" t="s">
+        <v>16</v>
+      </c>
+      <c r="J526" t="s">
+        <v>17</v>
+      </c>
+      <c r="K526" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>446</v>
+      </c>
+      <c r="B527" t="s">
+        <v>447</v>
+      </c>
+      <c r="C527" t="s">
+        <v>448</v>
+      </c>
+      <c r="D527">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E527" t="s">
+        <v>14</v>
+      </c>
+      <c r="F527">
+        <v>5</v>
+      </c>
+      <c r="G527">
+        <v>100</v>
+      </c>
+      <c r="I527" t="s">
+        <v>16</v>
+      </c>
+      <c r="J527" t="s">
+        <v>17</v>
+      </c>
+      <c r="K527" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>446</v>
+      </c>
+      <c r="B528" t="s">
+        <v>449</v>
+      </c>
+      <c r="C528" t="s">
+        <v>450</v>
+      </c>
+      <c r="D528">
+        <v>3.1269999999999998</v>
+      </c>
+      <c r="E528" t="s">
+        <v>14</v>
+      </c>
+      <c r="F528">
+        <v>5</v>
+      </c>
+      <c r="G528">
+        <v>100</v>
+      </c>
+      <c r="I528" t="s">
+        <v>16</v>
+      </c>
+      <c r="J528" t="s">
+        <v>17</v>
+      </c>
+      <c r="K528" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>446</v>
+      </c>
+      <c r="B529" t="s">
+        <v>451</v>
+      </c>
+      <c r="C529" t="s">
+        <v>452</v>
+      </c>
+      <c r="D529">
+        <v>3.089</v>
+      </c>
+      <c r="E529" t="s">
+        <v>14</v>
+      </c>
+      <c r="F529">
+        <v>5</v>
+      </c>
+      <c r="G529">
+        <v>100</v>
+      </c>
+      <c r="I529" t="s">
+        <v>16</v>
+      </c>
+      <c r="J529" t="s">
+        <v>17</v>
+      </c>
+      <c r="K529" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>446</v>
+      </c>
+      <c r="B530" t="s">
+        <v>453</v>
+      </c>
+      <c r="C530" t="s">
+        <v>454</v>
+      </c>
+      <c r="D530">
+        <v>3.0990000000000002</v>
+      </c>
+      <c r="E530" t="s">
+        <v>14</v>
+      </c>
+      <c r="F530">
+        <v>5</v>
+      </c>
+      <c r="G530">
+        <v>100</v>
+      </c>
+      <c r="I530" t="s">
+        <v>16</v>
+      </c>
+      <c r="J530" t="s">
+        <v>17</v>
+      </c>
+      <c r="K530" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>446</v>
+      </c>
+      <c r="B531" t="s">
+        <v>455</v>
+      </c>
+      <c r="C531" t="s">
+        <v>456</v>
+      </c>
+      <c r="D531">
+        <v>3.093</v>
+      </c>
+      <c r="E531" t="s">
+        <v>14</v>
+      </c>
+      <c r="F531">
+        <v>5</v>
+      </c>
+      <c r="G531">
+        <v>100</v>
+      </c>
+      <c r="I531" t="s">
+        <v>16</v>
+      </c>
+      <c r="J531" t="s">
+        <v>17</v>
+      </c>
+      <c r="K531" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>446</v>
+      </c>
+      <c r="B532" t="s">
+        <v>457</v>
+      </c>
+      <c r="C532" t="s">
+        <v>458</v>
+      </c>
+      <c r="D532">
+        <v>3.0870000000000002</v>
+      </c>
+      <c r="E532" t="s">
+        <v>14</v>
+      </c>
+      <c r="F532">
+        <v>5</v>
+      </c>
+      <c r="G532">
+        <v>100</v>
+      </c>
+      <c r="I532" t="s">
+        <v>16</v>
+      </c>
+      <c r="J532" t="s">
+        <v>17</v>
+      </c>
+      <c r="K532" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>446</v>
+      </c>
+      <c r="B533" t="s">
+        <v>459</v>
+      </c>
+      <c r="C533" t="s">
+        <v>460</v>
+      </c>
+      <c r="D533">
+        <v>3.089</v>
+      </c>
+      <c r="E533" t="s">
+        <v>14</v>
+      </c>
+      <c r="F533">
+        <v>5</v>
+      </c>
+      <c r="G533">
+        <v>100</v>
+      </c>
+      <c r="I533" t="s">
+        <v>16</v>
+      </c>
+      <c r="J533" t="s">
+        <v>17</v>
+      </c>
+      <c r="K533" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>446</v>
+      </c>
+      <c r="B534" t="s">
+        <v>461</v>
+      </c>
+      <c r="C534" t="s">
+        <v>462</v>
+      </c>
+      <c r="D534">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="E534" t="s">
+        <v>14</v>
+      </c>
+      <c r="F534">
+        <v>5</v>
+      </c>
+      <c r="G534">
+        <v>100</v>
+      </c>
+      <c r="I534" t="s">
+        <v>16</v>
+      </c>
+      <c r="J534" t="s">
+        <v>17</v>
+      </c>
+      <c r="K534" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>463</v>
+      </c>
+      <c r="B535" t="s">
+        <v>464</v>
+      </c>
+      <c r="C535" t="s">
+        <v>465</v>
+      </c>
+      <c r="D535">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="E535" t="s">
+        <v>50</v>
+      </c>
+      <c r="F535">
+        <v>7</v>
+      </c>
+      <c r="G535">
+        <v>100</v>
+      </c>
+      <c r="I535" t="s">
+        <v>16</v>
+      </c>
+      <c r="J535" t="s">
+        <v>17</v>
+      </c>
+      <c r="K535" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>463</v>
+      </c>
+      <c r="B536" t="s">
+        <v>466</v>
+      </c>
+      <c r="C536" t="s">
+        <v>467</v>
+      </c>
+      <c r="D536">
+        <v>3.048</v>
+      </c>
+      <c r="E536" t="s">
+        <v>50</v>
+      </c>
+      <c r="F536">
+        <v>7</v>
+      </c>
+      <c r="G536">
+        <v>100</v>
+      </c>
+      <c r="I536" t="s">
+        <v>16</v>
+      </c>
+      <c r="J536" t="s">
+        <v>17</v>
+      </c>
+      <c r="K536" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>463</v>
+      </c>
+      <c r="B537" t="s">
+        <v>468</v>
+      </c>
+      <c r="C537" t="s">
+        <v>469</v>
+      </c>
+      <c r="D537">
+        <v>3.0510000000000002</v>
+      </c>
+      <c r="E537" t="s">
+        <v>50</v>
+      </c>
+      <c r="F537">
+        <v>7</v>
+      </c>
+      <c r="G537">
+        <v>100</v>
+      </c>
+      <c r="I537" t="s">
+        <v>16</v>
+      </c>
+      <c r="J537" t="s">
+        <v>17</v>
+      </c>
+      <c r="K537" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>463</v>
+      </c>
+      <c r="B538" t="s">
+        <v>470</v>
+      </c>
+      <c r="C538" t="s">
+        <v>471</v>
+      </c>
+      <c r="D538">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E538" t="s">
+        <v>50</v>
+      </c>
+      <c r="F538">
+        <v>7</v>
+      </c>
+      <c r="G538">
+        <v>100</v>
+      </c>
+      <c r="I538" t="s">
+        <v>16</v>
+      </c>
+      <c r="J538" t="s">
+        <v>17</v>
+      </c>
+      <c r="K538" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>463</v>
+      </c>
+      <c r="B539" t="s">
+        <v>472</v>
+      </c>
+      <c r="C539" t="s">
+        <v>115</v>
+      </c>
+      <c r="D539">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="E539" t="s">
+        <v>50</v>
+      </c>
+      <c r="F539">
+        <v>7</v>
+      </c>
+      <c r="G539">
+        <v>100</v>
+      </c>
+      <c r="I539" t="s">
+        <v>16</v>
+      </c>
+      <c r="J539" t="s">
+        <v>17</v>
+      </c>
+      <c r="K539" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>473</v>
+      </c>
+      <c r="B540" t="s">
+        <v>474</v>
+      </c>
+      <c r="C540" t="s">
+        <v>31</v>
+      </c>
+      <c r="D540">
+        <v>2.984</v>
+      </c>
+      <c r="E540" t="s">
+        <v>22</v>
+      </c>
+      <c r="F540">
+        <v>0</v>
+      </c>
+      <c r="G540">
+        <v>100</v>
+      </c>
+      <c r="I540" t="s">
+        <v>16</v>
+      </c>
+      <c r="J540" t="s">
+        <v>17</v>
+      </c>
+      <c r="K540" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>473</v>
+      </c>
+      <c r="B541" t="s">
+        <v>475</v>
+      </c>
+      <c r="C541" t="s">
+        <v>31</v>
+      </c>
+      <c r="D541">
+        <v>2.9780000000000002</v>
+      </c>
+      <c r="E541" t="s">
+        <v>22</v>
+      </c>
+      <c r="F541">
+        <v>0</v>
+      </c>
+      <c r="G541">
+        <v>100</v>
+      </c>
+      <c r="I541" t="s">
+        <v>16</v>
+      </c>
+      <c r="J541" t="s">
+        <v>17</v>
+      </c>
+      <c r="K541" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>473</v>
+      </c>
+      <c r="B542" t="s">
+        <v>476</v>
+      </c>
+      <c r="C542" t="s">
+        <v>31</v>
+      </c>
+      <c r="D542">
+        <v>2.9740000000000002</v>
+      </c>
+      <c r="E542" t="s">
+        <v>22</v>
+      </c>
+      <c r="F542">
+        <v>0</v>
+      </c>
+      <c r="G542">
+        <v>100</v>
+      </c>
+      <c r="I542" t="s">
+        <v>16</v>
+      </c>
+      <c r="J542" t="s">
+        <v>17</v>
+      </c>
+      <c r="K542" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>473</v>
+      </c>
+      <c r="B543" t="s">
+        <v>477</v>
+      </c>
+      <c r="C543" t="s">
+        <v>31</v>
+      </c>
+      <c r="D543">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="E543" t="s">
+        <v>22</v>
+      </c>
+      <c r="F543">
+        <v>0</v>
+      </c>
+      <c r="G543">
+        <v>100</v>
+      </c>
+      <c r="I543" t="s">
+        <v>16</v>
+      </c>
+      <c r="J543" t="s">
+        <v>17</v>
+      </c>
+      <c r="K543" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>478</v>
+      </c>
+      <c r="B544" t="s">
+        <v>479</v>
+      </c>
+      <c r="C544" t="s">
+        <v>31</v>
+      </c>
+      <c r="D544">
+        <v>3.016</v>
+      </c>
+      <c r="E544" t="s">
+        <v>14</v>
+      </c>
+      <c r="F544">
+        <v>4</v>
+      </c>
+      <c r="G544">
+        <v>100</v>
+      </c>
+      <c r="I544" t="s">
+        <v>16</v>
+      </c>
+      <c r="J544" t="s">
+        <v>17</v>
+      </c>
+      <c r="K544" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>478</v>
+      </c>
+      <c r="B545" t="s">
+        <v>480</v>
+      </c>
+      <c r="C545" t="s">
+        <v>31</v>
+      </c>
+      <c r="D545">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E545" t="s">
+        <v>14</v>
+      </c>
+      <c r="F545">
+        <v>4</v>
+      </c>
+      <c r="G545">
+        <v>100</v>
+      </c>
+      <c r="I545" t="s">
+        <v>16</v>
+      </c>
+      <c r="J545" t="s">
+        <v>17</v>
+      </c>
+      <c r="K545" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>478</v>
+      </c>
+      <c r="B546" t="s">
+        <v>481</v>
+      </c>
+      <c r="C546" t="s">
+        <v>31</v>
+      </c>
+      <c r="D546">
+        <v>3.016</v>
+      </c>
+      <c r="E546" t="s">
+        <v>14</v>
+      </c>
+      <c r="F546">
+        <v>4</v>
+      </c>
+      <c r="G546">
+        <v>100</v>
+      </c>
+      <c r="I546" t="s">
+        <v>16</v>
+      </c>
+      <c r="J546" t="s">
+        <v>17</v>
+      </c>
+      <c r="K546" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>478</v>
+      </c>
+      <c r="B547" t="s">
+        <v>482</v>
+      </c>
+      <c r="C547" t="s">
+        <v>31</v>
+      </c>
+      <c r="D547">
+        <v>2.0779999999999998</v>
+      </c>
+      <c r="E547" t="s">
+        <v>14</v>
+      </c>
+      <c r="F547">
+        <v>4</v>
+      </c>
+      <c r="G547">
+        <v>100</v>
+      </c>
+      <c r="I547" t="s">
+        <v>16</v>
+      </c>
+      <c r="J547" t="s">
+        <v>17</v>
+      </c>
+      <c r="K547" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>483</v>
+      </c>
+      <c r="B548" t="s">
+        <v>484</v>
+      </c>
+      <c r="C548" t="s">
+        <v>485</v>
+      </c>
+      <c r="D548">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E548" t="s">
+        <v>14</v>
+      </c>
+      <c r="F548">
+        <v>6</v>
+      </c>
+      <c r="G548">
+        <v>100</v>
+      </c>
+      <c r="I548" t="s">
+        <v>16</v>
+      </c>
+      <c r="J548" t="s">
+        <v>17</v>
+      </c>
+      <c r="K548" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>483</v>
+      </c>
+      <c r="B549" t="s">
+        <v>486</v>
+      </c>
+      <c r="C549" t="s">
+        <v>487</v>
+      </c>
+      <c r="D549">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="E549" t="s">
+        <v>14</v>
+      </c>
+      <c r="F549">
+        <v>6</v>
+      </c>
+      <c r="G549">
+        <v>100</v>
+      </c>
+      <c r="I549" t="s">
+        <v>16</v>
+      </c>
+      <c r="J549" t="s">
+        <v>17</v>
+      </c>
+      <c r="K549" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>483</v>
+      </c>
+      <c r="B550" t="s">
+        <v>488</v>
+      </c>
+      <c r="C550" t="s">
+        <v>489</v>
+      </c>
+      <c r="D550">
+        <v>3.03</v>
+      </c>
+      <c r="E550" t="s">
+        <v>14</v>
+      </c>
+      <c r="F550">
+        <v>6</v>
+      </c>
+      <c r="G550">
+        <v>100</v>
+      </c>
+      <c r="I550" t="s">
+        <v>16</v>
+      </c>
+      <c r="J550" t="s">
+        <v>17</v>
+      </c>
+      <c r="K550" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>483</v>
+      </c>
+      <c r="B551" t="s">
+        <v>490</v>
+      </c>
+      <c r="C551" t="s">
+        <v>102</v>
+      </c>
+      <c r="D551">
+        <v>1.349</v>
+      </c>
+      <c r="E551" t="s">
+        <v>14</v>
+      </c>
+      <c r="F551">
+        <v>6</v>
+      </c>
+      <c r="G551">
+        <v>100</v>
+      </c>
+      <c r="I551" t="s">
+        <v>16</v>
+      </c>
+      <c r="J551" t="s">
+        <v>17</v>
+      </c>
+      <c r="K551" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>491</v>
+      </c>
+      <c r="B552" t="s">
+        <v>492</v>
+      </c>
+      <c r="C552" t="s">
+        <v>493</v>
+      </c>
+      <c r="D552">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E552" t="s">
+        <v>14</v>
+      </c>
+      <c r="F552">
+        <v>5</v>
+      </c>
+      <c r="G552">
+        <v>100</v>
+      </c>
+      <c r="I552" t="s">
+        <v>16</v>
+      </c>
+      <c r="J552" t="s">
+        <v>17</v>
+      </c>
+      <c r="K552" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>491</v>
+      </c>
+      <c r="B553" t="s">
+        <v>494</v>
+      </c>
+      <c r="C553" t="s">
+        <v>495</v>
+      </c>
+      <c r="D553">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E553" t="s">
+        <v>14</v>
+      </c>
+      <c r="F553">
+        <v>5</v>
+      </c>
+      <c r="G553">
+        <v>100</v>
+      </c>
+      <c r="I553" t="s">
+        <v>16</v>
+      </c>
+      <c r="J553" t="s">
+        <v>17</v>
+      </c>
+      <c r="K553" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>491</v>
+      </c>
+      <c r="B554" t="s">
+        <v>496</v>
+      </c>
+      <c r="C554" t="s">
+        <v>102</v>
+      </c>
+      <c r="D554">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="E554" t="s">
+        <v>14</v>
+      </c>
+      <c r="F554">
+        <v>5</v>
+      </c>
+      <c r="G554">
+        <v>100</v>
+      </c>
+      <c r="I554" t="s">
+        <v>16</v>
+      </c>
+      <c r="J554" t="s">
+        <v>17</v>
+      </c>
+      <c r="K554" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>497</v>
+      </c>
+      <c r="B555" t="s">
+        <v>498</v>
+      </c>
+      <c r="C555" t="s">
+        <v>115</v>
+      </c>
+      <c r="D555">
+        <v>3.024</v>
+      </c>
+      <c r="E555" t="s">
+        <v>22</v>
+      </c>
+      <c r="F555">
+        <v>4</v>
+      </c>
+      <c r="G555">
+        <v>100</v>
+      </c>
+      <c r="I555" t="s">
+        <v>16</v>
+      </c>
+      <c r="J555" t="s">
+        <v>17</v>
+      </c>
+      <c r="K555" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>497</v>
+      </c>
+      <c r="B556" t="s">
+        <v>499</v>
+      </c>
+      <c r="C556" t="s">
+        <v>500</v>
+      </c>
+      <c r="D556">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E556" t="s">
+        <v>22</v>
+      </c>
+      <c r="F556">
+        <v>4</v>
+      </c>
+      <c r="G556">
+        <v>100</v>
+      </c>
+      <c r="I556" t="s">
+        <v>16</v>
+      </c>
+      <c r="J556" t="s">
+        <v>17</v>
+      </c>
+      <c r="K556" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>497</v>
+      </c>
+      <c r="B557" t="s">
+        <v>501</v>
+      </c>
+      <c r="C557" t="s">
+        <v>102</v>
+      </c>
+      <c r="D557">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="E557" t="s">
+        <v>22</v>
+      </c>
+      <c r="F557">
+        <v>4</v>
+      </c>
+      <c r="G557">
+        <v>100</v>
+      </c>
+      <c r="I557" t="s">
+        <v>16</v>
+      </c>
+      <c r="J557" t="s">
+        <v>17</v>
+      </c>
+      <c r="K557" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>502</v>
+      </c>
+      <c r="B558" t="s">
+        <v>503</v>
+      </c>
+      <c r="C558" t="s">
+        <v>504</v>
+      </c>
+      <c r="D558">
+        <v>2.617</v>
+      </c>
+      <c r="E558" t="s">
+        <v>50</v>
+      </c>
+      <c r="J558" t="s">
+        <v>505</v>
+      </c>
+      <c r="K558" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>502</v>
+      </c>
+      <c r="B559" t="s">
+        <v>506</v>
+      </c>
+      <c r="C559" t="s">
+        <v>507</v>
+      </c>
+      <c r="D559">
+        <v>2.6970000000000001</v>
+      </c>
+      <c r="E559" t="s">
+        <v>50</v>
+      </c>
+      <c r="J559" t="s">
+        <v>505</v>
+      </c>
+      <c r="K559" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>502</v>
+      </c>
+      <c r="B560" t="s">
+        <v>508</v>
+      </c>
+      <c r="C560" t="s">
+        <v>509</v>
+      </c>
+      <c r="D560">
+        <v>2.6709999999999998</v>
+      </c>
+      <c r="E560" t="s">
+        <v>50</v>
+      </c>
+      <c r="J560" t="s">
+        <v>505</v>
+      </c>
+      <c r="K560" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>502</v>
+      </c>
+      <c r="B561" t="s">
+        <v>510</v>
+      </c>
+      <c r="C561" t="s">
+        <v>511</v>
+      </c>
+      <c r="D561">
+        <v>2.6680000000000001</v>
+      </c>
+      <c r="E561" t="s">
+        <v>50</v>
+      </c>
+      <c r="J561" t="s">
+        <v>505</v>
+      </c>
+      <c r="K561" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>502</v>
+      </c>
+      <c r="B562" t="s">
+        <v>512</v>
+      </c>
+      <c r="C562" t="s">
+        <v>513</v>
+      </c>
+      <c r="D562">
+        <v>2.6680000000000001</v>
+      </c>
+      <c r="E562" t="s">
+        <v>50</v>
+      </c>
+      <c r="J562" t="s">
+        <v>505</v>
+      </c>
+      <c r="K562" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>514</v>
+      </c>
+      <c r="B563" t="s">
+        <v>515</v>
+      </c>
+      <c r="C563" t="s">
+        <v>516</v>
+      </c>
+      <c r="D563">
+        <v>1.337</v>
+      </c>
+      <c r="E563" t="s">
+        <v>50</v>
+      </c>
+      <c r="J563" t="s">
+        <v>505</v>
+      </c>
+      <c r="K563" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>514</v>
+      </c>
+      <c r="B564" t="s">
+        <v>517</v>
+      </c>
+      <c r="C564" t="s">
+        <v>518</v>
+      </c>
+      <c r="D564">
+        <v>1.548</v>
+      </c>
+      <c r="E564" t="s">
+        <v>50</v>
+      </c>
+      <c r="J564" t="s">
+        <v>505</v>
+      </c>
+      <c r="K564" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>519</v>
+      </c>
+      <c r="B565" t="s">
+        <v>520</v>
+      </c>
+      <c r="C565" t="s">
+        <v>521</v>
+      </c>
+      <c r="D565">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="E565" t="s">
+        <v>22</v>
+      </c>
+      <c r="J565" t="s">
+        <v>505</v>
+      </c>
+      <c r="K565" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>519</v>
+      </c>
+      <c r="B566" t="s">
+        <v>522</v>
+      </c>
+      <c r="C566" t="s">
+        <v>523</v>
+      </c>
+      <c r="D566">
+        <v>2.5070000000000001</v>
+      </c>
+      <c r="E566" t="s">
+        <v>22</v>
+      </c>
+      <c r="J566" t="s">
+        <v>505</v>
+      </c>
+      <c r="K566" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>519</v>
+      </c>
+      <c r="B567" t="s">
+        <v>524</v>
+      </c>
+      <c r="C567" t="s">
+        <v>525</v>
+      </c>
+      <c r="D567">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="E567" t="s">
+        <v>22</v>
+      </c>
+      <c r="J567" t="s">
+        <v>505</v>
+      </c>
+      <c r="K567" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>519</v>
+      </c>
+      <c r="B568" t="s">
+        <v>526</v>
+      </c>
+      <c r="C568" t="s">
+        <v>527</v>
+      </c>
+      <c r="D568">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="E568" t="s">
+        <v>22</v>
+      </c>
+      <c r="J568" t="s">
+        <v>505</v>
+      </c>
+      <c r="K568" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>519</v>
+      </c>
+      <c r="B569" t="s">
+        <v>528</v>
+      </c>
+      <c r="C569" t="s">
+        <v>529</v>
+      </c>
+      <c r="D569">
+        <v>2.548</v>
+      </c>
+      <c r="E569" t="s">
+        <v>22</v>
+      </c>
+      <c r="J569" t="s">
+        <v>505</v>
+      </c>
+      <c r="K569" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>519</v>
+      </c>
+      <c r="B570" t="s">
+        <v>530</v>
+      </c>
+      <c r="C570" t="s">
+        <v>531</v>
+      </c>
+      <c r="D570">
+        <v>2.5150000000000001</v>
+      </c>
+      <c r="E570" t="s">
+        <v>22</v>
+      </c>
+      <c r="J570" t="s">
+        <v>505</v>
+      </c>
+      <c r="K570" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>519</v>
+      </c>
+      <c r="B571" t="s">
+        <v>532</v>
+      </c>
+      <c r="C571" t="s">
+        <v>533</v>
+      </c>
+      <c r="D571">
+        <v>2.5489999999999999</v>
+      </c>
+      <c r="E571" t="s">
+        <v>22</v>
+      </c>
+      <c r="J571" t="s">
+        <v>505</v>
+      </c>
+      <c r="K571" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>519</v>
+      </c>
+      <c r="B572" t="s">
+        <v>534</v>
+      </c>
+      <c r="C572" t="s">
+        <v>535</v>
+      </c>
+      <c r="D572">
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="E572" t="s">
+        <v>22</v>
+      </c>
+      <c r="J572" t="s">
+        <v>505</v>
+      </c>
+      <c r="K572" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>536</v>
+      </c>
+      <c r="B573" t="s">
+        <v>537</v>
+      </c>
+      <c r="C573" t="s">
+        <v>538</v>
+      </c>
+      <c r="D573">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E573" t="s">
+        <v>50</v>
+      </c>
+      <c r="J573" t="s">
+        <v>505</v>
+      </c>
+      <c r="K573" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>539</v>
+      </c>
+      <c r="B574" t="s">
+        <v>540</v>
+      </c>
+      <c r="C574" t="s">
+        <v>541</v>
+      </c>
+      <c r="D574">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="E574" t="s">
+        <v>50</v>
+      </c>
+      <c r="J574" t="s">
+        <v>505</v>
+      </c>
+      <c r="K574" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>539</v>
+      </c>
+      <c r="B575" t="s">
+        <v>542</v>
+      </c>
+      <c r="C575" t="s">
+        <v>543</v>
+      </c>
+      <c r="D575">
+        <v>2.1890000000000001</v>
+      </c>
+      <c r="E575" t="s">
+        <v>50</v>
+      </c>
+      <c r="J575" t="s">
+        <v>505</v>
+      </c>
+      <c r="K575" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>539</v>
+      </c>
+      <c r="B576" t="s">
+        <v>544</v>
+      </c>
+      <c r="C576" t="s">
+        <v>545</v>
+      </c>
+      <c r="D576">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="E576" t="s">
+        <v>50</v>
+      </c>
+      <c r="J576" t="s">
+        <v>505</v>
+      </c>
+      <c r="K576" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>539</v>
+      </c>
+      <c r="B577" t="s">
+        <v>546</v>
+      </c>
+      <c r="C577" t="s">
+        <v>547</v>
+      </c>
+      <c r="D577">
+        <v>4.343</v>
+      </c>
+      <c r="E577" t="s">
+        <v>50</v>
+      </c>
+      <c r="J577" t="s">
+        <v>505</v>
+      </c>
+      <c r="K577" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>539</v>
+      </c>
+      <c r="B578" t="s">
+        <v>548</v>
+      </c>
+      <c r="C578" t="s">
+        <v>549</v>
+      </c>
+      <c r="D578">
+        <v>2.1469999999999998</v>
+      </c>
+      <c r="E578" t="s">
+        <v>50</v>
+      </c>
+      <c r="J578" t="s">
+        <v>505</v>
+      </c>
+      <c r="K578" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>539</v>
+      </c>
+      <c r="B579" t="s">
+        <v>550</v>
+      </c>
+      <c r="C579" t="s">
+        <v>551</v>
+      </c>
+      <c r="D579">
+        <v>2.3490000000000002</v>
+      </c>
+      <c r="E579" t="s">
+        <v>50</v>
+      </c>
+      <c r="J579" t="s">
+        <v>505</v>
+      </c>
+      <c r="K579" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>539</v>
+      </c>
+      <c r="B580" t="s">
+        <v>552</v>
+      </c>
+      <c r="C580" t="s">
+        <v>553</v>
+      </c>
+      <c r="D580">
+        <v>2.2909999999999999</v>
+      </c>
+      <c r="E580" t="s">
+        <v>50</v>
+      </c>
+      <c r="J580" t="s">
+        <v>505</v>
+      </c>
+      <c r="K580" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>539</v>
+      </c>
+      <c r="B581" t="s">
+        <v>554</v>
+      </c>
+      <c r="C581" t="s">
+        <v>555</v>
+      </c>
+      <c r="D581">
+        <v>2.444</v>
+      </c>
+      <c r="E581" t="s">
+        <v>50</v>
+      </c>
+      <c r="J581" t="s">
+        <v>505</v>
+      </c>
+      <c r="K581" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>539</v>
+      </c>
+      <c r="B582" t="s">
+        <v>556</v>
+      </c>
+      <c r="C582" t="s">
+        <v>557</v>
+      </c>
+      <c r="D582">
+        <v>2.9380000000000002</v>
+      </c>
+      <c r="E582" t="s">
+        <v>50</v>
+      </c>
+      <c r="J582" t="s">
+        <v>505</v>
+      </c>
+      <c r="K582" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>539</v>
+      </c>
+      <c r="B583" t="s">
+        <v>558</v>
+      </c>
+      <c r="C583" t="s">
+        <v>549</v>
+      </c>
+      <c r="D583">
+        <v>2.15</v>
+      </c>
+      <c r="E583" t="s">
+        <v>50</v>
+      </c>
+      <c r="J583" t="s">
+        <v>505</v>
+      </c>
+      <c r="K583" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>559</v>
+      </c>
+      <c r="B584" t="s">
+        <v>560</v>
+      </c>
+      <c r="C584" t="s">
+        <v>561</v>
+      </c>
+      <c r="D584">
+        <v>2.39</v>
+      </c>
+      <c r="E584" t="s">
+        <v>50</v>
+      </c>
+      <c r="J584" t="s">
+        <v>505</v>
+      </c>
+      <c r="K584" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>559</v>
+      </c>
+      <c r="B585" t="s">
+        <v>562</v>
+      </c>
+      <c r="C585" t="s">
+        <v>563</v>
+      </c>
+      <c r="D585">
+        <v>2.008</v>
+      </c>
+      <c r="E585" t="s">
+        <v>50</v>
+      </c>
+      <c r="J585" t="s">
+        <v>505</v>
+      </c>
+      <c r="K585" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>559</v>
+      </c>
+      <c r="B586" t="s">
+        <v>564</v>
+      </c>
+      <c r="C586" t="s">
+        <v>565</v>
+      </c>
+      <c r="D586">
+        <v>2.028</v>
+      </c>
+      <c r="E586" t="s">
+        <v>50</v>
+      </c>
+      <c r="J586" t="s">
+        <v>505</v>
+      </c>
+      <c r="K586" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>559</v>
+      </c>
+      <c r="B587" t="s">
+        <v>566</v>
+      </c>
+      <c r="C587" t="s">
+        <v>567</v>
+      </c>
+      <c r="D587">
+        <v>1.6639999999999999</v>
+      </c>
+      <c r="E587" t="s">
+        <v>50</v>
+      </c>
+      <c r="J587" t="s">
+        <v>505</v>
+      </c>
+      <c r="K587" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>559</v>
+      </c>
+      <c r="B588" t="s">
+        <v>568</v>
+      </c>
+      <c r="C588" t="s">
+        <v>569</v>
+      </c>
+      <c r="D588">
+        <v>1.024</v>
+      </c>
+      <c r="E588" t="s">
+        <v>50</v>
+      </c>
+      <c r="J588" t="s">
+        <v>505</v>
+      </c>
+      <c r="K588" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>559</v>
+      </c>
+      <c r="B589" t="s">
+        <v>570</v>
+      </c>
+      <c r="C589" t="s">
+        <v>571</v>
+      </c>
+      <c r="D589">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="E589" t="s">
+        <v>50</v>
+      </c>
+      <c r="J589" t="s">
+        <v>505</v>
+      </c>
+      <c r="K589" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>559</v>
+      </c>
+      <c r="B590" t="s">
+        <v>572</v>
+      </c>
+      <c r="C590" t="s">
+        <v>573</v>
+      </c>
+      <c r="D590">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="E590" t="s">
+        <v>50</v>
+      </c>
+      <c r="J590" t="s">
+        <v>505</v>
+      </c>
+      <c r="K590" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>559</v>
+      </c>
+      <c r="B591" t="s">
+        <v>574</v>
+      </c>
+      <c r="C591" t="s">
+        <v>575</v>
+      </c>
+      <c r="D591">
+        <v>1.89</v>
+      </c>
+      <c r="E591" t="s">
+        <v>50</v>
+      </c>
+      <c r="J591" t="s">
+        <v>505</v>
+      </c>
+      <c r="K591" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>559</v>
+      </c>
+      <c r="B592" t="s">
+        <v>576</v>
+      </c>
+      <c r="C592" t="s">
+        <v>577</v>
+      </c>
+      <c r="D592">
+        <v>2.9</v>
+      </c>
+      <c r="E592" t="s">
+        <v>50</v>
+      </c>
+      <c r="J592" t="s">
+        <v>505</v>
+      </c>
+      <c r="K592" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>559</v>
+      </c>
+      <c r="B593" t="s">
+        <v>578</v>
+      </c>
+      <c r="C593" t="s">
+        <v>579</v>
+      </c>
+      <c r="D593">
+        <v>1.248</v>
+      </c>
+      <c r="E593" t="s">
+        <v>50</v>
+      </c>
+      <c r="J593" t="s">
+        <v>505</v>
+      </c>
+      <c r="K593" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>559</v>
+      </c>
+      <c r="B594" t="s">
+        <v>580</v>
+      </c>
+      <c r="C594" t="s">
+        <v>581</v>
+      </c>
+      <c r="D594">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="E594" t="s">
+        <v>50</v>
+      </c>
+      <c r="J594" t="s">
+        <v>505</v>
+      </c>
+      <c r="K594" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>582</v>
+      </c>
+      <c r="B595" t="s">
+        <v>583</v>
+      </c>
+      <c r="C595" t="s">
+        <v>584</v>
+      </c>
+      <c r="D595">
+        <v>2.1659999999999999</v>
+      </c>
+      <c r="E595" t="s">
+        <v>50</v>
+      </c>
+      <c r="J595" t="s">
+        <v>505</v>
+      </c>
+      <c r="K595" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>582</v>
+      </c>
+      <c r="B596" t="s">
+        <v>585</v>
+      </c>
+      <c r="C596" t="s">
+        <v>586</v>
+      </c>
+      <c r="D596">
+        <v>2.4159999999999999</v>
+      </c>
+      <c r="E596" t="s">
+        <v>50</v>
+      </c>
+      <c r="J596" t="s">
+        <v>505</v>
+      </c>
+      <c r="K596" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>582</v>
+      </c>
+      <c r="B597" t="s">
+        <v>587</v>
+      </c>
+      <c r="C597" t="s">
+        <v>588</v>
+      </c>
+      <c r="D597">
+        <v>2.863</v>
+      </c>
+      <c r="E597" t="s">
+        <v>50</v>
+      </c>
+      <c r="J597" t="s">
+        <v>505</v>
+      </c>
+      <c r="K597" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>589</v>
+      </c>
+      <c r="B598" t="s">
+        <v>590</v>
+      </c>
+      <c r="C598" t="s">
+        <v>591</v>
+      </c>
+      <c r="D598">
+        <v>1.27</v>
+      </c>
+      <c r="E598" t="s">
+        <v>50</v>
+      </c>
+      <c r="J598" t="s">
+        <v>505</v>
+      </c>
+      <c r="K598" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>592</v>
+      </c>
+      <c r="B599" t="s">
+        <v>609</v>
+      </c>
+      <c r="C599" t="s">
+        <v>593</v>
+      </c>
+      <c r="D599">
+        <v>0.96</v>
+      </c>
+      <c r="E599" t="s">
+        <v>50</v>
+      </c>
+      <c r="J599" t="s">
+        <v>505</v>
+      </c>
+      <c r="K599" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>592</v>
+      </c>
+      <c r="B600" t="s">
+        <v>610</v>
+      </c>
+      <c r="C600" t="s">
+        <v>594</v>
+      </c>
+      <c r="D600">
+        <v>1.8540000000000001</v>
+      </c>
+      <c r="E600" t="s">
+        <v>50</v>
+      </c>
+      <c r="J600" t="s">
+        <v>505</v>
+      </c>
+      <c r="K600" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>592</v>
+      </c>
+      <c r="B601" t="s">
+        <v>611</v>
+      </c>
+      <c r="C601" t="s">
+        <v>593</v>
+      </c>
+      <c r="D601">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="E601" t="s">
+        <v>50</v>
+      </c>
+      <c r="J601" t="s">
+        <v>505</v>
+      </c>
+      <c r="K601" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>595</v>
+      </c>
+      <c r="B602" t="s">
+        <v>596</v>
+      </c>
+      <c r="C602" t="s">
+        <v>597</v>
+      </c>
+      <c r="D602">
+        <v>1.0029999999999999</v>
+      </c>
+      <c r="E602" t="s">
+        <v>22</v>
+      </c>
+      <c r="J602" t="s">
+        <v>598</v>
+      </c>
+      <c r="K602" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>595</v>
+      </c>
+      <c r="B603" t="s">
+        <v>599</v>
+      </c>
+      <c r="C603" t="s">
+        <v>600</v>
+      </c>
+      <c r="D603">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="E603" t="s">
+        <v>22</v>
+      </c>
+      <c r="J603" t="s">
+        <v>598</v>
+      </c>
+      <c r="K603" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>595</v>
+      </c>
+      <c r="B604" t="s">
+        <v>601</v>
+      </c>
+      <c r="C604" t="s">
+        <v>602</v>
+      </c>
+      <c r="D604">
+        <v>1.883</v>
+      </c>
+      <c r="E604" t="s">
+        <v>22</v>
+      </c>
+      <c r="J604" t="s">
+        <v>598</v>
+      </c>
+      <c r="K604" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>603</v>
+      </c>
+      <c r="B605" t="s">
+        <v>604</v>
+      </c>
+      <c r="C605" t="s">
+        <v>605</v>
+      </c>
+      <c r="D605">
+        <v>1.034</v>
+      </c>
+      <c r="E605" t="s">
+        <v>22</v>
+      </c>
+      <c r="J605" t="s">
+        <v>598</v>
+      </c>
+      <c r="K605" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>603</v>
+      </c>
+      <c r="B606" t="s">
+        <v>606</v>
+      </c>
+      <c r="C606" t="s">
+        <v>607</v>
+      </c>
+      <c r="D606">
+        <v>2.0350000000000001</v>
+      </c>
+      <c r="E606" t="s">
+        <v>22</v>
+      </c>
+      <c r="J606" t="s">
+        <v>598</v>
+      </c>
+      <c r="K606" t="s">
+        <v>612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -2967,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2164"/>
+  <dimension ref="A1:K2163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -60427,38 +60427,73 @@
         <v>853</v>
       </c>
     </row>
+    <row r="1862" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1862" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1862" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1862" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1862" s="5">
+        <v>3.008</v>
+      </c>
+      <c r="E1862" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1862" s="5">
+        <v>6</v>
+      </c>
+      <c r="G1862" s="5">
+        <v>100</v>
+      </c>
+      <c r="H1862" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1862" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1862" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1862" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
     <row r="1863" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1863" s="5" t="s">
+      <c r="A1863" t="s">
         <v>11</v>
       </c>
-      <c r="B1863" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1863" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1863" s="5">
-        <v>3.008</v>
-      </c>
-      <c r="E1863" s="5" t="s">
+      <c r="B1863" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1863" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1863">
+        <v>3.0870000000000002</v>
+      </c>
+      <c r="E1863" t="s">
         <v>14</v>
       </c>
-      <c r="F1863" s="5">
+      <c r="F1863">
         <v>6</v>
       </c>
-      <c r="G1863" s="5">
-        <v>100</v>
-      </c>
-      <c r="H1863" s="5" t="s">
+      <c r="G1863">
+        <v>100</v>
+      </c>
+      <c r="H1863" t="s">
         <v>15</v>
       </c>
-      <c r="I1863" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1863" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1863" s="5" t="s">
+      <c r="I1863" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1863" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1863" t="s">
         <v>854</v>
       </c>
     </row>
@@ -60467,16 +60502,16 @@
         <v>11</v>
       </c>
       <c r="B1864" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1864" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1864">
-        <v>3.0870000000000002</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E1864" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F1864">
         <v>6</v>
@@ -60502,13 +60537,13 @@
         <v>11</v>
       </c>
       <c r="B1865" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C1865" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D1865">
-        <v>3.0419999999999998</v>
+        <v>3.0219999999999998</v>
       </c>
       <c r="E1865" t="s">
         <v>22</v>
@@ -60523,7 +60558,7 @@
         <v>15</v>
       </c>
       <c r="I1865" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J1865" t="s">
         <v>17</v>
@@ -60537,13 +60572,13 @@
         <v>11</v>
       </c>
       <c r="B1866" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C1866" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D1866">
-        <v>3.0219999999999998</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E1866" t="s">
         <v>22</v>
@@ -60572,13 +60607,13 @@
         <v>11</v>
       </c>
       <c r="B1867" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1867" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D1867">
-        <v>3.0419999999999998</v>
+        <v>3.04</v>
       </c>
       <c r="E1867" t="s">
         <v>22</v>
@@ -60593,7 +60628,7 @@
         <v>15</v>
       </c>
       <c r="I1867" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J1867" t="s">
         <v>17</v>
@@ -60607,13 +60642,13 @@
         <v>11</v>
       </c>
       <c r="B1868" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1868" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1868">
-        <v>3.04</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="E1868" t="s">
         <v>22</v>
@@ -60639,28 +60674,28 @@
     </row>
     <row r="1869" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1869" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B1869" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1869" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D1869">
-        <v>1.4450000000000001</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E1869" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F1869">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1869">
         <v>100</v>
       </c>
       <c r="H1869" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I1869" t="s">
         <v>16</v>
@@ -60677,13 +60712,13 @@
         <v>32</v>
       </c>
       <c r="B1870" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C1870" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D1870">
-        <v>3.0539999999999998</v>
+        <v>3.0310000000000001</v>
       </c>
       <c r="E1870" t="s">
         <v>14</v>
@@ -60712,13 +60747,13 @@
         <v>32</v>
       </c>
       <c r="B1871" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1871" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1871">
-        <v>3.0310000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="E1871" t="s">
         <v>14</v>
@@ -60744,28 +60779,28 @@
     </row>
     <row r="1872" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1872" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B1872" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C1872" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1872">
-        <v>3.05</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E1872" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F1872">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1872">
         <v>100</v>
       </c>
       <c r="H1872" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I1872" t="s">
         <v>16</v>
@@ -60782,13 +60817,13 @@
         <v>40</v>
       </c>
       <c r="B1873" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1873" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1873">
-        <v>3.0249999999999999</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E1873" t="s">
         <v>22</v>
@@ -60817,13 +60852,13 @@
         <v>40</v>
       </c>
       <c r="B1874" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1874" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1874">
-        <v>3.0350000000000001</v>
+        <v>3.02</v>
       </c>
       <c r="E1874" t="s">
         <v>22</v>
@@ -60852,13 +60887,13 @@
         <v>40</v>
       </c>
       <c r="B1875" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1875" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D1875">
-        <v>3.02</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="E1875" t="s">
         <v>22</v>
@@ -60884,31 +60919,31 @@
     </row>
     <row r="1876" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1876" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B1876" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1876" t="s">
         <v>31</v>
       </c>
       <c r="D1876">
-        <v>2.2200000000000002</v>
+        <v>1</v>
       </c>
       <c r="E1876" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F1876">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1876">
         <v>100</v>
       </c>
       <c r="H1876" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I1876" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J1876" t="s">
         <v>17</v>
@@ -60922,13 +60957,13 @@
         <v>49</v>
       </c>
       <c r="B1877" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1877" t="s">
         <v>31</v>
       </c>
       <c r="D1877">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="E1877" t="s">
         <v>50</v>
@@ -60940,7 +60975,7 @@
         <v>100</v>
       </c>
       <c r="H1877" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I1877" t="s">
         <v>52</v>
@@ -60957,13 +60992,13 @@
         <v>49</v>
       </c>
       <c r="B1878" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1878" t="s">
         <v>31</v>
       </c>
       <c r="D1878">
-        <v>3.1</v>
+        <v>3.093</v>
       </c>
       <c r="E1878" t="s">
         <v>50</v>
@@ -60975,7 +61010,7 @@
         <v>100</v>
       </c>
       <c r="H1878" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I1878" t="s">
         <v>52</v>
@@ -60992,13 +61027,13 @@
         <v>49</v>
       </c>
       <c r="B1879" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1879" t="s">
         <v>31</v>
       </c>
       <c r="D1879">
-        <v>3.093</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E1879" t="s">
         <v>50</v>
@@ -61027,13 +61062,13 @@
         <v>49</v>
       </c>
       <c r="B1880" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1880" t="s">
         <v>31</v>
       </c>
       <c r="D1880">
-        <v>3.0640000000000001</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="E1880" t="s">
         <v>50</v>
@@ -61059,31 +61094,31 @@
     </row>
     <row r="1881" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1881" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B1881" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1881" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D1881">
-        <v>0.88400000000000001</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E1881" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F1881">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1881">
         <v>100</v>
       </c>
       <c r="H1881" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I1881" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="J1881" t="s">
         <v>17</v>
@@ -61097,13 +61132,13 @@
         <v>59</v>
       </c>
       <c r="B1882" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C1882" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D1882">
-        <v>3.0230000000000001</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E1882" t="s">
         <v>14</v>
@@ -61118,7 +61153,7 @@
         <v>62</v>
       </c>
       <c r="I1882" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="J1882" t="s">
         <v>17</v>
@@ -61132,13 +61167,13 @@
         <v>59</v>
       </c>
       <c r="B1883" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1883" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1883">
-        <v>3.0390000000000001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E1883" t="s">
         <v>14</v>
@@ -61153,7 +61188,7 @@
         <v>62</v>
       </c>
       <c r="I1883" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="J1883" t="s">
         <v>17</v>
@@ -61167,13 +61202,13 @@
         <v>59</v>
       </c>
       <c r="B1884" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1884" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1884">
-        <v>3.0009999999999999</v>
+        <v>3.0369999999999999</v>
       </c>
       <c r="E1884" t="s">
         <v>14</v>
@@ -61202,13 +61237,13 @@
         <v>59</v>
       </c>
       <c r="B1885" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1885" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1885">
-        <v>3.0369999999999999</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E1885" t="s">
         <v>14</v>
@@ -61237,13 +61272,13 @@
         <v>59</v>
       </c>
       <c r="B1886" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1886" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="D1886">
-        <v>3.0009999999999999</v>
+        <v>2.2269999999999999</v>
       </c>
       <c r="E1886" t="s">
         <v>14</v>
@@ -61269,28 +61304,28 @@
     </row>
     <row r="1887" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1887" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B1887" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1887" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D1887">
-        <v>2.2269999999999999</v>
+        <v>3.036</v>
       </c>
       <c r="E1887" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F1887">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1887">
         <v>100</v>
       </c>
       <c r="H1887" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I1887" t="s">
         <v>16</v>
@@ -61307,13 +61342,13 @@
         <v>73</v>
       </c>
       <c r="B1888" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1888" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D1888">
-        <v>3.036</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E1888" t="s">
         <v>22</v>
@@ -61342,13 +61377,13 @@
         <v>73</v>
       </c>
       <c r="B1889" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1889" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1889">
-        <v>3.0259999999999998</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="E1889" t="s">
         <v>22</v>
@@ -61377,13 +61412,13 @@
         <v>73</v>
       </c>
       <c r="B1890" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1890" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D1890">
-        <v>3.0430000000000001</v>
+        <v>3.052</v>
       </c>
       <c r="E1890" t="s">
         <v>22</v>
@@ -61412,13 +61447,13 @@
         <v>73</v>
       </c>
       <c r="B1891" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1891" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1891">
-        <v>3.052</v>
+        <v>3.044</v>
       </c>
       <c r="E1891" t="s">
         <v>22</v>
@@ -61447,13 +61482,13 @@
         <v>73</v>
       </c>
       <c r="B1892" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1892" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1892">
-        <v>3.044</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="E1892" t="s">
         <v>22</v>
@@ -61479,19 +61514,19 @@
     </row>
     <row r="1893" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1893" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B1893" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C1893" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D1893">
-        <v>0.23799999999999999</v>
+        <v>3.024</v>
       </c>
       <c r="E1893" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="F1893">
         <v>1</v>
@@ -61517,13 +61552,13 @@
         <v>87</v>
       </c>
       <c r="B1894" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C1894" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1894">
-        <v>3.024</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E1894" t="s">
         <v>90</v>
@@ -61552,13 +61587,13 @@
         <v>87</v>
       </c>
       <c r="B1895" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1895" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1895">
-        <v>3.0230000000000001</v>
+        <v>3.008</v>
       </c>
       <c r="E1895" t="s">
         <v>90</v>
@@ -61587,13 +61622,13 @@
         <v>87</v>
       </c>
       <c r="B1896" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1896" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1896">
-        <v>3.008</v>
+        <v>3.0329999999999999</v>
       </c>
       <c r="E1896" t="s">
         <v>90</v>
@@ -61622,13 +61657,13 @@
         <v>87</v>
       </c>
       <c r="B1897" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C1897" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1897">
-        <v>3.0329999999999999</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E1897" t="s">
         <v>90</v>
@@ -61657,13 +61692,13 @@
         <v>87</v>
       </c>
       <c r="B1898" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C1898" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1898">
-        <v>3.0139999999999998</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E1898" t="s">
         <v>90</v>
@@ -61692,13 +61727,13 @@
         <v>87</v>
       </c>
       <c r="B1899" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C1899" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D1899">
-        <v>3.0070000000000001</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="E1899" t="s">
         <v>90</v>
@@ -61724,22 +61759,22 @@
     </row>
     <row r="1900" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1900" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B1900" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C1900" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D1900">
-        <v>0.78600000000000003</v>
+        <v>3.081</v>
       </c>
       <c r="E1900" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F1900">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1900">
         <v>100</v>
@@ -61762,13 +61797,13 @@
         <v>103</v>
       </c>
       <c r="B1901" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1901" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D1901">
-        <v>3.081</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E1901" t="s">
         <v>22</v>
@@ -61797,13 +61832,13 @@
         <v>103</v>
       </c>
       <c r="B1902" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1902" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1902">
-        <v>3.0470000000000002</v>
+        <v>3.048</v>
       </c>
       <c r="E1902" t="s">
         <v>22</v>
@@ -61832,13 +61867,13 @@
         <v>103</v>
       </c>
       <c r="B1903" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1903" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1903">
-        <v>3.048</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E1903" t="s">
         <v>22</v>
@@ -61867,13 +61902,13 @@
         <v>103</v>
       </c>
       <c r="B1904" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1904" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1904">
-        <v>3.0470000000000002</v>
+        <v>3.0459999999999998</v>
       </c>
       <c r="E1904" t="s">
         <v>22</v>
@@ -61902,13 +61937,13 @@
         <v>103</v>
       </c>
       <c r="B1905" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1905" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D1905">
-        <v>3.0459999999999998</v>
+        <v>1.855</v>
       </c>
       <c r="E1905" t="s">
         <v>22</v>
@@ -61934,22 +61969,22 @@
     </row>
     <row r="1906" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1906" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B1906" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C1906" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D1906">
-        <v>1.855</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E1906" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F1906">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1906">
         <v>100</v>
@@ -61972,13 +62007,13 @@
         <v>116</v>
       </c>
       <c r="B1907" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C1907" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D1907">
-        <v>3.0230000000000001</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E1907" t="s">
         <v>14</v>
@@ -62007,10 +62042,10 @@
         <v>116</v>
       </c>
       <c r="B1908" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C1908" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D1908">
         <v>3.0379999999999998</v>
@@ -62042,13 +62077,13 @@
         <v>116</v>
       </c>
       <c r="B1909" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1909" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D1909">
-        <v>3.0379999999999998</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E1909" t="s">
         <v>14</v>
@@ -62077,13 +62112,13 @@
         <v>116</v>
       </c>
       <c r="B1910" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C1910" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D1910">
-        <v>3.0390000000000001</v>
+        <v>3.02</v>
       </c>
       <c r="E1910" t="s">
         <v>14</v>
@@ -62112,13 +62147,13 @@
         <v>116</v>
       </c>
       <c r="B1911" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1911" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1911">
-        <v>3.02</v>
+        <v>2.3460000000000001</v>
       </c>
       <c r="E1911" t="s">
         <v>14</v>
@@ -62147,13 +62182,13 @@
         <v>116</v>
       </c>
       <c r="B1912" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C1912" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D1912">
-        <v>2.3460000000000001</v>
+        <v>3.0659999999999998</v>
       </c>
       <c r="E1912" t="s">
         <v>14</v>
@@ -62182,13 +62217,13 @@
         <v>116</v>
       </c>
       <c r="B1913" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1913" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D1913">
-        <v>3.0659999999999998</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="E1913" t="s">
         <v>14</v>
@@ -62217,13 +62252,13 @@
         <v>116</v>
       </c>
       <c r="B1914" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C1914" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D1914">
-        <v>3.0779999999999998</v>
+        <v>3.0739999999999998</v>
       </c>
       <c r="E1914" t="s">
         <v>14</v>
@@ -62252,13 +62287,13 @@
         <v>116</v>
       </c>
       <c r="B1915" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1915" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1915">
-        <v>3.0739999999999998</v>
+        <v>3.0939999999999999</v>
       </c>
       <c r="E1915" t="s">
         <v>14</v>
@@ -62287,13 +62322,13 @@
         <v>116</v>
       </c>
       <c r="B1916" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C1916" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D1916">
-        <v>3.0939999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="E1916" t="s">
         <v>14</v>
@@ -62319,16 +62354,16 @@
     </row>
     <row r="1917" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1917" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B1917" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C1917" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D1917">
-        <v>1.89</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="E1917" t="s">
         <v>14</v>
@@ -62357,13 +62392,13 @@
         <v>138</v>
       </c>
       <c r="B1918" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C1918" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D1918">
-        <v>3.0489999999999999</v>
+        <v>3.004</v>
       </c>
       <c r="E1918" t="s">
         <v>14</v>
@@ -62392,13 +62427,13 @@
         <v>138</v>
       </c>
       <c r="B1919" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1919" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1919">
-        <v>3.004</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E1919" t="s">
         <v>14</v>
@@ -62427,13 +62462,13 @@
         <v>138</v>
       </c>
       <c r="B1920" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C1920" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D1920">
-        <v>3.0009999999999999</v>
+        <v>3.004</v>
       </c>
       <c r="E1920" t="s">
         <v>14</v>
@@ -62462,13 +62497,13 @@
         <v>138</v>
       </c>
       <c r="B1921" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C1921" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D1921">
-        <v>3.004</v>
+        <v>3.0049999999999999</v>
       </c>
       <c r="E1921" t="s">
         <v>14</v>
@@ -62497,13 +62532,13 @@
         <v>138</v>
       </c>
       <c r="B1922" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C1922" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D1922">
-        <v>3.0049999999999999</v>
+        <v>3.004</v>
       </c>
       <c r="E1922" t="s">
         <v>14</v>
@@ -62532,19 +62567,19 @@
         <v>138</v>
       </c>
       <c r="B1923" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C1923" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="D1923">
-        <v>3.004</v>
+        <v>3.3980000000000001</v>
       </c>
       <c r="E1923" t="s">
         <v>14</v>
       </c>
       <c r="F1923">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1923">
         <v>100</v>
@@ -62564,19 +62599,19 @@
     </row>
     <row r="1924" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1924" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B1924" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C1924" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D1924">
-        <v>3.3980000000000001</v>
+        <v>3.056</v>
       </c>
       <c r="E1924" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="F1924">
         <v>12</v>
@@ -62602,13 +62637,13 @@
         <v>152</v>
       </c>
       <c r="B1925" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C1925" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D1925">
-        <v>3.056</v>
+        <v>3.0739999999999998</v>
       </c>
       <c r="E1925" t="s">
         <v>155</v>
@@ -62637,13 +62672,13 @@
         <v>152</v>
       </c>
       <c r="B1926" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C1926" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D1926">
-        <v>3.0739999999999998</v>
+        <v>2.8969999999999998</v>
       </c>
       <c r="E1926" t="s">
         <v>155</v>
@@ -62672,13 +62707,13 @@
         <v>152</v>
       </c>
       <c r="B1927" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C1927" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="D1927">
-        <v>2.8969999999999998</v>
+        <v>1.4790000000000001</v>
       </c>
       <c r="E1927" t="s">
         <v>155</v>
@@ -62707,13 +62742,13 @@
         <v>152</v>
       </c>
       <c r="B1928" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C1928" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="D1928">
-        <v>1.4790000000000001</v>
+        <v>3.0960000000000001</v>
       </c>
       <c r="E1928" t="s">
         <v>155</v>
@@ -62742,13 +62777,13 @@
         <v>152</v>
       </c>
       <c r="B1929" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C1929" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D1929">
-        <v>3.0960000000000001</v>
+        <v>3.0840000000000001</v>
       </c>
       <c r="E1929" t="s">
         <v>155</v>
@@ -62777,13 +62812,13 @@
         <v>152</v>
       </c>
       <c r="B1930" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C1930" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D1930">
-        <v>3.0840000000000001</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E1930" t="s">
         <v>155</v>
@@ -62812,10 +62847,10 @@
         <v>152</v>
       </c>
       <c r="B1931" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C1931" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D1931">
         <v>3.1030000000000002</v>
@@ -62847,13 +62882,13 @@
         <v>152</v>
       </c>
       <c r="B1932" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C1932" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D1932">
-        <v>3.1030000000000002</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E1932" t="s">
         <v>155</v>
@@ -62882,13 +62917,13 @@
         <v>152</v>
       </c>
       <c r="B1933" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1933" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D1933">
-        <v>3.0129999999999999</v>
+        <v>3.0529999999999999</v>
       </c>
       <c r="E1933" t="s">
         <v>155</v>
@@ -62917,13 +62952,13 @@
         <v>152</v>
       </c>
       <c r="B1934" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C1934" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D1934">
-        <v>3.0529999999999999</v>
+        <v>2.9830000000000001</v>
       </c>
       <c r="E1934" t="s">
         <v>155</v>
@@ -62952,13 +62987,13 @@
         <v>152</v>
       </c>
       <c r="B1935" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C1935" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D1935">
-        <v>2.9830000000000001</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E1935" t="s">
         <v>155</v>
@@ -62987,10 +63022,10 @@
         <v>152</v>
       </c>
       <c r="B1936" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C1936" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D1936">
         <v>3.1030000000000002</v>
@@ -63022,13 +63057,13 @@
         <v>152</v>
       </c>
       <c r="B1937" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C1937" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D1937">
-        <v>3.1030000000000002</v>
+        <v>3.036</v>
       </c>
       <c r="E1937" t="s">
         <v>155</v>
@@ -63057,13 +63092,13 @@
         <v>152</v>
       </c>
       <c r="B1938" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C1938" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="D1938">
-        <v>3.036</v>
+        <v>0.45</v>
       </c>
       <c r="E1938" t="s">
         <v>155</v>
@@ -63089,22 +63124,22 @@
     </row>
     <row r="1939" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1939" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B1939" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C1939" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="D1939">
-        <v>0.45</v>
+        <v>3.1230000000000002</v>
       </c>
       <c r="E1939" t="s">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="F1939">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1939">
         <v>100</v>
@@ -63127,13 +63162,13 @@
         <v>182</v>
       </c>
       <c r="B1940" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1940" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D1940">
-        <v>3.1230000000000002</v>
+        <v>3.1219999999999999</v>
       </c>
       <c r="E1940" t="s">
         <v>14</v>
@@ -63162,13 +63197,13 @@
         <v>182</v>
       </c>
       <c r="B1941" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C1941" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D1941">
-        <v>3.1219999999999999</v>
+        <v>3.145</v>
       </c>
       <c r="E1941" t="s">
         <v>14</v>
@@ -63197,16 +63232,16 @@
         <v>182</v>
       </c>
       <c r="B1942" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C1942" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D1942">
-        <v>3.145</v>
+        <v>3.14</v>
       </c>
       <c r="E1942" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F1942">
         <v>4</v>
@@ -63232,13 +63267,13 @@
         <v>182</v>
       </c>
       <c r="B1943" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C1943" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D1943">
-        <v>3.14</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="E1943" t="s">
         <v>22</v>
@@ -63267,13 +63302,13 @@
         <v>182</v>
       </c>
       <c r="B1944" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C1944" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D1944">
-        <v>3.0779999999999998</v>
+        <v>3.077</v>
       </c>
       <c r="E1944" t="s">
         <v>22</v>
@@ -63302,13 +63337,13 @@
         <v>182</v>
       </c>
       <c r="B1945" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C1945" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D1945">
-        <v>3.077</v>
+        <v>3.1579999999999999</v>
       </c>
       <c r="E1945" t="s">
         <v>22</v>
@@ -63337,13 +63372,13 @@
         <v>182</v>
       </c>
       <c r="B1946" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1946" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="D1946">
-        <v>3.1579999999999999</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="E1946" t="s">
         <v>22</v>
@@ -63369,22 +63404,22 @@
     </row>
     <row r="1947" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1947" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B1947" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C1947" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="D1947">
-        <v>1.8149999999999999</v>
+        <v>3.024</v>
       </c>
       <c r="E1947" t="s">
         <v>22</v>
       </c>
       <c r="F1947">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1947">
         <v>100</v>
@@ -63407,13 +63442,13 @@
         <v>198</v>
       </c>
       <c r="B1948" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C1948" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D1948">
-        <v>3.024</v>
+        <v>3.016</v>
       </c>
       <c r="E1948" t="s">
         <v>22</v>
@@ -63442,13 +63477,13 @@
         <v>198</v>
       </c>
       <c r="B1949" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1949" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D1949">
-        <v>3.016</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E1949" t="s">
         <v>22</v>
@@ -63477,10 +63512,10 @@
         <v>198</v>
       </c>
       <c r="B1950" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1950" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D1950">
         <v>3.0139999999999998</v>
@@ -63512,13 +63547,13 @@
         <v>198</v>
       </c>
       <c r="B1951" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1951" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D1951">
-        <v>3.0139999999999998</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E1951" t="s">
         <v>22</v>
@@ -63547,13 +63582,13 @@
         <v>198</v>
       </c>
       <c r="B1952" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C1952" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D1952">
-        <v>3.0150000000000001</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E1952" t="s">
         <v>22</v>
@@ -63582,13 +63617,13 @@
         <v>198</v>
       </c>
       <c r="B1953" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C1953" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1953">
-        <v>3.0070000000000001</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E1953" t="s">
         <v>22</v>
@@ -63617,13 +63652,13 @@
         <v>198</v>
       </c>
       <c r="B1954" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1954" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D1954">
-        <v>3.0129999999999999</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E1954" t="s">
         <v>22</v>
@@ -63652,13 +63687,13 @@
         <v>198</v>
       </c>
       <c r="B1955" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C1955" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D1955">
-        <v>3.0070000000000001</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E1955" t="s">
         <v>22</v>
@@ -63687,13 +63722,13 @@
         <v>198</v>
       </c>
       <c r="B1956" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C1956" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D1956">
-        <v>3.0419999999999998</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E1956" t="s">
         <v>22</v>
@@ -63722,13 +63757,13 @@
         <v>198</v>
       </c>
       <c r="B1957" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1957" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D1957">
-        <v>3.0129999999999999</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E1957" t="s">
         <v>22</v>
@@ -63757,13 +63792,13 @@
         <v>198</v>
       </c>
       <c r="B1958" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C1958" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="D1958">
-        <v>3.0070000000000001</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="E1958" t="s">
         <v>22</v>
@@ -63789,22 +63824,22 @@
     </row>
     <row r="1959" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1959" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B1959" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1959" t="s">
         <v>102</v>
       </c>
       <c r="D1959">
-        <v>0.67200000000000004</v>
+        <v>3.012</v>
       </c>
       <c r="E1959" t="s">
         <v>22</v>
       </c>
       <c r="F1959">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1959">
         <v>100</v>
@@ -63827,13 +63862,13 @@
         <v>222</v>
       </c>
       <c r="B1960" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1960" t="s">
         <v>102</v>
       </c>
       <c r="D1960">
-        <v>3.012</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E1960" t="s">
         <v>22</v>
@@ -63862,13 +63897,13 @@
         <v>222</v>
       </c>
       <c r="B1961" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1961" t="s">
         <v>102</v>
       </c>
       <c r="D1961">
-        <v>3.0350000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="E1961" t="s">
         <v>22</v>
@@ -63897,13 +63932,13 @@
         <v>222</v>
       </c>
       <c r="B1962" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1962" t="s">
         <v>102</v>
       </c>
       <c r="D1962">
-        <v>3.05</v>
+        <v>3.0190000000000001</v>
       </c>
       <c r="E1962" t="s">
         <v>22</v>
@@ -63932,13 +63967,13 @@
         <v>222</v>
       </c>
       <c r="B1963" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1963" t="s">
         <v>102</v>
       </c>
       <c r="D1963">
-        <v>3.0190000000000001</v>
+        <v>2.3879999999999999</v>
       </c>
       <c r="E1963" t="s">
         <v>22</v>
@@ -63964,22 +63999,22 @@
     </row>
     <row r="1964" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1964" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B1964" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C1964" t="s">
         <v>102</v>
       </c>
       <c r="D1964">
-        <v>2.3879999999999999</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E1964" t="s">
         <v>22</v>
       </c>
       <c r="F1964">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1964">
         <v>100</v>
@@ -64002,13 +64037,13 @@
         <v>228</v>
       </c>
       <c r="B1965" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1965" t="s">
         <v>102</v>
       </c>
       <c r="D1965">
-        <v>3.0249999999999999</v>
+        <v>3.024</v>
       </c>
       <c r="E1965" t="s">
         <v>22</v>
@@ -64037,13 +64072,13 @@
         <v>228</v>
       </c>
       <c r="B1966" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C1966" t="s">
         <v>102</v>
       </c>
       <c r="D1966">
-        <v>3.024</v>
+        <v>3.004</v>
       </c>
       <c r="E1966" t="s">
         <v>22</v>
@@ -64072,13 +64107,13 @@
         <v>228</v>
       </c>
       <c r="B1967" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C1967" t="s">
         <v>102</v>
       </c>
       <c r="D1967">
-        <v>3.004</v>
+        <v>3.032</v>
       </c>
       <c r="E1967" t="s">
         <v>22</v>
@@ -64107,7 +64142,7 @@
         <v>228</v>
       </c>
       <c r="B1968" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1968" t="s">
         <v>102</v>
@@ -64142,13 +64177,13 @@
         <v>228</v>
       </c>
       <c r="B1969" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1969" t="s">
         <v>102</v>
       </c>
       <c r="D1969">
-        <v>3.032</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E1969" t="s">
         <v>22</v>
@@ -64177,13 +64212,13 @@
         <v>228</v>
       </c>
       <c r="B1970" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1970" t="s">
         <v>102</v>
       </c>
       <c r="D1970">
-        <v>3.0270000000000001</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E1970" t="s">
         <v>22</v>
@@ -64212,13 +64247,13 @@
         <v>228</v>
       </c>
       <c r="B1971" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1971" t="s">
         <v>102</v>
       </c>
       <c r="D1971">
-        <v>3.0259999999999998</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="E1971" t="s">
         <v>22</v>
@@ -64247,13 +64282,13 @@
         <v>228</v>
       </c>
       <c r="B1972" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1972" t="s">
         <v>102</v>
       </c>
       <c r="D1972">
-        <v>3.0019999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="E1972" t="s">
         <v>22</v>
@@ -64279,19 +64314,19 @@
     </row>
     <row r="1973" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1973" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B1973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C1973" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="D1973">
-        <v>0.95</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E1973" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="F1973">
         <v>1</v>
@@ -64314,22 +64349,22 @@
     </row>
     <row r="1974" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1974" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1974" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C1974" t="s">
-        <v>31</v>
+        <v>241</v>
       </c>
       <c r="D1974">
-        <v>4.1950000000000003</v>
+        <v>3.077</v>
       </c>
       <c r="E1974" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F1974">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1974">
         <v>100</v>
@@ -64352,13 +64387,13 @@
         <v>239</v>
       </c>
       <c r="B1975" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C1975" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D1975">
-        <v>3.077</v>
+        <v>3.08</v>
       </c>
       <c r="E1975" t="s">
         <v>50</v>
@@ -64387,13 +64422,13 @@
         <v>239</v>
       </c>
       <c r="B1976" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C1976" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D1976">
-        <v>3.08</v>
+        <v>3.0369999999999999</v>
       </c>
       <c r="E1976" t="s">
         <v>50</v>
@@ -64422,13 +64457,13 @@
         <v>239</v>
       </c>
       <c r="B1977" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C1977" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D1977">
-        <v>3.0369999999999999</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E1977" t="s">
         <v>50</v>
@@ -64457,13 +64492,13 @@
         <v>239</v>
       </c>
       <c r="B1978" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C1978" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D1978">
-        <v>3.0390000000000001</v>
+        <v>3.0510000000000002</v>
       </c>
       <c r="E1978" t="s">
         <v>50</v>
@@ -64492,13 +64527,13 @@
         <v>239</v>
       </c>
       <c r="B1979" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C1979" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="D1979">
-        <v>3.0510000000000002</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="E1979" t="s">
         <v>50</v>
@@ -64524,19 +64559,19 @@
     </row>
     <row r="1980" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1980" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B1980" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C1980" t="s">
         <v>102</v>
       </c>
       <c r="D1980">
-        <v>0.79500000000000004</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="E1980" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F1980">
         <v>2</v>
@@ -64562,13 +64597,13 @@
         <v>251</v>
       </c>
       <c r="B1981" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C1981" t="s">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="D1981">
-        <v>1.7470000000000001</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E1981" t="s">
         <v>22</v>
@@ -64597,13 +64632,13 @@
         <v>251</v>
       </c>
       <c r="B1982" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C1982" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D1982">
-        <v>3.0139999999999998</v>
+        <v>3.101</v>
       </c>
       <c r="E1982" t="s">
         <v>22</v>
@@ -64632,13 +64667,13 @@
         <v>251</v>
       </c>
       <c r="B1983" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C1983" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D1983">
-        <v>3.101</v>
+        <v>3.109</v>
       </c>
       <c r="E1983" t="s">
         <v>22</v>
@@ -64667,13 +64702,13 @@
         <v>251</v>
       </c>
       <c r="B1984" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C1984" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D1984">
-        <v>3.109</v>
+        <v>3.0939999999999999</v>
       </c>
       <c r="E1984" t="s">
         <v>22</v>
@@ -64699,16 +64734,16 @@
     </row>
     <row r="1985" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1985" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B1985" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1985" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D1985">
-        <v>3.0939999999999999</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E1985" t="s">
         <v>22</v>
@@ -64737,13 +64772,13 @@
         <v>261</v>
       </c>
       <c r="B1986" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1986" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1986">
-        <v>3.0009999999999999</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E1986" t="s">
         <v>22</v>
@@ -64772,13 +64807,13 @@
         <v>261</v>
       </c>
       <c r="B1987" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C1987" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D1987">
-        <v>3.0059999999999998</v>
+        <v>3.0169999999999999</v>
       </c>
       <c r="E1987" t="s">
         <v>22</v>
@@ -64807,13 +64842,13 @@
         <v>261</v>
       </c>
       <c r="B1988" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1988" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D1988">
-        <v>3.0169999999999999</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="E1988" t="s">
         <v>22</v>
@@ -64842,13 +64877,13 @@
         <v>261</v>
       </c>
       <c r="B1989" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C1989" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D1989">
-        <v>3.0019999999999998</v>
+        <v>3.0289999999999999</v>
       </c>
       <c r="E1989" t="s">
         <v>22</v>
@@ -64877,13 +64912,13 @@
         <v>261</v>
       </c>
       <c r="B1990" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C1990" t="s">
-        <v>271</v>
+        <v>102</v>
       </c>
       <c r="D1990">
-        <v>3.0289999999999999</v>
+        <v>1.8340000000000001</v>
       </c>
       <c r="E1990" t="s">
         <v>22</v>
@@ -64909,22 +64944,22 @@
     </row>
     <row r="1991" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1991" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B1991" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C1991" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="D1991">
-        <v>1.8340000000000001</v>
+        <v>3.032</v>
       </c>
       <c r="E1991" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F1991">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1991">
         <v>100</v>
@@ -64947,13 +64982,13 @@
         <v>273</v>
       </c>
       <c r="B1992" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C1992" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D1992">
-        <v>3.032</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E1992" t="s">
         <v>14</v>
@@ -64982,13 +65017,13 @@
         <v>273</v>
       </c>
       <c r="B1993" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C1993" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D1993">
-        <v>3.0009999999999999</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="E1993" t="s">
         <v>14</v>
@@ -65017,10 +65052,10 @@
         <v>273</v>
       </c>
       <c r="B1994" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C1994" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D1994">
         <v>3.0430000000000001</v>
@@ -65052,13 +65087,13 @@
         <v>273</v>
       </c>
       <c r="B1995" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C1995" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D1995">
-        <v>3.0430000000000001</v>
+        <v>3.044</v>
       </c>
       <c r="E1995" t="s">
         <v>14</v>
@@ -65087,13 +65122,13 @@
         <v>273</v>
       </c>
       <c r="B1996" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C1996" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D1996">
-        <v>3.044</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E1996" t="s">
         <v>14</v>
@@ -65122,13 +65157,13 @@
         <v>273</v>
       </c>
       <c r="B1997" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C1997" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D1997">
-        <v>3.0419999999999998</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E1997" t="s">
         <v>14</v>
@@ -65157,13 +65192,13 @@
         <v>273</v>
       </c>
       <c r="B1998" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C1998" t="s">
-        <v>287</v>
+        <v>102</v>
       </c>
       <c r="D1998">
-        <v>3.0390000000000001</v>
+        <v>1.6679999999999999</v>
       </c>
       <c r="E1998" t="s">
         <v>14</v>
@@ -65189,22 +65224,22 @@
     </row>
     <row r="1999" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1999" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B1999" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C1999" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D1999">
-        <v>1.6679999999999999</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E1999" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F1999">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1999">
         <v>100</v>
@@ -65227,13 +65262,13 @@
         <v>289</v>
       </c>
       <c r="B2000" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C2000" t="s">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c r="D2000">
-        <v>3.0539999999999998</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E2000" t="s">
         <v>22</v>
@@ -65262,13 +65297,13 @@
         <v>289</v>
       </c>
       <c r="B2001" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C2001" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D2001">
-        <v>3.0550000000000002</v>
+        <v>3.141</v>
       </c>
       <c r="E2001" t="s">
         <v>22</v>
@@ -65297,13 +65332,13 @@
         <v>289</v>
       </c>
       <c r="B2002" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C2002" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D2002">
-        <v>3.141</v>
+        <v>3.12</v>
       </c>
       <c r="E2002" t="s">
         <v>22</v>
@@ -65332,13 +65367,13 @@
         <v>289</v>
       </c>
       <c r="B2003" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C2003" t="s">
-        <v>296</v>
+        <v>115</v>
       </c>
       <c r="D2003">
-        <v>3.12</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E2003" t="s">
         <v>22</v>
@@ -65367,13 +65402,13 @@
         <v>289</v>
       </c>
       <c r="B2004" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C2004" t="s">
-        <v>115</v>
+        <v>299</v>
       </c>
       <c r="D2004">
-        <v>3.0640000000000001</v>
+        <v>3.004</v>
       </c>
       <c r="E2004" t="s">
         <v>22</v>
@@ -65402,13 +65437,13 @@
         <v>289</v>
       </c>
       <c r="B2005" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C2005" t="s">
-        <v>299</v>
+        <v>102</v>
       </c>
       <c r="D2005">
-        <v>3.004</v>
+        <v>0.114</v>
       </c>
       <c r="E2005" t="s">
         <v>22</v>
@@ -65434,22 +65469,22 @@
     </row>
     <row r="2006" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2006" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B2006" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C2006" t="s">
-        <v>102</v>
+        <v>303</v>
       </c>
       <c r="D2006">
-        <v>0.114</v>
+        <v>3.05</v>
       </c>
       <c r="E2006" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F2006">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G2006">
         <v>100</v>
@@ -65472,13 +65507,13 @@
         <v>301</v>
       </c>
       <c r="B2007" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C2007" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D2007">
-        <v>3.05</v>
+        <v>3.0529999999999999</v>
       </c>
       <c r="E2007" t="s">
         <v>50</v>
@@ -65507,13 +65542,13 @@
         <v>301</v>
       </c>
       <c r="B2008" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C2008" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D2008">
-        <v>3.0529999999999999</v>
+        <v>3.0459999999999998</v>
       </c>
       <c r="E2008" t="s">
         <v>50</v>
@@ -65542,13 +65577,13 @@
         <v>301</v>
       </c>
       <c r="B2009" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C2009" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D2009">
-        <v>3.0459999999999998</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E2009" t="s">
         <v>50</v>
@@ -65577,13 +65612,13 @@
         <v>301</v>
       </c>
       <c r="B2010" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C2010" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D2010">
-        <v>3.0539999999999998</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E2010" t="s">
         <v>50</v>
@@ -65612,13 +65647,13 @@
         <v>301</v>
       </c>
       <c r="B2011" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C2011" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D2011">
-        <v>3.0550000000000002</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E2011" t="s">
         <v>50</v>
@@ -65647,13 +65682,13 @@
         <v>301</v>
       </c>
       <c r="B2012" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C2012" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D2012">
-        <v>3.0640000000000001</v>
+        <v>3.0710000000000002</v>
       </c>
       <c r="E2012" t="s">
         <v>50</v>
@@ -65682,13 +65717,13 @@
         <v>301</v>
       </c>
       <c r="B2013" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C2013" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D2013">
-        <v>3.0710000000000002</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="E2013" t="s">
         <v>50</v>
@@ -65717,13 +65752,13 @@
         <v>301</v>
       </c>
       <c r="B2014" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C2014" t="s">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="D2014">
-        <v>3.0489999999999999</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="E2014" t="s">
         <v>50</v>
@@ -65749,22 +65784,22 @@
     </row>
     <row r="2015" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2015" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B2015" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C2015" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="D2015">
-        <v>0.36199999999999999</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E2015" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F2015">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2015">
         <v>100</v>
@@ -65787,13 +65822,13 @@
         <v>319</v>
       </c>
       <c r="B2016" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C2016" t="s">
         <v>31</v>
       </c>
       <c r="D2016">
-        <v>3.0379999999999998</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E2016" t="s">
         <v>22</v>
@@ -65822,13 +65857,13 @@
         <v>319</v>
       </c>
       <c r="B2017" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C2017" t="s">
         <v>31</v>
       </c>
       <c r="D2017">
-        <v>3.0249999999999999</v>
+        <v>3.03</v>
       </c>
       <c r="E2017" t="s">
         <v>22</v>
@@ -65857,7 +65892,7 @@
         <v>319</v>
       </c>
       <c r="B2018" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C2018" t="s">
         <v>31</v>
@@ -65892,13 +65927,13 @@
         <v>319</v>
       </c>
       <c r="B2019" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C2019" t="s">
         <v>31</v>
       </c>
       <c r="D2019">
-        <v>3.03</v>
+        <v>3.0049999999999999</v>
       </c>
       <c r="E2019" t="s">
         <v>22</v>
@@ -65927,13 +65962,13 @@
         <v>319</v>
       </c>
       <c r="B2020" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C2020" t="s">
         <v>31</v>
       </c>
       <c r="D2020">
-        <v>3.0049999999999999</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="E2020" t="s">
         <v>22</v>
@@ -65962,13 +65997,13 @@
         <v>319</v>
       </c>
       <c r="B2021" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C2021" t="s">
         <v>31</v>
       </c>
       <c r="D2021">
-        <v>3.0110000000000001</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="E2021" t="s">
         <v>22</v>
@@ -65994,22 +66029,22 @@
     </row>
     <row r="2022" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2022" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B2022" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C2022" t="s">
         <v>31</v>
       </c>
       <c r="D2022">
-        <v>1.0109999999999999</v>
+        <v>4.0510000000000002</v>
       </c>
       <c r="E2022" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="F2022">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2022">
         <v>100</v>
@@ -66032,13 +66067,13 @@
         <v>327</v>
       </c>
       <c r="B2023" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C2023" t="s">
-        <v>31</v>
+        <v>330</v>
       </c>
       <c r="D2023">
-        <v>4.0510000000000002</v>
+        <v>3.02</v>
       </c>
       <c r="E2023" t="s">
         <v>90</v>
@@ -66067,16 +66102,16 @@
         <v>327</v>
       </c>
       <c r="B2024" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C2024" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D2024">
         <v>3.02</v>
       </c>
       <c r="E2024" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F2024">
         <v>2</v>
@@ -66102,13 +66137,13 @@
         <v>327</v>
       </c>
       <c r="B2025" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C2025" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D2025">
-        <v>3.02</v>
+        <v>3.028</v>
       </c>
       <c r="E2025" t="s">
         <v>22</v>
@@ -66137,13 +66172,13 @@
         <v>327</v>
       </c>
       <c r="B2026" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2026" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D2026">
-        <v>3.028</v>
+        <v>3.0209999999999999</v>
       </c>
       <c r="E2026" t="s">
         <v>22</v>
@@ -66172,10 +66207,10 @@
         <v>327</v>
       </c>
       <c r="B2027" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C2027" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D2027">
         <v>3.0209999999999999</v>
@@ -66207,13 +66242,13 @@
         <v>327</v>
       </c>
       <c r="B2028" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C2028" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D2028">
-        <v>3.0209999999999999</v>
+        <v>3.028</v>
       </c>
       <c r="E2028" t="s">
         <v>22</v>
@@ -66242,13 +66277,13 @@
         <v>327</v>
       </c>
       <c r="B2029" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C2029" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D2029">
-        <v>3.028</v>
+        <v>3.004</v>
       </c>
       <c r="E2029" t="s">
         <v>22</v>
@@ -66274,22 +66309,22 @@
     </row>
     <row r="2030" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2030" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B2030" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C2030" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D2030">
-        <v>3.004</v>
+        <v>3.097</v>
       </c>
       <c r="E2030" t="s">
         <v>22</v>
       </c>
       <c r="F2030">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2030">
         <v>100</v>
@@ -66312,13 +66347,13 @@
         <v>343</v>
       </c>
       <c r="B2031" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C2031" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D2031">
-        <v>3.097</v>
+        <v>3.1179999999999999</v>
       </c>
       <c r="E2031" t="s">
         <v>22</v>
@@ -66347,13 +66382,13 @@
         <v>343</v>
       </c>
       <c r="B2032" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C2032" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D2032">
-        <v>3.1179999999999999</v>
+        <v>3.1360000000000001</v>
       </c>
       <c r="E2032" t="s">
         <v>22</v>
@@ -66382,10 +66417,10 @@
         <v>343</v>
       </c>
       <c r="B2033" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C2033" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D2033">
         <v>3.1360000000000001</v>
@@ -66417,13 +66452,13 @@
         <v>343</v>
       </c>
       <c r="B2034" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C2034" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D2034">
-        <v>3.1360000000000001</v>
+        <v>3.141</v>
       </c>
       <c r="E2034" t="s">
         <v>22</v>
@@ -66452,13 +66487,13 @@
         <v>343</v>
       </c>
       <c r="B2035" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C2035" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D2035">
-        <v>3.141</v>
+        <v>2.6970000000000001</v>
       </c>
       <c r="E2035" t="s">
         <v>22</v>
@@ -66484,22 +66519,22 @@
     </row>
     <row r="2036" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2036" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B2036" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C2036" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D2036">
-        <v>2.6970000000000001</v>
+        <v>2.9940000000000002</v>
       </c>
       <c r="E2036" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F2036">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2036">
         <v>100</v>
@@ -66522,13 +66557,13 @@
         <v>356</v>
       </c>
       <c r="B2037" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C2037" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D2037">
-        <v>2.9940000000000002</v>
+        <v>2.992</v>
       </c>
       <c r="E2037" t="s">
         <v>14</v>
@@ -66557,13 +66592,13 @@
         <v>356</v>
       </c>
       <c r="B2038" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C2038" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D2038">
-        <v>2.992</v>
+        <v>2.996</v>
       </c>
       <c r="E2038" t="s">
         <v>14</v>
@@ -66592,13 +66627,13 @@
         <v>356</v>
       </c>
       <c r="B2039" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C2039" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D2039">
-        <v>2.996</v>
+        <v>2.9969999999999999</v>
       </c>
       <c r="E2039" t="s">
         <v>14</v>
@@ -66627,13 +66662,13 @@
         <v>356</v>
       </c>
       <c r="B2040" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C2040" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D2040">
-        <v>2.9969999999999999</v>
+        <v>2.996</v>
       </c>
       <c r="E2040" t="s">
         <v>14</v>
@@ -66662,10 +66697,10 @@
         <v>356</v>
       </c>
       <c r="B2041" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C2041" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D2041">
         <v>2.996</v>
@@ -66697,10 +66732,10 @@
         <v>356</v>
       </c>
       <c r="B2042" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C2042" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D2042">
         <v>2.996</v>
@@ -66732,13 +66767,13 @@
         <v>356</v>
       </c>
       <c r="B2043" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C2043" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D2043">
-        <v>2.996</v>
+        <v>2.9969999999999999</v>
       </c>
       <c r="E2043" t="s">
         <v>14</v>
@@ -66767,13 +66802,13 @@
         <v>356</v>
       </c>
       <c r="B2044" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C2044" t="s">
-        <v>372</v>
+        <v>102</v>
       </c>
       <c r="D2044">
-        <v>2.9969999999999999</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="E2044" t="s">
         <v>14</v>
@@ -66799,22 +66834,22 @@
     </row>
     <row r="2045" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2045" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B2045" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C2045" t="s">
-        <v>102</v>
+        <v>376</v>
       </c>
       <c r="D2045">
-        <v>0.14299999999999999</v>
+        <v>3.1080000000000001</v>
       </c>
       <c r="E2045" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F2045">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2045">
         <v>100</v>
@@ -66837,13 +66872,13 @@
         <v>374</v>
       </c>
       <c r="B2046" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C2046" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D2046">
-        <v>3.1080000000000001</v>
+        <v>3.1259999999999999</v>
       </c>
       <c r="E2046" t="s">
         <v>50</v>
@@ -66872,13 +66907,13 @@
         <v>374</v>
       </c>
       <c r="B2047" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C2047" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D2047">
-        <v>3.1259999999999999</v>
+        <v>3.125</v>
       </c>
       <c r="E2047" t="s">
         <v>50</v>
@@ -66907,13 +66942,13 @@
         <v>374</v>
       </c>
       <c r="B2048" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C2048" t="s">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="D2048">
-        <v>3.125</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="E2048" t="s">
         <v>50</v>
@@ -66939,22 +66974,22 @@
     </row>
     <row r="2049" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2049" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B2049" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C2049" t="s">
-        <v>102</v>
+        <v>384</v>
       </c>
       <c r="D2049">
-        <v>4.6340000000000003</v>
+        <v>3.016</v>
       </c>
       <c r="E2049" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F2049">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2049">
         <v>100</v>
@@ -66977,13 +67012,13 @@
         <v>382</v>
       </c>
       <c r="B2050" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C2050" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D2050">
-        <v>3.016</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E2050" t="s">
         <v>22</v>
@@ -67012,13 +67047,13 @@
         <v>382</v>
       </c>
       <c r="B2051" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C2051" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D2051">
-        <v>3.0270000000000001</v>
+        <v>3.024</v>
       </c>
       <c r="E2051" t="s">
         <v>22</v>
@@ -67047,13 +67082,13 @@
         <v>382</v>
       </c>
       <c r="B2052" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C2052" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D2052">
-        <v>3.024</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E2052" t="s">
         <v>22</v>
@@ -67082,10 +67117,10 @@
         <v>382</v>
       </c>
       <c r="B2053" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C2053" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D2053">
         <v>3.0270000000000001</v>
@@ -67117,13 +67152,13 @@
         <v>382</v>
       </c>
       <c r="B2054" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C2054" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D2054">
-        <v>3.0270000000000001</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E2054" t="s">
         <v>22</v>
@@ -67152,13 +67187,13 @@
         <v>382</v>
       </c>
       <c r="B2055" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C2055" t="s">
-        <v>394</v>
+        <v>102</v>
       </c>
       <c r="D2055">
-        <v>3.0129999999999999</v>
+        <v>3.0030000000000001</v>
       </c>
       <c r="E2055" t="s">
         <v>22</v>
@@ -67187,13 +67222,13 @@
         <v>382</v>
       </c>
       <c r="B2056" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C2056" t="s">
         <v>102</v>
       </c>
       <c r="D2056">
-        <v>3.0030000000000001</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="E2056" t="s">
         <v>22</v>
@@ -67219,22 +67254,22 @@
     </row>
     <row r="2057" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2057" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B2057" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C2057" t="s">
-        <v>102</v>
+        <v>399</v>
       </c>
       <c r="D2057">
-        <v>2.0249999999999999</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E2057" t="s">
         <v>22</v>
       </c>
       <c r="F2057">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G2057">
         <v>100</v>
@@ -67257,13 +67292,13 @@
         <v>397</v>
       </c>
       <c r="B2058" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C2058" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D2058">
-        <v>3.0009999999999999</v>
+        <v>2.8969999999999998</v>
       </c>
       <c r="E2058" t="s">
         <v>22</v>
@@ -67292,13 +67327,13 @@
         <v>397</v>
       </c>
       <c r="B2059" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C2059" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D2059">
-        <v>2.8969999999999998</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E2059" t="s">
         <v>22</v>
@@ -67324,22 +67359,22 @@
     </row>
     <row r="2060" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2060" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B2060" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C2060" t="s">
-        <v>403</v>
+        <v>31</v>
       </c>
       <c r="D2060">
-        <v>3.0059999999999998</v>
+        <v>3.036</v>
       </c>
       <c r="E2060" t="s">
         <v>22</v>
       </c>
       <c r="F2060">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2060">
         <v>100</v>
@@ -67362,13 +67397,13 @@
         <v>404</v>
       </c>
       <c r="B2061" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C2061" t="s">
         <v>31</v>
       </c>
       <c r="D2061">
-        <v>3.036</v>
+        <v>3.01</v>
       </c>
       <c r="E2061" t="s">
         <v>22</v>
@@ -67397,13 +67432,13 @@
         <v>404</v>
       </c>
       <c r="B2062" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C2062" t="s">
         <v>31</v>
       </c>
       <c r="D2062">
-        <v>3.01</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E2062" t="s">
         <v>22</v>
@@ -67432,13 +67467,13 @@
         <v>404</v>
       </c>
       <c r="B2063" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C2063" t="s">
         <v>31</v>
       </c>
       <c r="D2063">
-        <v>3.0150000000000001</v>
+        <v>3.0409999999999999</v>
       </c>
       <c r="E2063" t="s">
         <v>22</v>
@@ -67467,13 +67502,13 @@
         <v>404</v>
       </c>
       <c r="B2064" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C2064" t="s">
         <v>31</v>
       </c>
       <c r="D2064">
-        <v>3.0409999999999999</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E2064" t="s">
         <v>22</v>
@@ -67502,13 +67537,13 @@
         <v>404</v>
       </c>
       <c r="B2065" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C2065" t="s">
         <v>31</v>
       </c>
       <c r="D2065">
-        <v>3.0390000000000001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E2065" t="s">
         <v>22</v>
@@ -67537,7 +67572,7 @@
         <v>404</v>
       </c>
       <c r="B2066" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C2066" t="s">
         <v>31</v>
@@ -67572,13 +67607,13 @@
         <v>404</v>
       </c>
       <c r="B2067" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C2067" t="s">
         <v>31</v>
       </c>
       <c r="D2067">
-        <v>3.0009999999999999</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="E2067" t="s">
         <v>22</v>
@@ -67604,22 +67639,22 @@
     </row>
     <row r="2068" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2068" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B2068" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C2068" t="s">
-        <v>31</v>
+        <v>415</v>
       </c>
       <c r="D2068">
-        <v>0.71499999999999997</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E2068" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F2068">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2068">
         <v>100</v>
@@ -67642,13 +67677,13 @@
         <v>413</v>
       </c>
       <c r="B2069" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C2069" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D2069">
-        <v>3.0249999999999999</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E2069" t="s">
         <v>50</v>
@@ -67677,10 +67712,10 @@
         <v>413</v>
       </c>
       <c r="B2070" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C2070" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D2070">
         <v>3.0259999999999998</v>
@@ -67712,10 +67747,10 @@
         <v>413</v>
       </c>
       <c r="B2071" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C2071" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D2071">
         <v>3.0259999999999998</v>
@@ -67747,13 +67782,13 @@
         <v>413</v>
       </c>
       <c r="B2072" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C2072" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D2072">
-        <v>3.0259999999999998</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E2072" t="s">
         <v>50</v>
@@ -67782,10 +67817,10 @@
         <v>413</v>
       </c>
       <c r="B2073" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C2073" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D2073">
         <v>3.0249999999999999</v>
@@ -67817,13 +67852,13 @@
         <v>413</v>
       </c>
       <c r="B2074" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C2074" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D2074">
-        <v>3.0249999999999999</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E2074" t="s">
         <v>50</v>
@@ -67852,13 +67887,13 @@
         <v>413</v>
       </c>
       <c r="B2075" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C2075" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D2075">
-        <v>3.0259999999999998</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E2075" t="s">
         <v>50</v>
@@ -67887,13 +67922,13 @@
         <v>413</v>
       </c>
       <c r="B2076" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C2076" t="s">
-        <v>429</v>
+        <v>102</v>
       </c>
       <c r="D2076">
-        <v>3.0230000000000001</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="E2076" t="s">
         <v>50</v>
@@ -67919,16 +67954,16 @@
     </row>
     <row r="2077" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2077" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="B2077" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C2077" t="s">
-        <v>102</v>
+        <v>433</v>
       </c>
       <c r="D2077">
-        <v>0.84499999999999997</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E2077" t="s">
         <v>50</v>
@@ -67957,13 +67992,13 @@
         <v>431</v>
       </c>
       <c r="B2078" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C2078" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D2078">
-        <v>3.0059999999999998</v>
+        <v>3.0089999999999999</v>
       </c>
       <c r="E2078" t="s">
         <v>50</v>
@@ -67992,13 +68027,13 @@
         <v>431</v>
       </c>
       <c r="B2079" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C2079" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D2079">
-        <v>3.0089999999999999</v>
+        <v>3.0190000000000001</v>
       </c>
       <c r="E2079" t="s">
         <v>50</v>
@@ -68027,13 +68062,13 @@
         <v>431</v>
       </c>
       <c r="B2080" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C2080" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D2080">
-        <v>3.0190000000000001</v>
+        <v>3.012</v>
       </c>
       <c r="E2080" t="s">
         <v>50</v>
@@ -68062,10 +68097,10 @@
         <v>431</v>
       </c>
       <c r="B2081" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C2081" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D2081">
         <v>3.012</v>
@@ -68097,13 +68132,13 @@
         <v>431</v>
       </c>
       <c r="B2082" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C2082" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D2082">
-        <v>3.012</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E2082" t="s">
         <v>50</v>
@@ -68132,13 +68167,13 @@
         <v>431</v>
       </c>
       <c r="B2083" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C2083" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D2083">
-        <v>3.0470000000000002</v>
+        <v>3.0329999999999999</v>
       </c>
       <c r="E2083" t="s">
         <v>50</v>
@@ -68164,22 +68199,22 @@
     </row>
     <row r="2084" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2084" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="B2084" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C2084" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D2084">
-        <v>3.0329999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E2084" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F2084">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2084">
         <v>100</v>
@@ -68202,13 +68237,13 @@
         <v>446</v>
       </c>
       <c r="B2085" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C2085" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D2085">
-        <v>3.0550000000000002</v>
+        <v>3.1269999999999998</v>
       </c>
       <c r="E2085" t="s">
         <v>14</v>
@@ -68237,13 +68272,13 @@
         <v>446</v>
       </c>
       <c r="B2086" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C2086" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D2086">
-        <v>3.1269999999999998</v>
+        <v>3.089</v>
       </c>
       <c r="E2086" t="s">
         <v>14</v>
@@ -68272,13 +68307,13 @@
         <v>446</v>
       </c>
       <c r="B2087" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C2087" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D2087">
-        <v>3.089</v>
+        <v>3.0990000000000002</v>
       </c>
       <c r="E2087" t="s">
         <v>14</v>
@@ -68307,13 +68342,13 @@
         <v>446</v>
       </c>
       <c r="B2088" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C2088" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D2088">
-        <v>3.0990000000000002</v>
+        <v>3.093</v>
       </c>
       <c r="E2088" t="s">
         <v>14</v>
@@ -68342,13 +68377,13 @@
         <v>446</v>
       </c>
       <c r="B2089" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C2089" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D2089">
-        <v>3.093</v>
+        <v>3.0870000000000002</v>
       </c>
       <c r="E2089" t="s">
         <v>14</v>
@@ -68377,13 +68412,13 @@
         <v>446</v>
       </c>
       <c r="B2090" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C2090" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D2090">
-        <v>3.0870000000000002</v>
+        <v>3.089</v>
       </c>
       <c r="E2090" t="s">
         <v>14</v>
@@ -68412,13 +68447,13 @@
         <v>446</v>
       </c>
       <c r="B2091" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C2091" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D2091">
-        <v>3.089</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E2091" t="s">
         <v>14</v>
@@ -68444,22 +68479,22 @@
     </row>
     <row r="2092" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2092" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="B2092" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2092" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D2092">
-        <v>2.9039999999999999</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="E2092" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F2092">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2092">
         <v>100</v>
@@ -68482,13 +68517,13 @@
         <v>463</v>
       </c>
       <c r="B2093" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C2093" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D2093">
-        <v>3.0110000000000001</v>
+        <v>3.048</v>
       </c>
       <c r="E2093" t="s">
         <v>50</v>
@@ -68517,13 +68552,13 @@
         <v>463</v>
       </c>
       <c r="B2094" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C2094" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D2094">
-        <v>3.048</v>
+        <v>3.0510000000000002</v>
       </c>
       <c r="E2094" t="s">
         <v>50</v>
@@ -68552,13 +68587,13 @@
         <v>463</v>
       </c>
       <c r="B2095" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C2095" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D2095">
-        <v>3.0510000000000002</v>
+        <v>3.0190000000000001</v>
       </c>
       <c r="E2095" t="s">
         <v>50</v>
@@ -68587,13 +68622,13 @@
         <v>463</v>
       </c>
       <c r="B2096" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C2096" t="s">
-        <v>471</v>
+        <v>115</v>
       </c>
       <c r="D2096">
-        <v>3.0190000000000001</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="E2096" t="s">
         <v>50</v>
@@ -68619,22 +68654,22 @@
     </row>
     <row r="2097" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2097" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B2097" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C2097" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="D2097">
-        <v>0.44900000000000001</v>
+        <v>2.984</v>
       </c>
       <c r="E2097" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F2097">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2097">
         <v>100</v>
@@ -68657,13 +68692,13 @@
         <v>473</v>
       </c>
       <c r="B2098" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C2098" t="s">
         <v>31</v>
       </c>
       <c r="D2098">
-        <v>2.984</v>
+        <v>2.9780000000000002</v>
       </c>
       <c r="E2098" t="s">
         <v>22</v>
@@ -68692,13 +68727,13 @@
         <v>473</v>
       </c>
       <c r="B2099" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C2099" t="s">
         <v>31</v>
       </c>
       <c r="D2099">
-        <v>2.9780000000000002</v>
+        <v>2.9740000000000002</v>
       </c>
       <c r="E2099" t="s">
         <v>22</v>
@@ -68727,13 +68762,13 @@
         <v>473</v>
       </c>
       <c r="B2100" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C2100" t="s">
         <v>31</v>
       </c>
       <c r="D2100">
-        <v>2.9740000000000002</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="E2100" t="s">
         <v>22</v>
@@ -68759,22 +68794,22 @@
     </row>
     <row r="2101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2101" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B2101" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C2101" t="s">
         <v>31</v>
       </c>
       <c r="D2101">
-        <v>0.84399999999999997</v>
+        <v>3.016</v>
       </c>
       <c r="E2101" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F2101">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2101">
         <v>100</v>
@@ -68797,13 +68832,13 @@
         <v>478</v>
       </c>
       <c r="B2102" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C2102" t="s">
         <v>31</v>
       </c>
       <c r="D2102">
-        <v>3.016</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E2102" t="s">
         <v>14</v>
@@ -68832,13 +68867,13 @@
         <v>478</v>
       </c>
       <c r="B2103" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C2103" t="s">
         <v>31</v>
       </c>
       <c r="D2103">
-        <v>3.0150000000000001</v>
+        <v>3.016</v>
       </c>
       <c r="E2103" t="s">
         <v>14</v>
@@ -68867,13 +68902,13 @@
         <v>478</v>
       </c>
       <c r="B2104" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C2104" t="s">
         <v>31</v>
       </c>
       <c r="D2104">
-        <v>3.016</v>
+        <v>2.0779999999999998</v>
       </c>
       <c r="E2104" t="s">
         <v>14</v>
@@ -68899,22 +68934,22 @@
     </row>
     <row r="2105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2105" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B2105" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C2105" t="s">
-        <v>31</v>
+        <v>485</v>
       </c>
       <c r="D2105">
-        <v>2.0779999999999998</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E2105" t="s">
         <v>14</v>
       </c>
       <c r="F2105">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2105">
         <v>100</v>
@@ -68937,13 +68972,13 @@
         <v>483</v>
       </c>
       <c r="B2106" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C2106" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D2106">
-        <v>3.0249999999999999</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E2106" t="s">
         <v>14</v>
@@ -68972,13 +69007,13 @@
         <v>483</v>
       </c>
       <c r="B2107" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C2107" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D2107">
-        <v>3.0350000000000001</v>
+        <v>3.03</v>
       </c>
       <c r="E2107" t="s">
         <v>14</v>
@@ -69007,13 +69042,13 @@
         <v>483</v>
       </c>
       <c r="B2108" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C2108" t="s">
-        <v>489</v>
+        <v>102</v>
       </c>
       <c r="D2108">
-        <v>3.03</v>
+        <v>1.349</v>
       </c>
       <c r="E2108" t="s">
         <v>14</v>
@@ -69039,22 +69074,22 @@
     </row>
     <row r="2109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2109" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B2109" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C2109" t="s">
-        <v>102</v>
+        <v>493</v>
       </c>
       <c r="D2109">
-        <v>1.349</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E2109" t="s">
         <v>14</v>
       </c>
       <c r="F2109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2109">
         <v>100</v>
@@ -69077,10 +69112,10 @@
         <v>491</v>
       </c>
       <c r="B2110" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C2110" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D2110">
         <v>3.0249999999999999</v>
@@ -69112,13 +69147,13 @@
         <v>491</v>
       </c>
       <c r="B2111" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C2111" t="s">
-        <v>495</v>
+        <v>102</v>
       </c>
       <c r="D2111">
-        <v>3.0249999999999999</v>
+        <v>1.1240000000000001</v>
       </c>
       <c r="E2111" t="s">
         <v>14</v>
@@ -69144,22 +69179,22 @@
     </row>
     <row r="2112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2112" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B2112" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C2112" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D2112">
-        <v>1.1240000000000001</v>
+        <v>3.024</v>
       </c>
       <c r="E2112" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F2112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2112">
         <v>100</v>
@@ -69182,13 +69217,13 @@
         <v>497</v>
       </c>
       <c r="B2113" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2113" t="s">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D2113">
-        <v>3.024</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E2113" t="s">
         <v>22</v>
@@ -69217,13 +69252,13 @@
         <v>497</v>
       </c>
       <c r="B2114" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C2114" t="s">
-        <v>500</v>
+        <v>102</v>
       </c>
       <c r="D2114">
-        <v>3.0259999999999998</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="E2114" t="s">
         <v>22</v>
@@ -69249,34 +69284,25 @@
     </row>
     <row r="2115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2115" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B2115" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C2115" t="s">
-        <v>102</v>
+        <v>504</v>
       </c>
       <c r="D2115">
-        <v>2.6880000000000002</v>
+        <v>2.617</v>
       </c>
       <c r="E2115" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2115">
-        <v>4</v>
-      </c>
-      <c r="G2115">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H2115" t="s">
         <v>76</v>
       </c>
-      <c r="I2115" t="s">
-        <v>16</v>
-      </c>
       <c r="J2115" t="s">
-        <v>17</v>
+        <v>505</v>
       </c>
       <c r="K2115" t="s">
         <v>854</v>
@@ -69287,13 +69313,13 @@
         <v>502</v>
       </c>
       <c r="B2116" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C2116" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D2116">
-        <v>2.617</v>
+        <v>2.6970000000000001</v>
       </c>
       <c r="E2116" t="s">
         <v>50</v>
@@ -69313,13 +69339,13 @@
         <v>502</v>
       </c>
       <c r="B2117" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C2117" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D2117">
-        <v>2.6970000000000001</v>
+        <v>2.6709999999999998</v>
       </c>
       <c r="E2117" t="s">
         <v>50</v>
@@ -69339,13 +69365,13 @@
         <v>502</v>
       </c>
       <c r="B2118" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C2118" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D2118">
-        <v>2.6709999999999998</v>
+        <v>2.6680000000000001</v>
       </c>
       <c r="E2118" t="s">
         <v>50</v>
@@ -69365,10 +69391,10 @@
         <v>502</v>
       </c>
       <c r="B2119" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C2119" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D2119">
         <v>2.6680000000000001</v>
@@ -69388,16 +69414,16 @@
     </row>
     <row r="2120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2120" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B2120" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C2120" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D2120">
-        <v>2.6680000000000001</v>
+        <v>1.337</v>
       </c>
       <c r="E2120" t="s">
         <v>50</v>
@@ -69417,13 +69443,13 @@
         <v>514</v>
       </c>
       <c r="B2121" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C2121" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D2121">
-        <v>1.337</v>
+        <v>1.548</v>
       </c>
       <c r="E2121" t="s">
         <v>50</v>
@@ -69440,19 +69466,19 @@
     </row>
     <row r="2122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2122" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B2122" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C2122" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D2122">
-        <v>1.548</v>
+        <v>2.5179999999999998</v>
       </c>
       <c r="E2122" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H2122" t="s">
         <v>76</v>
@@ -69469,13 +69495,13 @@
         <v>519</v>
       </c>
       <c r="B2123" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C2123" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D2123">
-        <v>2.5179999999999998</v>
+        <v>2.5070000000000001</v>
       </c>
       <c r="E2123" t="s">
         <v>22</v>
@@ -69495,13 +69521,13 @@
         <v>519</v>
       </c>
       <c r="B2124" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C2124" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D2124">
-        <v>2.5070000000000001</v>
+        <v>1.2589999999999999</v>
       </c>
       <c r="E2124" t="s">
         <v>22</v>
@@ -69521,13 +69547,13 @@
         <v>519</v>
       </c>
       <c r="B2125" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C2125" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D2125">
-        <v>1.2589999999999999</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="E2125" t="s">
         <v>22</v>
@@ -69547,13 +69573,13 @@
         <v>519</v>
       </c>
       <c r="B2126" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C2126" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D2126">
-        <v>2.5299999999999998</v>
+        <v>2.548</v>
       </c>
       <c r="E2126" t="s">
         <v>22</v>
@@ -69573,13 +69599,13 @@
         <v>519</v>
       </c>
       <c r="B2127" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C2127" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D2127">
-        <v>2.548</v>
+        <v>2.5150000000000001</v>
       </c>
       <c r="E2127" t="s">
         <v>22</v>
@@ -69599,13 +69625,13 @@
         <v>519</v>
       </c>
       <c r="B2128" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C2128" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D2128">
-        <v>2.5150000000000001</v>
+        <v>2.5489999999999999</v>
       </c>
       <c r="E2128" t="s">
         <v>22</v>
@@ -69625,13 +69651,13 @@
         <v>519</v>
       </c>
       <c r="B2129" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C2129" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D2129">
-        <v>2.5489999999999999</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="E2129" t="s">
         <v>22</v>
@@ -69648,19 +69674,19 @@
     </row>
     <row r="2130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2130" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B2130" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C2130" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D2130">
-        <v>2.5049999999999999</v>
+        <v>2.4460000000000002</v>
       </c>
       <c r="E2130" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H2130" t="s">
         <v>76</v>
@@ -69674,16 +69700,16 @@
     </row>
     <row r="2131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2131" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B2131" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C2131" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D2131">
-        <v>2.4460000000000002</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="E2131" t="s">
         <v>50</v>
@@ -69703,13 +69729,13 @@
         <v>539</v>
       </c>
       <c r="B2132" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C2132" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D2132">
-        <v>2.1850000000000001</v>
+        <v>2.1890000000000001</v>
       </c>
       <c r="E2132" t="s">
         <v>50</v>
@@ -69729,13 +69755,13 @@
         <v>539</v>
       </c>
       <c r="B2133" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C2133" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D2133">
-        <v>2.1890000000000001</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="E2133" t="s">
         <v>50</v>
@@ -69755,13 +69781,13 @@
         <v>539</v>
       </c>
       <c r="B2134" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C2134" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D2134">
-        <v>2.1840000000000002</v>
+        <v>4.343</v>
       </c>
       <c r="E2134" t="s">
         <v>50</v>
@@ -69781,13 +69807,13 @@
         <v>539</v>
       </c>
       <c r="B2135" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C2135" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D2135">
-        <v>4.343</v>
+        <v>2.1469999999999998</v>
       </c>
       <c r="E2135" t="s">
         <v>50</v>
@@ -69807,13 +69833,13 @@
         <v>539</v>
       </c>
       <c r="B2136" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C2136" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D2136">
-        <v>2.1469999999999998</v>
+        <v>2.3490000000000002</v>
       </c>
       <c r="E2136" t="s">
         <v>50</v>
@@ -69833,13 +69859,13 @@
         <v>539</v>
       </c>
       <c r="B2137" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C2137" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D2137">
-        <v>2.3490000000000002</v>
+        <v>2.2909999999999999</v>
       </c>
       <c r="E2137" t="s">
         <v>50</v>
@@ -69859,13 +69885,13 @@
         <v>539</v>
       </c>
       <c r="B2138" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C2138" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D2138">
-        <v>2.2909999999999999</v>
+        <v>2.444</v>
       </c>
       <c r="E2138" t="s">
         <v>50</v>
@@ -69885,13 +69911,13 @@
         <v>539</v>
       </c>
       <c r="B2139" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C2139" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D2139">
-        <v>2.444</v>
+        <v>2.9380000000000002</v>
       </c>
       <c r="E2139" t="s">
         <v>50</v>
@@ -69911,13 +69937,13 @@
         <v>539</v>
       </c>
       <c r="B2140" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C2140" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D2140">
-        <v>2.9380000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="E2140" t="s">
         <v>50</v>
@@ -69934,16 +69960,16 @@
     </row>
     <row r="2141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2141" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="B2141" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C2141" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="D2141">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="E2141" t="s">
         <v>50</v>
@@ -69963,13 +69989,13 @@
         <v>559</v>
       </c>
       <c r="B2142" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C2142" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D2142">
-        <v>2.39</v>
+        <v>2.008</v>
       </c>
       <c r="E2142" t="s">
         <v>50</v>
@@ -69989,13 +70015,13 @@
         <v>559</v>
       </c>
       <c r="B2143" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C2143" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D2143">
-        <v>2.008</v>
+        <v>2.028</v>
       </c>
       <c r="E2143" t="s">
         <v>50</v>
@@ -70015,13 +70041,13 @@
         <v>559</v>
       </c>
       <c r="B2144" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C2144" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D2144">
-        <v>2.028</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="E2144" t="s">
         <v>50</v>
@@ -70041,13 +70067,13 @@
         <v>559</v>
       </c>
       <c r="B2145" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C2145" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D2145">
-        <v>1.6639999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E2145" t="s">
         <v>50</v>
@@ -70067,13 +70093,13 @@
         <v>559</v>
       </c>
       <c r="B2146" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C2146" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D2146">
-        <v>1.024</v>
+        <v>2.0049999999999999</v>
       </c>
       <c r="E2146" t="s">
         <v>50</v>
@@ -70093,13 +70119,13 @@
         <v>559</v>
       </c>
       <c r="B2147" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C2147" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D2147">
-        <v>2.0049999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="E2147" t="s">
         <v>50</v>
@@ -70119,13 +70145,13 @@
         <v>559</v>
       </c>
       <c r="B2148" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C2148" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D2148">
-        <v>1.0009999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="E2148" t="s">
         <v>50</v>
@@ -70145,13 +70171,13 @@
         <v>559</v>
       </c>
       <c r="B2149" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C2149" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D2149">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="E2149" t="s">
         <v>50</v>
@@ -70171,13 +70197,13 @@
         <v>559</v>
       </c>
       <c r="B2150" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C2150" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D2150">
-        <v>2.9</v>
+        <v>1.248</v>
       </c>
       <c r="E2150" t="s">
         <v>50</v>
@@ -70197,13 +70223,13 @@
         <v>559</v>
       </c>
       <c r="B2151" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C2151" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D2151">
-        <v>1.248</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E2151" t="s">
         <v>50</v>
@@ -70220,16 +70246,16 @@
     </row>
     <row r="2152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2152" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="B2152" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C2152" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D2152">
-        <v>1.0309999999999999</v>
+        <v>2.1659999999999999</v>
       </c>
       <c r="E2152" t="s">
         <v>50</v>
@@ -70249,13 +70275,13 @@
         <v>582</v>
       </c>
       <c r="B2153" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C2153" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D2153">
-        <v>2.1659999999999999</v>
+        <v>2.4159999999999999</v>
       </c>
       <c r="E2153" t="s">
         <v>50</v>
@@ -70275,13 +70301,13 @@
         <v>582</v>
       </c>
       <c r="B2154" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C2154" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D2154">
-        <v>2.4159999999999999</v>
+        <v>2.863</v>
       </c>
       <c r="E2154" t="s">
         <v>50</v>
@@ -70298,16 +70324,16 @@
     </row>
     <row r="2155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2155" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B2155" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C2155" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D2155">
-        <v>2.863</v>
+        <v>1.27</v>
       </c>
       <c r="E2155" t="s">
         <v>50</v>
@@ -70324,16 +70350,16 @@
     </row>
     <row r="2156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2156" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B2156" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="C2156" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D2156">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="E2156" t="s">
         <v>50</v>
@@ -70353,13 +70379,13 @@
         <v>592</v>
       </c>
       <c r="B2157" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C2157" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D2157">
-        <v>0.96</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="E2157" t="s">
         <v>50</v>
@@ -70379,13 +70405,13 @@
         <v>592</v>
       </c>
       <c r="B2158" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C2158" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D2158">
-        <v>1.8540000000000001</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="E2158" t="s">
         <v>50</v>
@@ -70402,25 +70428,25 @@
     </row>
     <row r="2159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2159" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B2159" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
       <c r="C2159" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D2159">
-        <v>0.95199999999999996</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="E2159" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H2159" t="s">
         <v>76</v>
       </c>
       <c r="J2159" t="s">
-        <v>505</v>
+        <v>598</v>
       </c>
       <c r="K2159" t="s">
         <v>854</v>
@@ -70431,13 +70457,13 @@
         <v>595</v>
       </c>
       <c r="B2160" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C2160" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D2160">
-        <v>1.0029999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="E2160" t="s">
         <v>22</v>
@@ -70457,13 +70483,13 @@
         <v>595</v>
       </c>
       <c r="B2161" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C2161" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D2161">
-        <v>1.0389999999999999</v>
+        <v>1.883</v>
       </c>
       <c r="E2161" t="s">
         <v>22</v>
@@ -70480,16 +70506,16 @@
     </row>
     <row r="2162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2162" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B2162" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C2162" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D2162">
-        <v>1.883</v>
+        <v>1.034</v>
       </c>
       <c r="E2162" t="s">
         <v>22</v>
@@ -70509,13 +70535,13 @@
         <v>603</v>
       </c>
       <c r="B2163" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C2163" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D2163">
-        <v>1.034</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="E2163" t="s">
         <v>22</v>
@@ -70527,32 +70553,6 @@
         <v>598</v>
       </c>
       <c r="K2163" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="2164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2164" t="s">
-        <v>603</v>
-      </c>
-      <c r="B2164" t="s">
-        <v>606</v>
-      </c>
-      <c r="C2164" t="s">
-        <v>607</v>
-      </c>
-      <c r="D2164">
-        <v>2.0350000000000001</v>
-      </c>
-      <c r="E2164" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2164" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2164" t="s">
-        <v>598</v>
-      </c>
-      <c r="K2164" t="s">
         <v>854</v>
       </c>
     </row>

--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -13148,7 +13148,7 @@
         <v>3.008</v>
       </c>
       <c r="E304" t="s">
-        <v>14</v>
+        <v>851</v>
       </c>
       <c r="F304">
         <v>6</v>
@@ -13180,7 +13180,7 @@
         <v>3.0870000000000002</v>
       </c>
       <c r="E305" t="s">
-        <v>14</v>
+        <v>851</v>
       </c>
       <c r="F305">
         <v>6</v>
@@ -13212,7 +13212,7 @@
         <v>3.0419999999999998</v>
       </c>
       <c r="E306" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F306">
         <v>6</v>
@@ -13244,7 +13244,7 @@
         <v>3.0219999999999998</v>
       </c>
       <c r="E307" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F307">
         <v>6</v>
@@ -13276,7 +13276,7 @@
         <v>3.0419999999999998</v>
       </c>
       <c r="E308" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F308">
         <v>6</v>
@@ -13308,7 +13308,7 @@
         <v>3.04</v>
       </c>
       <c r="E309" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F309">
         <v>6</v>
@@ -13340,7 +13340,7 @@
         <v>1.4450000000000001</v>
       </c>
       <c r="E310" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F310">
         <v>6</v>
@@ -13372,7 +13372,7 @@
         <v>3.0539999999999998</v>
       </c>
       <c r="E311" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="F311">
         <v>5</v>
@@ -13404,7 +13404,7 @@
         <v>3.0310000000000001</v>
       </c>
       <c r="E312" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="F312">
         <v>5</v>
@@ -13436,7 +13436,7 @@
         <v>3.05</v>
       </c>
       <c r="E313" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="F313">
         <v>5</v>
@@ -13596,7 +13596,7 @@
         <v>3.0960000000000001</v>
       </c>
       <c r="E318" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F318">
         <v>7</v>
@@ -13628,7 +13628,7 @@
         <v>3.105</v>
       </c>
       <c r="E319" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F319">
         <v>7</v>
@@ -13660,7 +13660,7 @@
         <v>3.1</v>
       </c>
       <c r="E320" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F320">
         <v>7</v>
@@ -13692,7 +13692,7 @@
         <v>3.093</v>
       </c>
       <c r="E321" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -13724,7 +13724,7 @@
         <v>3.0640000000000001</v>
       </c>
       <c r="E322" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F322">
         <v>7</v>
@@ -13753,10 +13753,10 @@
         <v>31</v>
       </c>
       <c r="D323">
-        <v>0.88400000000000001</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="E323" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F323">
         <v>7</v>
@@ -15644,7 +15644,7 @@
         <v>3.1230000000000002</v>
       </c>
       <c r="E382" t="s">
-        <v>14</v>
+        <v>851</v>
       </c>
       <c r="F382">
         <v>4</v>
@@ -15676,7 +15676,7 @@
         <v>3.1219999999999999</v>
       </c>
       <c r="E383" t="s">
-        <v>14</v>
+        <v>851</v>
       </c>
       <c r="F383">
         <v>4</v>
@@ -15708,7 +15708,7 @@
         <v>3.145</v>
       </c>
       <c r="E384" t="s">
-        <v>14</v>
+        <v>851</v>
       </c>
       <c r="F384">
         <v>4</v>
@@ -15740,7 +15740,7 @@
         <v>3.14</v>
       </c>
       <c r="E385" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F385">
         <v>4</v>
@@ -15772,7 +15772,7 @@
         <v>3.0779999999999998</v>
       </c>
       <c r="E386" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F386">
         <v>4</v>
@@ -15804,7 +15804,7 @@
         <v>3.077</v>
       </c>
       <c r="E387" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F387">
         <v>4</v>
@@ -15836,7 +15836,7 @@
         <v>3.1579999999999999</v>
       </c>
       <c r="E388" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F388">
         <v>4</v>
@@ -15868,7 +15868,7 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="E389" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F389">
         <v>4</v>
@@ -18300,7 +18300,7 @@
         <v>4.0510000000000002</v>
       </c>
       <c r="E465" t="s">
-        <v>90</v>
+        <v>851</v>
       </c>
       <c r="F465">
         <v>2</v>
@@ -18332,7 +18332,7 @@
         <v>3.02</v>
       </c>
       <c r="E466" t="s">
-        <v>90</v>
+        <v>851</v>
       </c>
       <c r="F466">
         <v>2</v>
@@ -18364,7 +18364,7 @@
         <v>3.02</v>
       </c>
       <c r="E467" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F467">
         <v>2</v>
@@ -18396,7 +18396,7 @@
         <v>3.028</v>
       </c>
       <c r="E468" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F468">
         <v>2</v>
@@ -18428,7 +18428,7 @@
         <v>3.0209999999999999</v>
       </c>
       <c r="E469" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F469">
         <v>2</v>
@@ -18460,7 +18460,7 @@
         <v>3.0209999999999999</v>
       </c>
       <c r="E470" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F470">
         <v>2</v>
@@ -18492,7 +18492,7 @@
         <v>3.028</v>
       </c>
       <c r="E471" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F471">
         <v>2</v>
@@ -18524,7 +18524,7 @@
         <v>3.004</v>
       </c>
       <c r="E472" t="s">
-        <v>22</v>
+        <v>851</v>
       </c>
       <c r="F472">
         <v>2</v>
@@ -19036,7 +19036,7 @@
         <v>3.1080000000000001</v>
       </c>
       <c r="E488" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F488">
         <v>7</v>
@@ -19068,7 +19068,7 @@
         <v>3.1259999999999999</v>
       </c>
       <c r="E489" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F489">
         <v>7</v>
@@ -19100,7 +19100,7 @@
         <v>3.125</v>
       </c>
       <c r="E490" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F490">
         <v>7</v>
@@ -19132,7 +19132,7 @@
         <v>4.6340000000000003</v>
       </c>
       <c r="E491" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F491">
         <v>7</v>
@@ -20540,7 +20540,7 @@
         <v>3.0110000000000001</v>
       </c>
       <c r="E535" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F535">
         <v>7</v>
@@ -20572,7 +20572,7 @@
         <v>3.048</v>
       </c>
       <c r="E536" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F536">
         <v>7</v>
@@ -20604,7 +20604,7 @@
         <v>3.0510000000000002</v>
       </c>
       <c r="E537" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F537">
         <v>7</v>
@@ -20636,7 +20636,7 @@
         <v>3.0190000000000001</v>
       </c>
       <c r="E538" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F538">
         <v>7</v>
@@ -20668,7 +20668,7 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="E539" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F539">
         <v>7</v>
